--- a/youzi/新生代/index.xlsx
+++ b/youzi/新生代/index.xlsx
@@ -39,12 +39,72 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF29A746"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB5E0BF"/>
         <bgColor/>
       </patternFill>
@@ -57,30 +117,1500 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8B94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D0D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D0D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF8F0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF79C88B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1E2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35D6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAADCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF35AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1ECD7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C1C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3FB059"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8993"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF22903C"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -93,19 +1623,757 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3646"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3606D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA4AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0ECD7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD63242"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -117,18 +2385,162 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8891"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE3C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -153,6 +2565,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -165,7 +2583,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -177,12 +2595,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -195,2563 +2607,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8B94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D0D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D0D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF8F0"/>
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD6AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD6AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46572"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46572"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD6AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4636F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF79C88B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1E2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAADCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1ECD7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF35AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C1C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3FB059"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8993"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3606D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3646"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0ECD7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8891"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBAE3C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46572"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46572"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4636F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -7642,7 +7642,7 @@
       <c r="C2" t="str">
         <v>002238</v>
       </c>
-      <c r="D2" s="10" t="str">
+      <c r="D2" s="6" t="str">
         <v>净卖: -808.36万</v>
       </c>
       <c r="E2">
@@ -7657,40 +7657,40 @@
       <c r="H2">
         <v>4.28</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>5.53</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="7">
         <v>-4.96</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="12">
         <v>-1.72</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="2">
         <v>-6.11</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="3">
         <v>-6.87</v>
       </c>
-      <c r="N2" s="7">
+      <c r="N2" s="8">
         <v>-8.3</v>
       </c>
-      <c r="O2" s="3">
+      <c r="O2" s="13">
         <v>-8.78</v>
       </c>
-      <c r="P2" s="8">
+      <c r="P2" s="11">
         <v>-12.21</v>
       </c>
-      <c r="Q2" s="13">
+      <c r="Q2" s="9">
         <v>-13.17</v>
       </c>
       <c r="R2" s="4">
         <v>-14.03</v>
       </c>
-      <c r="S2" s="9">
+      <c r="S2" s="1">
         <v>-13.84</v>
       </c>
-      <c r="T2" s="6">
+      <c r="T2" s="5">
         <v>-30.15</v>
       </c>
     </row>
@@ -7704,7 +7704,7 @@
       <c r="C3" t="str">
         <v>002238</v>
       </c>
-      <c r="D3" s="22" t="str">
+      <c r="D3" s="17" t="str">
         <v>净卖: -1634.66万</v>
       </c>
       <c r="E3">
@@ -7719,40 +7719,40 @@
       <c r="H3">
         <v>-0.54</v>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="22">
         <v>-9.45</v>
       </c>
-      <c r="J3" s="24">
+      <c r="J3" s="14">
         <v>-6.36</v>
       </c>
-      <c r="K3" s="25">
+      <c r="K3" s="18">
         <v>-10.55</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="19">
         <v>-11.27</v>
       </c>
-      <c r="M3" s="26">
+      <c r="M3" s="25">
         <v>-12.64</v>
       </c>
-      <c r="N3" s="17">
+      <c r="N3" s="23">
         <v>-13.09</v>
       </c>
-      <c r="O3" s="19">
+      <c r="O3" s="26">
         <v>-16.36</v>
       </c>
-      <c r="P3" s="14">
+      <c r="P3" s="15">
         <v>-17.27</v>
       </c>
-      <c r="Q3" s="15">
+      <c r="Q3" s="20">
         <v>-18.09</v>
       </c>
-      <c r="R3" s="18">
+      <c r="R3" s="16">
         <v>-17.91</v>
       </c>
-      <c r="S3" s="20">
+      <c r="S3" s="21">
         <v>-17.55</v>
       </c>
-      <c r="T3" s="21">
+      <c r="T3" s="24">
         <v>-33.45</v>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
       <c r="C4" t="str">
         <v>600540</v>
       </c>
-      <c r="D4" s="39" t="str">
+      <c r="D4" s="30" t="str">
         <v>净卖: -203.46万</v>
       </c>
       <c r="E4">
@@ -7781,40 +7781,40 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" s="27">
+      <c r="I4" s="31">
         <v>10.08</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="32">
         <v>21.19</v>
       </c>
       <c r="K4" s="29">
         <v>33.33</v>
       </c>
-      <c r="L4" s="30">
+      <c r="L4" s="33">
         <v>46.77</v>
       </c>
-      <c r="M4" s="36">
+      <c r="M4" s="34">
         <v>61.5</v>
       </c>
       <c r="N4" s="35">
         <v>45.48</v>
       </c>
-      <c r="O4" s="31">
+      <c r="O4" s="39">
         <v>53.23</v>
       </c>
-      <c r="P4" s="32">
+      <c r="P4" s="36">
         <v>58.66</v>
       </c>
-      <c r="Q4" s="37">
+      <c r="Q4" s="27">
         <v>51.94</v>
       </c>
-      <c r="R4" s="38">
+      <c r="R4" s="28">
         <v>36.69</v>
       </c>
-      <c r="S4" s="34">
+      <c r="S4" s="37">
         <v>23</v>
       </c>
-      <c r="T4" s="33">
+      <c r="T4" s="38">
         <v>22.74</v>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       <c r="C5" t="str">
         <v>002041</v>
       </c>
-      <c r="D5" s="48" t="str">
+      <c r="D5" s="40" t="str">
         <v>净卖: -388.51万</v>
       </c>
       <c r="E5">
@@ -7843,40 +7843,40 @@
       <c r="H5">
         <v>4.75</v>
       </c>
-      <c r="I5" s="42">
+      <c r="I5" s="49">
         <v>4.91</v>
       </c>
-      <c r="J5" s="49">
+      <c r="J5" s="41">
         <v>15.37</v>
       </c>
-      <c r="K5" s="50">
+      <c r="K5" s="42">
         <v>10.56</v>
       </c>
       <c r="L5" s="43">
         <v>11.76</v>
       </c>
-      <c r="M5" s="51">
+      <c r="M5" s="44">
         <v>4.07</v>
       </c>
-      <c r="N5" s="44">
+      <c r="N5" s="45">
         <v>5.09</v>
       </c>
-      <c r="O5" s="45">
+      <c r="O5" s="46">
         <v>2.87</v>
       </c>
-      <c r="P5" s="52">
+      <c r="P5" s="51">
         <v>0.56</v>
       </c>
-      <c r="Q5" s="40">
+      <c r="Q5" s="47">
         <v>0.19</v>
       </c>
-      <c r="R5" s="41">
+      <c r="R5" s="48">
         <v>-3.15</v>
       </c>
-      <c r="S5" s="46">
+      <c r="S5" s="50">
         <v>-2.31</v>
       </c>
-      <c r="T5" s="47">
+      <c r="T5" s="52">
         <v>-4.35</v>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       <c r="C6" t="str">
         <v>001368</v>
       </c>
-      <c r="D6" s="53" t="str">
+      <c r="D6" s="59" t="str">
         <v>净卖: -491.53万</v>
       </c>
       <c r="E6">
@@ -7905,40 +7905,40 @@
       <c r="H6">
         <v>9.99</v>
       </c>
-      <c r="I6" s="60">
+      <c r="I6" s="61">
         <v>0</v>
       </c>
-      <c r="J6" s="59">
+      <c r="J6" s="55">
         <v>-9.94</v>
       </c>
-      <c r="K6" s="63">
+      <c r="K6" s="62">
         <v>-12.52</v>
       </c>
-      <c r="L6" s="61">
+      <c r="L6" s="63">
         <v>-3.79</v>
       </c>
-      <c r="M6" s="62">
+      <c r="M6" s="56">
         <v>-1.89</v>
       </c>
-      <c r="N6" s="54">
+      <c r="N6" s="64">
         <v>-5.64</v>
       </c>
-      <c r="O6" s="64">
+      <c r="O6" s="65">
         <v>-7.27</v>
       </c>
-      <c r="P6" s="55">
+      <c r="P6" s="53">
         <v>-8.13</v>
       </c>
-      <c r="Q6" s="56">
+      <c r="Q6" s="60">
         <v>-8.91</v>
       </c>
       <c r="R6" s="57">
         <v>-8.61</v>
       </c>
-      <c r="S6" s="58">
+      <c r="S6" s="54">
         <v>-5.85</v>
       </c>
-      <c r="T6" s="65">
+      <c r="T6" s="58">
         <v>20.4</v>
       </c>
     </row>
@@ -7952,7 +7952,7 @@
       <c r="C7" t="str">
         <v>603516</v>
       </c>
-      <c r="D7" s="71" t="str">
+      <c r="D7" s="66" t="str">
         <v>净买: 374.25万</v>
       </c>
       <c r="E7">
@@ -7967,40 +7967,40 @@
       <c r="H7">
         <v>-10.01</v>
       </c>
-      <c r="I7" s="72">
+      <c r="I7" s="75">
         <v>0</v>
       </c>
-      <c r="J7" s="74">
+      <c r="J7" s="71">
         <v>4.02</v>
       </c>
-      <c r="K7" s="70">
+      <c r="K7" s="67">
         <v>2.06</v>
       </c>
-      <c r="L7" s="66">
+      <c r="L7" s="68">
         <v>3.75</v>
       </c>
-      <c r="M7" s="67">
+      <c r="M7" s="73">
         <v>7.52</v>
       </c>
-      <c r="N7" s="75">
+      <c r="N7" s="76">
         <v>6.86</v>
       </c>
-      <c r="O7" s="76">
+      <c r="O7" s="77">
         <v>11.67</v>
       </c>
-      <c r="P7" s="68">
+      <c r="P7" s="74">
         <v>9.4</v>
       </c>
-      <c r="Q7" s="77">
+      <c r="Q7" s="72">
         <v>11.63</v>
       </c>
-      <c r="R7" s="78">
+      <c r="R7" s="69">
         <v>11.12</v>
       </c>
-      <c r="S7" s="69">
+      <c r="S7" s="70">
         <v>9.79</v>
       </c>
-      <c r="T7" s="73">
+      <c r="T7" s="78">
         <v>345.15</v>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       <c r="C8" t="str">
         <v>002510</v>
       </c>
-      <c r="D8" s="82" t="str">
+      <c r="D8" s="79" t="str">
         <v>净卖: -764.76万</v>
       </c>
       <c r="E8">
@@ -8029,37 +8029,37 @@
       <c r="H8">
         <v>10.06</v>
       </c>
-      <c r="I8" s="83">
+      <c r="I8" s="80">
         <v>0</v>
       </c>
-      <c r="J8" s="79">
+      <c r="J8" s="89">
         <v>10</v>
       </c>
-      <c r="K8" s="80">
+      <c r="K8" s="90">
         <v>21</v>
       </c>
-      <c r="L8" s="89">
+      <c r="L8" s="84">
         <v>17.57</v>
       </c>
-      <c r="M8" s="90">
+      <c r="M8" s="91">
         <v>5.86</v>
       </c>
       <c r="N8" s="81">
         <v>1.57</v>
       </c>
-      <c r="O8" s="86">
+      <c r="O8" s="85">
         <v>3.57</v>
       </c>
-      <c r="P8" s="84">
+      <c r="P8" s="87">
         <v>1.14</v>
       </c>
-      <c r="Q8" s="87">
+      <c r="Q8" s="86">
         <v>1.14</v>
       </c>
-      <c r="R8" s="91">
+      <c r="R8" s="82">
         <v>-4.57</v>
       </c>
-      <c r="S8" s="85">
+      <c r="S8" s="83">
         <v>-2.71</v>
       </c>
       <c r="T8" s="88">
@@ -8076,7 +8076,7 @@
       <c r="C9" t="str">
         <v>600367</v>
       </c>
-      <c r="D9" s="104" t="str">
+      <c r="D9" s="102" t="str">
         <v>净买: 3583.76万</v>
       </c>
       <c r="E9">
@@ -8091,40 +8091,40 @@
       <c r="H9">
         <v>4.52</v>
       </c>
-      <c r="I9" s="95">
+      <c r="I9" s="96">
         <v>-0.98</v>
       </c>
-      <c r="J9" s="93">
+      <c r="J9" s="103">
         <v>-4.07</v>
       </c>
-      <c r="K9" s="96">
+      <c r="K9" s="97">
         <v>-0.39</v>
       </c>
-      <c r="L9" s="97">
+      <c r="L9" s="93">
         <v>5.44</v>
       </c>
-      <c r="M9" s="100">
+      <c r="M9" s="94">
         <v>5.18</v>
       </c>
-      <c r="N9" s="101">
+      <c r="N9" s="92">
         <v>12.52</v>
       </c>
-      <c r="O9" s="92">
+      <c r="O9" s="98">
         <v>1.25</v>
       </c>
-      <c r="P9" s="98">
+      <c r="P9" s="104">
         <v>11.34</v>
       </c>
-      <c r="Q9" s="99">
+      <c r="Q9" s="95">
         <v>4.07</v>
       </c>
-      <c r="R9" s="94">
+      <c r="R9" s="99">
         <v>0.26</v>
       </c>
-      <c r="S9" s="102">
+      <c r="S9" s="100">
         <v>2.89</v>
       </c>
-      <c r="T9" s="103">
+      <c r="T9" s="101">
         <v>40.07</v>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       <c r="C10" t="str">
         <v>603585</v>
       </c>
-      <c r="D10" s="110" t="str">
+      <c r="D10" s="115" t="str">
         <v>净买: 620.83万</v>
       </c>
       <c r="E10">
@@ -8153,37 +8153,37 @@
       <c r="H10">
         <v>-7.49</v>
       </c>
-      <c r="I10" s="111">
+      <c r="I10" s="110">
         <v>-2.7</v>
       </c>
-      <c r="J10" s="112">
+      <c r="J10" s="107">
         <v>-7</v>
       </c>
-      <c r="K10" s="113">
+      <c r="K10" s="116">
         <v>-4.8</v>
       </c>
-      <c r="L10" s="117">
+      <c r="L10" s="108">
         <v>-5.45</v>
       </c>
-      <c r="M10" s="114">
+      <c r="M10" s="111">
         <v>-7.65</v>
       </c>
-      <c r="N10" s="107">
+      <c r="N10" s="112">
         <v>-8.8</v>
       </c>
-      <c r="O10" s="115">
+      <c r="O10" s="105">
         <v>-8.55</v>
       </c>
-      <c r="P10" s="105">
+      <c r="P10" s="113">
         <v>-7.55</v>
       </c>
       <c r="Q10" s="106">
         <v>-1.95</v>
       </c>
-      <c r="R10" s="108">
+      <c r="R10" s="117">
         <v>-3.1</v>
       </c>
-      <c r="S10" s="116">
+      <c r="S10" s="114">
         <v>6.6</v>
       </c>
       <c r="T10" s="109">
@@ -8200,7 +8200,7 @@
       <c r="C11" t="str">
         <v>600962</v>
       </c>
-      <c r="D11" s="127" t="str">
+      <c r="D11" s="130" t="str">
         <v>净卖: -17.88万</v>
       </c>
       <c r="E11">
@@ -8215,40 +8215,40 @@
       <c r="H11">
         <v>10.03</v>
       </c>
-      <c r="I11" s="119">
+      <c r="I11" s="126">
         <v>0</v>
       </c>
-      <c r="J11" s="120">
+      <c r="J11" s="127">
         <v>10.01</v>
       </c>
-      <c r="K11" s="124">
+      <c r="K11" s="128">
         <v>21.03</v>
       </c>
-      <c r="L11" s="122">
+      <c r="L11" s="123">
         <v>19.13</v>
       </c>
-      <c r="M11" s="128">
+      <c r="M11" s="125">
         <v>9.62</v>
       </c>
-      <c r="N11" s="125">
+      <c r="N11" s="124">
         <v>16.33</v>
       </c>
-      <c r="O11" s="129">
+      <c r="O11" s="118">
         <v>18.74</v>
       </c>
-      <c r="P11" s="130">
+      <c r="P11" s="129">
         <v>18.01</v>
       </c>
-      <c r="Q11" s="123">
+      <c r="Q11" s="119">
         <v>14.09</v>
       </c>
-      <c r="R11" s="121">
+      <c r="R11" s="120">
         <v>10.91</v>
       </c>
-      <c r="S11" s="126">
+      <c r="S11" s="121">
         <v>10.29</v>
       </c>
-      <c r="T11" s="118">
+      <c r="T11" s="122">
         <v>15.83</v>
       </c>
     </row>
@@ -8262,7 +8262,7 @@
       <c r="C12" t="str">
         <v>003037</v>
       </c>
-      <c r="D12" s="139" t="str">
+      <c r="D12" s="134" t="str">
         <v>净卖: -2233.11万</v>
       </c>
       <c r="E12">
@@ -8283,34 +8283,34 @@
       <c r="J12" s="133">
         <v>8.77</v>
       </c>
-      <c r="K12" s="141">
+      <c r="K12" s="135">
         <v>-1.89</v>
       </c>
-      <c r="L12" s="137">
+      <c r="L12" s="139">
         <v>-3.22</v>
       </c>
-      <c r="M12" s="142">
+      <c r="M12" s="143">
         <v>6.44</v>
       </c>
-      <c r="N12" s="143">
+      <c r="N12" s="140">
         <v>17.09</v>
       </c>
-      <c r="O12" s="134">
+      <c r="O12" s="131">
         <v>16.09</v>
       </c>
-      <c r="P12" s="135">
+      <c r="P12" s="141">
         <v>14.32</v>
       </c>
       <c r="Q12" s="136">
         <v>4.88</v>
       </c>
-      <c r="R12" s="131">
+      <c r="R12" s="137">
         <v>3.77</v>
       </c>
       <c r="S12" s="138">
         <v>4</v>
       </c>
-      <c r="T12" s="140">
+      <c r="T12" s="142">
         <v>-20.87</v>
       </c>
     </row>
@@ -8324,7 +8324,7 @@
       <c r="C13" t="str">
         <v>001306</v>
       </c>
-      <c r="D13" s="154" t="str">
+      <c r="D13" s="156" t="str">
         <v>净卖: -462.25万</v>
       </c>
       <c r="E13">
@@ -8339,40 +8339,40 @@
       <c r="H13">
         <v>0.03</v>
       </c>
-      <c r="I13" s="148">
+      <c r="I13" s="144">
         <v>6.62</v>
       </c>
-      <c r="J13" s="146">
+      <c r="J13" s="150">
         <v>17.29</v>
       </c>
-      <c r="K13" s="149">
+      <c r="K13" s="154">
         <v>22.79</v>
       </c>
-      <c r="L13" s="150">
+      <c r="L13" s="155">
         <v>28.15</v>
       </c>
-      <c r="M13" s="152">
+      <c r="M13" s="151">
         <v>23.18</v>
       </c>
-      <c r="N13" s="151">
+      <c r="N13" s="152">
         <v>22.64</v>
       </c>
-      <c r="O13" s="155">
+      <c r="O13" s="153">
         <v>27.89</v>
       </c>
-      <c r="P13" s="156">
+      <c r="P13" s="147">
         <v>23.34</v>
       </c>
-      <c r="Q13" s="144">
+      <c r="Q13" s="145">
         <v>24.33</v>
       </c>
-      <c r="R13" s="147">
+      <c r="R13" s="148">
         <v>22.68</v>
       </c>
-      <c r="S13" s="145">
+      <c r="S13" s="149">
         <v>28.62</v>
       </c>
-      <c r="T13" s="153">
+      <c r="T13" s="146">
         <v>-13.98</v>
       </c>
     </row>
@@ -8401,40 +8401,40 @@
       <c r="H14">
         <v>-2.07</v>
       </c>
-      <c r="I14" s="166">
+      <c r="I14" s="157">
         <v>12.29</v>
       </c>
-      <c r="J14" s="167">
+      <c r="J14" s="162">
         <v>17.19</v>
       </c>
       <c r="K14" s="158">
         <v>10.41</v>
       </c>
-      <c r="L14" s="168">
+      <c r="L14" s="163">
         <v>21.42</v>
       </c>
-      <c r="M14" s="169">
+      <c r="M14" s="159">
         <v>15.91</v>
       </c>
-      <c r="N14" s="165">
+      <c r="N14" s="168">
         <v>4.3</v>
       </c>
-      <c r="O14" s="157">
+      <c r="O14" s="164">
         <v>-1.96</v>
       </c>
-      <c r="P14" s="159">
+      <c r="P14" s="169">
         <v>-1.06</v>
       </c>
       <c r="Q14" s="160">
         <v>-0.75</v>
       </c>
-      <c r="R14" s="162">
+      <c r="R14" s="165">
         <v>-0.98</v>
       </c>
-      <c r="S14" s="163">
+      <c r="S14" s="166">
         <v>-4.68</v>
       </c>
-      <c r="T14" s="164">
+      <c r="T14" s="167">
         <v>-6.03</v>
       </c>
     </row>
@@ -8448,7 +8448,7 @@
       <c r="C15" t="str">
         <v>605133</v>
       </c>
-      <c r="D15" s="178" t="str">
+      <c r="D15" s="180" t="str">
         <v>净买: 3043.68万</v>
       </c>
       <c r="E15">
@@ -8463,40 +8463,40 @@
       <c r="H15">
         <v>-0.11</v>
       </c>
-      <c r="I15" s="170">
+      <c r="I15" s="177">
         <v>10.11</v>
       </c>
-      <c r="J15" s="176">
+      <c r="J15" s="181">
         <v>6.15</v>
       </c>
-      <c r="K15" s="179">
+      <c r="K15" s="182">
         <v>-4.46</v>
       </c>
-      <c r="L15" s="177">
+      <c r="L15" s="170">
         <v>-0.27</v>
       </c>
-      <c r="M15" s="171">
+      <c r="M15" s="179">
         <v>3.14</v>
       </c>
-      <c r="N15" s="172">
+      <c r="N15" s="174">
         <v>1.53</v>
       </c>
-      <c r="O15" s="180">
+      <c r="O15" s="171">
         <v>-1.62</v>
       </c>
-      <c r="P15" s="174">
+      <c r="P15" s="172">
         <v>-0.46</v>
       </c>
-      <c r="Q15" s="181">
+      <c r="Q15" s="173">
         <v>-2.94</v>
       </c>
-      <c r="R15" s="182">
+      <c r="R15" s="175">
         <v>-0.55</v>
       </c>
-      <c r="S15" s="175">
+      <c r="S15" s="178">
         <v>9.41</v>
       </c>
-      <c r="T15" s="173">
+      <c r="T15" s="176">
         <v>-26.38</v>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       <c r="C16" t="str">
         <v>301533</v>
       </c>
-      <c r="D16" s="195" t="str">
+      <c r="D16" s="190" t="str">
         <v>净卖: -733.04万</v>
       </c>
       <c r="E16">
@@ -8525,40 +8525,40 @@
       <c r="H16">
         <v>2.26</v>
       </c>
-      <c r="I16" s="183">
+      <c r="I16" s="191">
         <v>3.46</v>
       </c>
-      <c r="J16" s="191">
+      <c r="J16" s="186">
         <v>8.33</v>
       </c>
-      <c r="K16" s="188">
+      <c r="K16" s="187">
         <v>10.64</v>
       </c>
-      <c r="L16" s="184">
+      <c r="L16" s="192">
         <v>7.14</v>
       </c>
-      <c r="M16" s="192">
+      <c r="M16" s="193">
         <v>11.64</v>
       </c>
-      <c r="N16" s="193">
+      <c r="N16" s="194">
         <v>6.19</v>
       </c>
-      <c r="O16" s="185">
+      <c r="O16" s="188">
         <v>3.76</v>
       </c>
-      <c r="P16" s="189">
+      <c r="P16" s="183">
         <v>0.97</v>
       </c>
-      <c r="Q16" s="186">
+      <c r="Q16" s="184">
         <v>-1.04</v>
       </c>
-      <c r="R16" s="187">
+      <c r="R16" s="195">
         <v>-2.01</v>
       </c>
-      <c r="S16" s="194">
+      <c r="S16" s="185">
         <v>-5.7</v>
       </c>
-      <c r="T16" s="190">
+      <c r="T16" s="189">
         <v>-18.85</v>
       </c>
     </row>
@@ -8572,7 +8572,7 @@
       <c r="C17" t="str">
         <v>688148</v>
       </c>
-      <c r="D17" s="200" t="str">
+      <c r="D17" s="202" t="str">
         <v>净卖: -1051.47万</v>
       </c>
       <c r="E17">
@@ -8587,40 +8587,40 @@
       <c r="H17">
         <v>4.34</v>
       </c>
-      <c r="I17" s="208">
+      <c r="I17" s="199">
         <v>15.03</v>
       </c>
-      <c r="J17" s="196">
+      <c r="J17" s="200">
         <v>37.63</v>
       </c>
       <c r="K17" s="201">
         <v>33.37</v>
       </c>
-      <c r="L17" s="197">
+      <c r="L17" s="208">
         <v>33.9</v>
       </c>
-      <c r="M17" s="206">
+      <c r="M17" s="203">
         <v>29</v>
       </c>
-      <c r="N17" s="198">
+      <c r="N17" s="196">
         <v>24.95</v>
       </c>
-      <c r="O17" s="207">
+      <c r="O17" s="197">
         <v>20.36</v>
       </c>
-      <c r="P17" s="205">
+      <c r="P17" s="204">
         <v>18.44</v>
       </c>
-      <c r="Q17" s="202">
+      <c r="Q17" s="205">
         <v>13.11</v>
       </c>
-      <c r="R17" s="203">
+      <c r="R17" s="206">
         <v>1.49</v>
       </c>
-      <c r="S17" s="199">
+      <c r="S17" s="198">
         <v>-1.39</v>
       </c>
-      <c r="T17" s="204">
+      <c r="T17" s="207">
         <v>-0.43</v>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       <c r="C18" t="str">
         <v>688148</v>
       </c>
-      <c r="D18" s="221" t="str">
+      <c r="D18" s="212" t="str">
         <v>净卖: -2325.34万</v>
       </c>
       <c r="E18">
@@ -8649,40 +8649,40 @@
       <c r="H18">
         <v>5.56</v>
       </c>
-      <c r="I18" s="214">
+      <c r="I18" s="217">
         <v>13.35</v>
       </c>
-      <c r="J18" s="215">
+      <c r="J18" s="209">
         <v>9.83</v>
       </c>
-      <c r="K18" s="209">
+      <c r="K18" s="218">
         <v>10.27</v>
       </c>
-      <c r="L18" s="210">
+      <c r="L18" s="214">
         <v>6.23</v>
       </c>
-      <c r="M18" s="211">
+      <c r="M18" s="219">
         <v>2.9</v>
       </c>
-      <c r="N18" s="217">
+      <c r="N18" s="220">
         <v>-0.88</v>
       </c>
-      <c r="O18" s="212">
+      <c r="O18" s="221">
         <v>-2.46</v>
       </c>
-      <c r="P18" s="213">
+      <c r="P18" s="210">
         <v>-6.85</v>
       </c>
-      <c r="Q18" s="216">
+      <c r="Q18" s="213">
         <v>-16.42</v>
       </c>
-      <c r="R18" s="218">
+      <c r="R18" s="215">
         <v>-18.79</v>
       </c>
-      <c r="S18" s="220">
+      <c r="S18" s="211">
         <v>-16.86</v>
       </c>
-      <c r="T18" s="219">
+      <c r="T18" s="216">
         <v>-18</v>
       </c>
     </row>
@@ -8711,40 +8711,40 @@
       <c r="H19">
         <v>1.86</v>
       </c>
-      <c r="I19" s="222">
+      <c r="I19" s="230">
         <v>8.03</v>
       </c>
-      <c r="J19" s="226">
+      <c r="J19" s="234">
         <v>14.23</v>
       </c>
       <c r="K19" s="227">
         <v>15.69</v>
       </c>
-      <c r="L19" s="228">
+      <c r="L19" s="224">
         <v>17.52</v>
       </c>
-      <c r="M19" s="234">
+      <c r="M19" s="225">
         <v>14.6</v>
       </c>
-      <c r="N19" s="223">
+      <c r="N19" s="226">
         <v>8.39</v>
       </c>
-      <c r="O19" s="224">
+      <c r="O19" s="222">
         <v>4.74</v>
       </c>
-      <c r="P19" s="229">
+      <c r="P19" s="228">
         <v>1.46</v>
       </c>
-      <c r="Q19" s="230">
+      <c r="Q19" s="231">
         <v>-6.93</v>
       </c>
-      <c r="R19" s="231">
+      <c r="R19" s="229">
         <v>-7.3</v>
       </c>
-      <c r="S19" s="225">
+      <c r="S19" s="232">
         <v>-6.57</v>
       </c>
-      <c r="T19" s="232">
+      <c r="T19" s="223">
         <v>62.41</v>
       </c>
     </row>
@@ -8758,7 +8758,7 @@
       <c r="C20" t="str">
         <v>603778</v>
       </c>
-      <c r="D20" s="240" t="str">
+      <c r="D20" s="244" t="str">
         <v>净卖: -3366.51万</v>
       </c>
       <c r="E20">
@@ -8773,40 +8773,40 @@
       <c r="H20">
         <v>6.69</v>
       </c>
-      <c r="I20" s="246">
+      <c r="I20" s="245">
         <v>3.07</v>
       </c>
-      <c r="J20" s="247">
+      <c r="J20" s="246">
         <v>13.33</v>
       </c>
-      <c r="K20" s="243">
+      <c r="K20" s="237">
         <v>5.33</v>
       </c>
-      <c r="L20" s="235">
+      <c r="L20" s="247">
         <v>8.67</v>
       </c>
-      <c r="M20" s="241">
+      <c r="M20" s="240">
         <v>19.6</v>
       </c>
-      <c r="N20" s="237">
+      <c r="N20" s="238">
         <v>7.6</v>
       </c>
-      <c r="O20" s="244">
+      <c r="O20" s="236">
         <v>-2</v>
       </c>
-      <c r="P20" s="236">
+      <c r="P20" s="241">
         <v>7.87</v>
       </c>
-      <c r="Q20" s="238">
+      <c r="Q20" s="242">
         <v>18.67</v>
       </c>
-      <c r="R20" s="239">
+      <c r="R20" s="235">
         <v>27.73</v>
       </c>
-      <c r="S20" s="242">
+      <c r="S20" s="243">
         <v>40.53</v>
       </c>
-      <c r="T20" s="245">
+      <c r="T20" s="239">
         <v>223.33</v>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       <c r="C21" t="str">
         <v>600252</v>
       </c>
-      <c r="D21" s="250" t="str">
+      <c r="D21" s="258" t="str">
         <v>净卖: -331.54万</v>
       </c>
       <c r="E21">
@@ -8835,40 +8835,40 @@
       <c r="H21">
         <v>0.37</v>
       </c>
-      <c r="I21" s="248">
+      <c r="I21" s="259">
         <v>9.67</v>
       </c>
-      <c r="J21" s="256">
+      <c r="J21" s="249">
         <v>6.32</v>
       </c>
-      <c r="K21" s="257">
+      <c r="K21" s="260">
         <v>7.81</v>
       </c>
-      <c r="L21" s="258">
+      <c r="L21" s="250">
         <v>10.41</v>
       </c>
       <c r="M21" s="253">
         <v>9.29</v>
       </c>
-      <c r="N21" s="251">
+      <c r="N21" s="254">
         <v>11.9</v>
       </c>
-      <c r="O21" s="252">
+      <c r="O21" s="255">
         <v>10.78</v>
       </c>
-      <c r="P21" s="259">
+      <c r="P21" s="251">
         <v>11.52</v>
       </c>
-      <c r="Q21" s="249">
+      <c r="Q21" s="256">
         <v>10.04</v>
       </c>
-      <c r="R21" s="254">
+      <c r="R21" s="257">
         <v>6.32</v>
       </c>
-      <c r="S21" s="260">
+      <c r="S21" s="248">
         <v>5.58</v>
       </c>
-      <c r="T21" s="255">
+      <c r="T21" s="252">
         <v>-6.69</v>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       <c r="C22" t="str">
         <v>003018</v>
       </c>
-      <c r="D22" s="262" t="str">
+      <c r="D22" s="261" t="str">
         <v>净卖: -1172.31万</v>
       </c>
       <c r="E22">
@@ -8897,40 +8897,40 @@
       <c r="H22">
         <v>10.01</v>
       </c>
-      <c r="I22" s="273">
+      <c r="I22" s="270">
         <v>0</v>
       </c>
-      <c r="J22" s="269">
+      <c r="J22" s="271">
         <v>-9.99</v>
       </c>
-      <c r="K22" s="261">
+      <c r="K22" s="272">
         <v>-18.85</v>
       </c>
-      <c r="L22" s="263">
+      <c r="L22" s="266">
         <v>-18.77</v>
       </c>
-      <c r="M22" s="264">
+      <c r="M22" s="262">
         <v>-15.14</v>
       </c>
-      <c r="N22" s="267">
+      <c r="N22" s="263">
         <v>-23.48</v>
       </c>
-      <c r="O22" s="270">
+      <c r="O22" s="267">
         <v>-18.81</v>
       </c>
-      <c r="P22" s="265">
+      <c r="P22" s="268">
         <v>-22.71</v>
       </c>
-      <c r="Q22" s="271">
+      <c r="Q22" s="269">
         <v>-25.49</v>
       </c>
-      <c r="R22" s="266">
+      <c r="R22" s="264">
         <v>-25.49</v>
       </c>
-      <c r="S22" s="268">
+      <c r="S22" s="265">
         <v>-29.4</v>
       </c>
-      <c r="T22" s="272">
+      <c r="T22" s="273">
         <v>57.95</v>
       </c>
     </row>
@@ -8944,7 +8944,7 @@
       <c r="C23" t="str">
         <v>603958</v>
       </c>
-      <c r="D23" s="274" t="str">
+      <c r="D23" s="280" t="str">
         <v>净买: 48.48万</v>
       </c>
       <c r="E23">
@@ -8959,13 +8959,13 @@
       <c r="H23">
         <v>-5.98</v>
       </c>
-      <c r="I23" s="278">
+      <c r="I23" s="282">
         <v>-4.29</v>
       </c>
-      <c r="J23" s="279">
+      <c r="J23" s="281">
         <v>-7.64</v>
       </c>
-      <c r="K23" s="276">
+      <c r="K23" s="274">
         <v>-8.21</v>
       </c>
       <c r="L23" s="283">
@@ -8977,22 +8977,22 @@
       <c r="N23" s="275">
         <v>-8.36</v>
       </c>
-      <c r="O23" s="280">
+      <c r="O23" s="276">
         <v>-10.57</v>
       </c>
-      <c r="P23" s="285">
+      <c r="P23" s="277">
         <v>-8.86</v>
       </c>
-      <c r="Q23" s="277">
+      <c r="Q23" s="278">
         <v>-7.43</v>
       </c>
-      <c r="R23" s="286">
+      <c r="R23" s="285">
         <v>-8</v>
       </c>
-      <c r="S23" s="281">
+      <c r="S23" s="279">
         <v>-8.71</v>
       </c>
-      <c r="T23" s="282">
+      <c r="T23" s="286">
         <v>81.64</v>
       </c>
     </row>
@@ -9006,7 +9006,7 @@
       <c r="C24" t="str">
         <v>002187</v>
       </c>
-      <c r="D24" s="299" t="str">
+      <c r="D24" s="294" t="str">
         <v>净卖: -1062.98万</v>
       </c>
       <c r="E24">
@@ -9021,40 +9021,40 @@
       <c r="H24">
         <v>2</v>
       </c>
-      <c r="I24" s="295">
+      <c r="I24" s="297">
         <v>7.83</v>
       </c>
-      <c r="J24" s="287">
+      <c r="J24" s="291">
         <v>3.92</v>
       </c>
       <c r="K24" s="292">
         <v>3.26</v>
       </c>
-      <c r="L24" s="296">
+      <c r="L24" s="298">
         <v>7.57</v>
       </c>
-      <c r="M24" s="298">
+      <c r="M24" s="299">
         <v>10.05</v>
       </c>
-      <c r="N24" s="288">
+      <c r="N24" s="295">
         <v>8.88</v>
       </c>
-      <c r="O24" s="289">
+      <c r="O24" s="287">
         <v>4.96</v>
       </c>
-      <c r="P24" s="290">
+      <c r="P24" s="288">
         <v>7.83</v>
       </c>
-      <c r="Q24" s="291">
+      <c r="Q24" s="296">
         <v>6.4</v>
       </c>
-      <c r="R24" s="297">
+      <c r="R24" s="289">
         <v>17.1</v>
       </c>
       <c r="S24" s="293">
         <v>5.61</v>
       </c>
-      <c r="T24" s="294">
+      <c r="T24" s="290">
         <v>-18.54</v>
       </c>
     </row>
@@ -9068,7 +9068,7 @@
       <c r="C25" t="str">
         <v>688273</v>
       </c>
-      <c r="D25" s="306" t="str">
+      <c r="D25" s="300" t="str">
         <v>净卖: -963.67万</v>
       </c>
       <c r="E25">
@@ -9083,40 +9083,40 @@
       <c r="H25">
         <v>-1.99</v>
       </c>
-      <c r="I25" s="303">
+      <c r="I25" s="311">
         <v>-8.57</v>
       </c>
-      <c r="J25" s="307">
+      <c r="J25" s="303">
         <v>-8.03</v>
       </c>
-      <c r="K25" s="311">
+      <c r="K25" s="306">
         <v>-11.27</v>
       </c>
-      <c r="L25" s="300">
+      <c r="L25" s="312">
         <v>-8.63</v>
       </c>
-      <c r="M25" s="301">
+      <c r="M25" s="304">
         <v>-13</v>
       </c>
-      <c r="N25" s="302">
+      <c r="N25" s="305">
         <v>-13.83</v>
       </c>
-      <c r="O25" s="308">
+      <c r="O25" s="301">
         <v>-17.22</v>
       </c>
-      <c r="P25" s="309">
+      <c r="P25" s="307">
         <v>-20.37</v>
       </c>
-      <c r="Q25" s="312">
+      <c r="Q25" s="308">
         <v>-20.43</v>
       </c>
-      <c r="R25" s="310">
+      <c r="R25" s="309">
         <v>-22.83</v>
       </c>
-      <c r="S25" s="304">
+      <c r="S25" s="302">
         <v>-23.42</v>
       </c>
-      <c r="T25" s="305">
+      <c r="T25" s="310">
         <v>-18.5</v>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       <c r="C26" t="str">
         <v>688523</v>
       </c>
-      <c r="D26" s="321" t="str">
+      <c r="D26" s="324" t="str">
         <v>净卖: -2032.96万</v>
       </c>
       <c r="E26">
@@ -9145,19 +9145,19 @@
       <c r="H26">
         <v>-6.9</v>
       </c>
-      <c r="I26" s="322">
+      <c r="I26" s="320">
         <v>-12.28</v>
       </c>
-      <c r="J26" s="314">
+      <c r="J26" s="315">
         <v>-15.94</v>
       </c>
-      <c r="K26" s="323">
+      <c r="K26" s="316">
         <v>-22.53</v>
       </c>
-      <c r="L26" s="317">
+      <c r="L26" s="322">
         <v>-23.98</v>
       </c>
-      <c r="M26" s="324">
+      <c r="M26" s="323">
         <v>-21.69</v>
       </c>
       <c r="N26" s="325">
@@ -9166,19 +9166,19 @@
       <c r="O26" s="313">
         <v>-29.76</v>
       </c>
-      <c r="P26" s="315">
+      <c r="P26" s="321">
         <v>-23.74</v>
       </c>
-      <c r="Q26" s="319">
+      <c r="Q26" s="314">
         <v>-13.62</v>
       </c>
-      <c r="R26" s="320">
+      <c r="R26" s="317">
         <v>-23.24</v>
       </c>
       <c r="S26" s="318">
         <v>-24.4</v>
       </c>
-      <c r="T26" s="316">
+      <c r="T26" s="319">
         <v>-17.28</v>
       </c>
     </row>
@@ -9192,7 +9192,7 @@
       <c r="C27" t="str">
         <v>002131</v>
       </c>
-      <c r="D27" s="336" t="str">
+      <c r="D27" s="327" t="str">
         <v>净买: 384.51万</v>
       </c>
       <c r="E27">
@@ -9210,37 +9210,37 @@
       <c r="I27" s="328">
         <v>0</v>
       </c>
-      <c r="J27" s="332">
+      <c r="J27" s="333">
         <v>-10.04</v>
       </c>
-      <c r="K27" s="337">
+      <c r="K27" s="330">
         <v>-10.26</v>
       </c>
-      <c r="L27" s="338">
+      <c r="L27" s="334">
         <v>-14.53</v>
       </c>
       <c r="M27" s="329">
         <v>-9.19</v>
       </c>
-      <c r="N27" s="330">
+      <c r="N27" s="335">
         <v>-6.3</v>
       </c>
-      <c r="O27" s="333">
+      <c r="O27" s="331">
         <v>2.24</v>
       </c>
-      <c r="P27" s="326">
+      <c r="P27" s="332">
         <v>-0.43</v>
       </c>
-      <c r="Q27" s="334">
+      <c r="Q27" s="336">
         <v>5.88</v>
       </c>
-      <c r="R27" s="335">
+      <c r="R27" s="326">
         <v>8.76</v>
       </c>
-      <c r="S27" s="331">
+      <c r="S27" s="337">
         <v>-1.07</v>
       </c>
-      <c r="T27" s="327">
+      <c r="T27" s="338">
         <v>-14.96</v>
       </c>
     </row>
@@ -9254,7 +9254,7 @@
       <c r="C28" t="str">
         <v>603698</v>
       </c>
-      <c r="D28" s="339" t="str">
+      <c r="D28" s="344" t="str">
         <v>净卖: -1965.64万</v>
       </c>
       <c r="E28">
@@ -9269,37 +9269,37 @@
       <c r="H28">
         <v>-1.78</v>
       </c>
-      <c r="I28" s="348">
+      <c r="I28" s="345">
         <v>-8.38</v>
       </c>
-      <c r="J28" s="340">
+      <c r="J28" s="339">
         <v>-9.03</v>
       </c>
-      <c r="K28" s="341">
+      <c r="K28" s="349">
         <v>-9.19</v>
       </c>
-      <c r="L28" s="342">
+      <c r="L28" s="346">
         <v>-8.54</v>
       </c>
-      <c r="M28" s="349">
+      <c r="M28" s="350">
         <v>-7.3</v>
       </c>
-      <c r="N28" s="343">
+      <c r="N28" s="340">
         <v>-6.49</v>
       </c>
-      <c r="O28" s="346">
+      <c r="O28" s="342">
         <v>0.59</v>
       </c>
-      <c r="P28" s="344">
+      <c r="P28" s="343">
         <v>2.27</v>
       </c>
-      <c r="Q28" s="350">
+      <c r="Q28" s="347">
         <v>2.54</v>
       </c>
-      <c r="R28" s="345">
+      <c r="R28" s="341">
         <v>4.92</v>
       </c>
-      <c r="S28" s="347">
+      <c r="S28" s="348">
         <v>10.54</v>
       </c>
       <c r="T28" s="351">
@@ -9316,7 +9316,7 @@
       <c r="C29" t="str">
         <v>603619</v>
       </c>
-      <c r="D29" s="353" t="str">
+      <c r="D29" s="359" t="str">
         <v>净买: 3411.20万</v>
       </c>
       <c r="E29">
@@ -9331,40 +9331,40 @@
       <c r="H29">
         <v>1.96</v>
       </c>
-      <c r="I29" s="364">
+      <c r="I29" s="361">
         <v>-8.71</v>
       </c>
       <c r="J29" s="354">
         <v>-17.84</v>
       </c>
-      <c r="K29" s="360">
+      <c r="K29" s="355">
         <v>-20.82</v>
       </c>
-      <c r="L29" s="361">
+      <c r="L29" s="360">
         <v>-14.71</v>
       </c>
-      <c r="M29" s="362">
+      <c r="M29" s="356">
         <v>-18.76</v>
       </c>
-      <c r="N29" s="358">
+      <c r="N29" s="362">
         <v>-14.24</v>
       </c>
       <c r="O29" s="363">
         <v>-16.47</v>
       </c>
-      <c r="P29" s="352">
+      <c r="P29" s="357">
         <v>-12.61</v>
       </c>
-      <c r="Q29" s="355">
+      <c r="Q29" s="364">
         <v>-7.45</v>
       </c>
-      <c r="R29" s="356">
+      <c r="R29" s="358">
         <v>-9.16</v>
       </c>
-      <c r="S29" s="359">
+      <c r="S29" s="352">
         <v>-12.42</v>
       </c>
-      <c r="T29" s="357">
+      <c r="T29" s="353">
         <v>-11.71</v>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       <c r="C30" t="str">
         <v>688530</v>
       </c>
-      <c r="D30" s="366" t="str">
+      <c r="D30" s="370" t="str">
         <v>净卖: -1311.39万</v>
       </c>
       <c r="E30">
@@ -9393,40 +9393,40 @@
       <c r="H30">
         <v>-2.23</v>
       </c>
-      <c r="I30" s="373">
+      <c r="I30" s="371">
         <v>15.5</v>
       </c>
-      <c r="J30" s="367">
+      <c r="J30" s="375">
         <v>11.55</v>
       </c>
-      <c r="K30" s="368">
+      <c r="K30" s="376">
         <v>20.14</v>
       </c>
-      <c r="L30" s="369">
+      <c r="L30" s="365">
         <v>15.82</v>
       </c>
-      <c r="M30" s="374">
+      <c r="M30" s="366">
         <v>32.04</v>
       </c>
-      <c r="N30" s="370">
+      <c r="N30" s="367">
         <v>29.72</v>
       </c>
-      <c r="O30" s="375">
+      <c r="O30" s="368">
         <v>28.01</v>
       </c>
-      <c r="P30" s="371">
+      <c r="P30" s="369">
         <v>31.8</v>
       </c>
-      <c r="Q30" s="376">
+      <c r="Q30" s="377">
         <v>58.17</v>
       </c>
-      <c r="R30" s="377">
+      <c r="R30" s="372">
         <v>66.44</v>
       </c>
-      <c r="S30" s="372">
+      <c r="S30" s="373">
         <v>58.53</v>
       </c>
-      <c r="T30" s="365">
+      <c r="T30" s="374">
         <v>42.83</v>
       </c>
     </row>
@@ -9440,7 +9440,7 @@
       <c r="C31" t="str">
         <v>688530</v>
       </c>
-      <c r="D31" s="383" t="str">
+      <c r="D31" s="389" t="str">
         <v>净卖: -4653.87万</v>
       </c>
       <c r="E31">
@@ -9458,37 +9458,37 @@
       <c r="I31" s="384">
         <v>21.29</v>
       </c>
-      <c r="J31" s="378">
+      <c r="J31" s="380">
         <v>27.63</v>
       </c>
-      <c r="K31" s="381">
+      <c r="K31" s="390">
         <v>21.57</v>
       </c>
-      <c r="L31" s="386">
+      <c r="L31" s="381">
         <v>13.14</v>
       </c>
-      <c r="M31" s="387">
+      <c r="M31" s="378">
         <v>8.21</v>
       </c>
-      <c r="N31" s="388">
+      <c r="N31" s="379">
         <v>6.59</v>
       </c>
-      <c r="O31" s="379">
+      <c r="O31" s="385">
         <v>1.78</v>
       </c>
-      <c r="P31" s="389">
+      <c r="P31" s="386">
         <v>0.09</v>
       </c>
-      <c r="Q31" s="390">
+      <c r="Q31" s="387">
         <v>6.43</v>
       </c>
-      <c r="R31" s="385">
+      <c r="R31" s="382">
         <v>1.5</v>
       </c>
-      <c r="S31" s="380">
+      <c r="S31" s="388">
         <v>5.55</v>
       </c>
-      <c r="T31" s="382">
+      <c r="T31" s="383">
         <v>9.53</v>
       </c>
     </row>
@@ -9502,7 +9502,7 @@
       <c r="C32" t="str">
         <v>600367</v>
       </c>
-      <c r="D32" s="394" t="str">
+      <c r="D32" s="396" t="str">
         <v>净买: 7875.30万</v>
       </c>
       <c r="E32">
@@ -9517,7 +9517,7 @@
       <c r="H32">
         <v>6.88</v>
       </c>
-      <c r="I32" s="395">
+      <c r="I32" s="398">
         <v>2.94</v>
       </c>
       <c r="J32" s="399">
@@ -9526,31 +9526,31 @@
       <c r="K32" s="400">
         <v>-2.86</v>
       </c>
-      <c r="L32" s="392">
+      <c r="L32" s="401">
         <v>-5.36</v>
       </c>
-      <c r="M32" s="396">
+      <c r="M32" s="392">
         <v>-7.83</v>
       </c>
-      <c r="N32" s="393">
+      <c r="N32" s="402">
         <v>-11.24</v>
       </c>
-      <c r="O32" s="401">
+      <c r="O32" s="393">
         <v>-9.85</v>
       </c>
-      <c r="P32" s="402">
+      <c r="P32" s="403">
         <v>-6.2</v>
       </c>
-      <c r="Q32" s="403">
+      <c r="Q32" s="394">
         <v>-1.47</v>
       </c>
       <c r="R32" s="397">
         <v>6.52</v>
       </c>
-      <c r="S32" s="391">
+      <c r="S32" s="395">
         <v>13.79</v>
       </c>
-      <c r="T32" s="398">
+      <c r="T32" s="391">
         <v>-15.14</v>
       </c>
     </row>
@@ -9579,40 +9579,40 @@
       <c r="H33">
         <v>0.8</v>
       </c>
-      <c r="I33" s="416">
+      <c r="I33" s="407">
         <v>9.21</v>
       </c>
-      <c r="J33" s="408">
+      <c r="J33" s="416">
         <v>6.83</v>
       </c>
-      <c r="K33" s="409">
+      <c r="K33" s="410">
         <v>5.87</v>
       </c>
-      <c r="L33" s="410">
+      <c r="L33" s="404">
         <v>7.46</v>
       </c>
-      <c r="M33" s="411">
+      <c r="M33" s="408">
         <v>10.32</v>
       </c>
-      <c r="N33" s="414">
+      <c r="N33" s="413">
         <v>12.86</v>
       </c>
       <c r="O33" s="405">
         <v>7.3</v>
       </c>
-      <c r="P33" s="406">
+      <c r="P33" s="411">
         <v>4.92</v>
       </c>
-      <c r="Q33" s="404">
+      <c r="Q33" s="414">
         <v>1.11</v>
       </c>
-      <c r="R33" s="407">
+      <c r="R33" s="412">
         <v>-1.59</v>
       </c>
-      <c r="S33" s="412">
+      <c r="S33" s="409">
         <v>-5.24</v>
       </c>
-      <c r="T33" s="413">
+      <c r="T33" s="406">
         <v>-11.27</v>
       </c>
     </row>
@@ -9626,7 +9626,7 @@
       <c r="C34" t="str">
         <v>300131</v>
       </c>
-      <c r="D34" s="423" t="str">
+      <c r="D34" s="422" t="str">
         <v>净卖: -9057.02万</v>
       </c>
       <c r="E34">
@@ -9641,40 +9641,40 @@
       <c r="H34">
         <v>2.57</v>
       </c>
-      <c r="I34" s="428">
+      <c r="I34" s="418">
         <v>-18.81</v>
       </c>
-      <c r="J34" s="429">
+      <c r="J34" s="427">
         <v>-16.59</v>
       </c>
-      <c r="K34" s="424">
+      <c r="K34" s="423">
         <v>-10.32</v>
       </c>
-      <c r="L34" s="420">
+      <c r="L34" s="424">
         <v>-11.8</v>
       </c>
-      <c r="M34" s="421">
+      <c r="M34" s="419">
         <v>-16.08</v>
       </c>
-      <c r="N34" s="417">
+      <c r="N34" s="428">
         <v>-14.6</v>
       </c>
-      <c r="O34" s="425">
+      <c r="O34" s="420">
         <v>-17.4</v>
       </c>
-      <c r="P34" s="418">
+      <c r="P34" s="421">
         <v>-16.22</v>
       </c>
-      <c r="Q34" s="419">
+      <c r="Q34" s="425">
         <v>-16.74</v>
       </c>
-      <c r="R34" s="422">
+      <c r="R34" s="426">
         <v>-9.44</v>
       </c>
-      <c r="S34" s="426">
+      <c r="S34" s="429">
         <v>-5.24</v>
       </c>
-      <c r="T34" s="427">
+      <c r="T34" s="417">
         <v>15.86</v>
       </c>
     </row>
@@ -9737,40 +9737,40 @@
       <c r="F36" t="str"/>
       <c r="G36" t="str"/>
       <c r="H36" t="str"/>
-      <c r="I36" s="437">
+      <c r="I36" s="436">
         <v>54.55</v>
       </c>
-      <c r="J36" s="432">
+      <c r="J36" s="439">
         <v>57.58</v>
       </c>
-      <c r="K36" s="441">
+      <c r="K36" s="437">
         <v>51.52</v>
       </c>
-      <c r="L36" s="433">
+      <c r="L36" s="430">
         <v>54.55</v>
       </c>
-      <c r="M36" s="438">
+      <c r="M36" s="433">
         <v>60.61</v>
       </c>
-      <c r="N36" s="430">
+      <c r="N36" s="440">
         <v>57.58</v>
       </c>
-      <c r="O36" s="436">
+      <c r="O36" s="434">
         <v>54.55</v>
       </c>
-      <c r="P36" s="439">
+      <c r="P36" s="435">
         <v>54.55</v>
       </c>
-      <c r="Q36" s="434">
+      <c r="Q36" s="431">
         <v>51.52</v>
       </c>
-      <c r="R36" s="431">
+      <c r="R36" s="438">
         <v>45.45</v>
       </c>
-      <c r="S36" s="435">
+      <c r="S36" s="432">
         <v>45.45</v>
       </c>
-      <c r="T36" s="440">
+      <c r="T36" s="441">
         <v>45.45</v>
       </c>
     </row>
@@ -9785,40 +9785,40 @@
       <c r="F37" t="str"/>
       <c r="G37" t="str"/>
       <c r="H37" t="str"/>
-      <c r="I37" s="443">
+      <c r="I37" s="449">
         <v>2.72</v>
       </c>
-      <c r="J37" s="444">
+      <c r="J37" s="450">
         <v>3.68</v>
       </c>
-      <c r="K37" s="451">
+      <c r="K37" s="452">
         <v>3.17</v>
       </c>
-      <c r="L37" s="452">
+      <c r="L37" s="442">
         <v>4.28</v>
       </c>
-      <c r="M37" s="447">
+      <c r="M37" s="444">
         <v>4.38</v>
       </c>
-      <c r="N37" s="453">
+      <c r="N37" s="445">
         <v>2.62</v>
       </c>
-      <c r="O37" s="448">
+      <c r="O37" s="446">
         <v>1.54</v>
       </c>
-      <c r="P37" s="445">
+      <c r="P37" s="443">
         <v>1.8</v>
       </c>
-      <c r="Q37" s="449">
+      <c r="Q37" s="453">
         <v>2.18</v>
       </c>
-      <c r="R37" s="442">
+      <c r="R37" s="447">
         <v>1.38</v>
       </c>
-      <c r="S37" s="450">
+      <c r="S37" s="448">
         <v>1.44</v>
       </c>
-      <c r="T37" s="446">
+      <c r="T37" s="451">
         <v>21.14</v>
       </c>
     </row>

--- a/youzi/新生代/index.xlsx
+++ b/youzi/新生代/index.xlsx
@@ -39,85 +39,2365 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF29A746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF24993F"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8B94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D0D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D0D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF8F0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF79C88B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1E2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35D6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1ECD7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF35AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAADCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3FB059"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C1C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8993"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF22903C"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF29A746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3606D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3646"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA4AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0ECD7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD63242"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFAB1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,18 +2409,132 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8891"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE3C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -153,6 +2547,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -165,12 +2571,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -201,385 +2601,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8B94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D0D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D0D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
+        <fgColor rgb="FFF9E0E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD6AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD6AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46572"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD6AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46572"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -597,121 +2709,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF8F0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4636F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -723,457 +2733,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF79C88B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1E2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAADCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF35AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1ECD7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C1C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3FB059"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
+        <fgColor rgb="FFDF4957"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1185,1573 +2745,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8993"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3646"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3606D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0ECD7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8891"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBAE3C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46572"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46572"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4636F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE56D79"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -7642,7 +7642,7 @@
       <c r="C2" t="str">
         <v>002238</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="9" t="str">
         <v>净卖: -808.36万</v>
       </c>
       <c r="E2">
@@ -7657,40 +7657,40 @@
       <c r="H2">
         <v>4.28</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="3">
         <v>5.53</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="5">
         <v>-4.96</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="10">
         <v>-1.72</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="13">
         <v>-6.11</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="1">
         <v>-6.87</v>
       </c>
-      <c r="N2" s="8">
+      <c r="N2" s="6">
         <v>-8.3</v>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="7">
         <v>-8.78</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="4">
         <v>-12.21</v>
       </c>
-      <c r="Q2" s="9">
+      <c r="Q2" s="2">
         <v>-13.17</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R2" s="8">
         <v>-14.03</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="11">
         <v>-13.84</v>
       </c>
-      <c r="T2" s="5">
+      <c r="T2" s="12">
         <v>-30.15</v>
       </c>
     </row>
@@ -7704,7 +7704,7 @@
       <c r="C3" t="str">
         <v>002238</v>
       </c>
-      <c r="D3" s="17" t="str">
+      <c r="D3" s="22" t="str">
         <v>净卖: -1634.66万</v>
       </c>
       <c r="E3">
@@ -7719,40 +7719,40 @@
       <c r="H3">
         <v>-0.54</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="17">
         <v>-9.45</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="23">
         <v>-6.36</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="25">
         <v>-10.55</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="24">
         <v>-11.27</v>
       </c>
-      <c r="M3" s="25">
+      <c r="M3" s="26">
         <v>-12.64</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="18">
         <v>-13.09</v>
       </c>
-      <c r="O3" s="26">
+      <c r="O3" s="19">
         <v>-16.36</v>
       </c>
-      <c r="P3" s="15">
+      <c r="P3" s="14">
         <v>-17.27</v>
       </c>
       <c r="Q3" s="20">
         <v>-18.09</v>
       </c>
-      <c r="R3" s="16">
+      <c r="R3" s="15">
         <v>-17.91</v>
       </c>
       <c r="S3" s="21">
         <v>-17.55</v>
       </c>
-      <c r="T3" s="24">
+      <c r="T3" s="16">
         <v>-33.45</v>
       </c>
     </row>
@@ -7781,40 +7781,40 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="27">
         <v>10.08</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="35">
         <v>21.19</v>
       </c>
-      <c r="K4" s="29">
+      <c r="K4" s="28">
         <v>33.33</v>
       </c>
-      <c r="L4" s="33">
+      <c r="L4" s="36">
         <v>46.77</v>
       </c>
-      <c r="M4" s="34">
+      <c r="M4" s="31">
         <v>61.5</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="37">
         <v>45.48</v>
       </c>
-      <c r="O4" s="39">
+      <c r="O4" s="38">
         <v>53.23</v>
       </c>
-      <c r="P4" s="36">
+      <c r="P4" s="34">
         <v>58.66</v>
       </c>
-      <c r="Q4" s="27">
+      <c r="Q4" s="39">
         <v>51.94</v>
       </c>
-      <c r="R4" s="28">
+      <c r="R4" s="32">
         <v>36.69</v>
       </c>
-      <c r="S4" s="37">
+      <c r="S4" s="29">
         <v>23</v>
       </c>
-      <c r="T4" s="38">
+      <c r="T4" s="33">
         <v>22.74</v>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       <c r="C5" t="str">
         <v>002041</v>
       </c>
-      <c r="D5" s="40" t="str">
+      <c r="D5" s="52" t="str">
         <v>净卖: -388.51万</v>
       </c>
       <c r="E5">
@@ -7843,40 +7843,40 @@
       <c r="H5">
         <v>4.75</v>
       </c>
-      <c r="I5" s="49">
+      <c r="I5" s="48">
         <v>4.91</v>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="40">
         <v>15.37</v>
       </c>
-      <c r="K5" s="42">
+      <c r="K5" s="41">
         <v>10.56</v>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="46">
         <v>11.76</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="42">
         <v>4.07</v>
       </c>
-      <c r="N5" s="45">
+      <c r="N5" s="49">
         <v>5.09</v>
       </c>
-      <c r="O5" s="46">
+      <c r="O5" s="43">
         <v>2.87</v>
       </c>
-      <c r="P5" s="51">
+      <c r="P5" s="50">
         <v>0.56</v>
       </c>
       <c r="Q5" s="47">
         <v>0.19</v>
       </c>
-      <c r="R5" s="48">
+      <c r="R5" s="44">
         <v>-3.15</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="51">
         <v>-2.31</v>
       </c>
-      <c r="T5" s="52">
+      <c r="T5" s="45">
         <v>-4.35</v>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       <c r="C6" t="str">
         <v>001368</v>
       </c>
-      <c r="D6" s="59" t="str">
+      <c r="D6" s="60" t="str">
         <v>净卖: -491.53万</v>
       </c>
       <c r="E6">
@@ -7908,37 +7908,37 @@
       <c r="I6" s="61">
         <v>0</v>
       </c>
-      <c r="J6" s="55">
+      <c r="J6" s="62">
         <v>-9.94</v>
       </c>
-      <c r="K6" s="62">
+      <c r="K6" s="63">
         <v>-12.52</v>
       </c>
-      <c r="L6" s="63">
+      <c r="L6" s="55">
         <v>-3.79</v>
       </c>
-      <c r="M6" s="56">
+      <c r="M6" s="64">
         <v>-1.89</v>
       </c>
-      <c r="N6" s="64">
+      <c r="N6" s="57">
         <v>-5.64</v>
       </c>
-      <c r="O6" s="65">
+      <c r="O6" s="58">
         <v>-7.27</v>
       </c>
-      <c r="P6" s="53">
+      <c r="P6" s="65">
         <v>-8.13</v>
       </c>
-      <c r="Q6" s="60">
+      <c r="Q6" s="53">
         <v>-8.91</v>
       </c>
-      <c r="R6" s="57">
+      <c r="R6" s="54">
         <v>-8.61</v>
       </c>
-      <c r="S6" s="54">
+      <c r="S6" s="56">
         <v>-5.85</v>
       </c>
-      <c r="T6" s="58">
+      <c r="T6" s="59">
         <v>20.4</v>
       </c>
     </row>
@@ -7952,7 +7952,7 @@
       <c r="C7" t="str">
         <v>603516</v>
       </c>
-      <c r="D7" s="66" t="str">
+      <c r="D7" s="71" t="str">
         <v>净买: 374.25万</v>
       </c>
       <c r="E7">
@@ -7970,37 +7970,37 @@
       <c r="I7" s="75">
         <v>0</v>
       </c>
-      <c r="J7" s="71">
+      <c r="J7" s="76">
         <v>4.02</v>
       </c>
-      <c r="K7" s="67">
+      <c r="K7" s="77">
         <v>2.06</v>
       </c>
       <c r="L7" s="68">
         <v>3.75</v>
       </c>
-      <c r="M7" s="73">
+      <c r="M7" s="70">
         <v>7.52</v>
       </c>
-      <c r="N7" s="76">
+      <c r="N7" s="78">
         <v>6.86</v>
       </c>
-      <c r="O7" s="77">
+      <c r="O7" s="69">
         <v>11.67</v>
       </c>
-      <c r="P7" s="74">
+      <c r="P7" s="66">
         <v>9.4</v>
       </c>
       <c r="Q7" s="72">
         <v>11.63</v>
       </c>
-      <c r="R7" s="69">
+      <c r="R7" s="67">
         <v>11.12</v>
       </c>
-      <c r="S7" s="70">
+      <c r="S7" s="73">
         <v>9.79</v>
       </c>
-      <c r="T7" s="78">
+      <c r="T7" s="74">
         <v>345.15</v>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       <c r="C8" t="str">
         <v>002510</v>
       </c>
-      <c r="D8" s="79" t="str">
+      <c r="D8" s="85" t="str">
         <v>净卖: -764.76万</v>
       </c>
       <c r="E8">
@@ -8029,40 +8029,40 @@
       <c r="H8">
         <v>10.06</v>
       </c>
-      <c r="I8" s="80">
+      <c r="I8" s="91">
         <v>0</v>
       </c>
-      <c r="J8" s="89">
+      <c r="J8" s="86">
         <v>10</v>
       </c>
-      <c r="K8" s="90">
+      <c r="K8" s="87">
         <v>21</v>
       </c>
-      <c r="L8" s="84">
+      <c r="L8" s="79">
         <v>17.57</v>
       </c>
-      <c r="M8" s="91">
+      <c r="M8" s="90">
         <v>5.86</v>
       </c>
-      <c r="N8" s="81">
+      <c r="N8" s="80">
         <v>1.57</v>
       </c>
-      <c r="O8" s="85">
+      <c r="O8" s="82">
         <v>3.57</v>
       </c>
-      <c r="P8" s="87">
+      <c r="P8" s="83">
         <v>1.14</v>
       </c>
-      <c r="Q8" s="86">
+      <c r="Q8" s="88">
         <v>1.14</v>
       </c>
-      <c r="R8" s="82">
+      <c r="R8" s="89">
         <v>-4.57</v>
       </c>
-      <c r="S8" s="83">
+      <c r="S8" s="81">
         <v>-2.71</v>
       </c>
-      <c r="T8" s="88">
+      <c r="T8" s="84">
         <v>1.29</v>
       </c>
     </row>
@@ -8076,7 +8076,7 @@
       <c r="C9" t="str">
         <v>600367</v>
       </c>
-      <c r="D9" s="102" t="str">
+      <c r="D9" s="101" t="str">
         <v>净买: 3583.76万</v>
       </c>
       <c r="E9">
@@ -8091,31 +8091,31 @@
       <c r="H9">
         <v>4.52</v>
       </c>
-      <c r="I9" s="96">
+      <c r="I9" s="94">
         <v>-0.98</v>
       </c>
-      <c r="J9" s="103">
+      <c r="J9" s="102">
         <v>-4.07</v>
       </c>
-      <c r="K9" s="97">
+      <c r="K9" s="98">
         <v>-0.39</v>
       </c>
-      <c r="L9" s="93">
+      <c r="L9" s="103">
         <v>5.44</v>
       </c>
-      <c r="M9" s="94">
+      <c r="M9" s="104">
         <v>5.18</v>
       </c>
       <c r="N9" s="92">
         <v>12.52</v>
       </c>
-      <c r="O9" s="98">
+      <c r="O9" s="95">
         <v>1.25</v>
       </c>
-      <c r="P9" s="104">
+      <c r="P9" s="96">
         <v>11.34</v>
       </c>
-      <c r="Q9" s="95">
+      <c r="Q9" s="97">
         <v>4.07</v>
       </c>
       <c r="R9" s="99">
@@ -8124,7 +8124,7 @@
       <c r="S9" s="100">
         <v>2.89</v>
       </c>
-      <c r="T9" s="101">
+      <c r="T9" s="93">
         <v>40.07</v>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       <c r="C10" t="str">
         <v>603585</v>
       </c>
-      <c r="D10" s="115" t="str">
+      <c r="D10" s="113" t="str">
         <v>净买: 620.83万</v>
       </c>
       <c r="E10">
@@ -8153,40 +8153,40 @@
       <c r="H10">
         <v>-7.49</v>
       </c>
-      <c r="I10" s="110">
+      <c r="I10" s="109">
         <v>-2.7</v>
       </c>
-      <c r="J10" s="107">
+      <c r="J10" s="114">
         <v>-7</v>
       </c>
-      <c r="K10" s="116">
+      <c r="K10" s="115">
         <v>-4.8</v>
       </c>
-      <c r="L10" s="108">
+      <c r="L10" s="116">
         <v>-5.45</v>
       </c>
-      <c r="M10" s="111">
+      <c r="M10" s="117">
         <v>-7.65</v>
       </c>
-      <c r="N10" s="112">
+      <c r="N10" s="105">
         <v>-8.8</v>
       </c>
-      <c r="O10" s="105">
+      <c r="O10" s="110">
         <v>-8.55</v>
       </c>
-      <c r="P10" s="113">
+      <c r="P10" s="106">
         <v>-7.55</v>
       </c>
-      <c r="Q10" s="106">
+      <c r="Q10" s="107">
         <v>-1.95</v>
       </c>
-      <c r="R10" s="117">
+      <c r="R10" s="108">
         <v>-3.1</v>
       </c>
-      <c r="S10" s="114">
+      <c r="S10" s="111">
         <v>6.6</v>
       </c>
-      <c r="T10" s="109">
+      <c r="T10" s="112">
         <v>20.3</v>
       </c>
     </row>
@@ -8200,7 +8200,7 @@
       <c r="C11" t="str">
         <v>600962</v>
       </c>
-      <c r="D11" s="130" t="str">
+      <c r="D11" s="120" t="str">
         <v>净卖: -17.88万</v>
       </c>
       <c r="E11">
@@ -8215,40 +8215,40 @@
       <c r="H11">
         <v>10.03</v>
       </c>
-      <c r="I11" s="126">
+      <c r="I11" s="121">
         <v>0</v>
       </c>
-      <c r="J11" s="127">
+      <c r="J11" s="129">
         <v>10.01</v>
       </c>
-      <c r="K11" s="128">
+      <c r="K11" s="122">
         <v>21.03</v>
       </c>
       <c r="L11" s="123">
         <v>19.13</v>
       </c>
-      <c r="M11" s="125">
+      <c r="M11" s="130">
         <v>9.62</v>
       </c>
-      <c r="N11" s="124">
+      <c r="N11" s="128">
         <v>16.33</v>
       </c>
-      <c r="O11" s="118">
+      <c r="O11" s="124">
         <v>18.74</v>
       </c>
-      <c r="P11" s="129">
+      <c r="P11" s="118">
         <v>18.01</v>
       </c>
-      <c r="Q11" s="119">
+      <c r="Q11" s="126">
         <v>14.09</v>
       </c>
-      <c r="R11" s="120">
+      <c r="R11" s="127">
         <v>10.91</v>
       </c>
-      <c r="S11" s="121">
+      <c r="S11" s="119">
         <v>10.29</v>
       </c>
-      <c r="T11" s="122">
+      <c r="T11" s="125">
         <v>15.83</v>
       </c>
     </row>
@@ -8262,7 +8262,7 @@
       <c r="C12" t="str">
         <v>003037</v>
       </c>
-      <c r="D12" s="134" t="str">
+      <c r="D12" s="139" t="str">
         <v>净卖: -2233.11万</v>
       </c>
       <c r="E12">
@@ -8277,40 +8277,40 @@
       <c r="H12">
         <v>4.89</v>
       </c>
-      <c r="I12" s="132">
+      <c r="I12" s="142">
         <v>4.88</v>
       </c>
-      <c r="J12" s="133">
+      <c r="J12" s="131">
         <v>8.77</v>
       </c>
-      <c r="K12" s="135">
+      <c r="K12" s="140">
         <v>-1.89</v>
       </c>
-      <c r="L12" s="139">
+      <c r="L12" s="132">
         <v>-3.22</v>
       </c>
-      <c r="M12" s="143">
+      <c r="M12" s="133">
         <v>6.44</v>
       </c>
-      <c r="N12" s="140">
+      <c r="N12" s="134">
         <v>17.09</v>
       </c>
-      <c r="O12" s="131">
+      <c r="O12" s="137">
         <v>16.09</v>
       </c>
-      <c r="P12" s="141">
+      <c r="P12" s="138">
         <v>14.32</v>
       </c>
-      <c r="Q12" s="136">
+      <c r="Q12" s="141">
         <v>4.88</v>
       </c>
-      <c r="R12" s="137">
+      <c r="R12" s="135">
         <v>3.77</v>
       </c>
-      <c r="S12" s="138">
+      <c r="S12" s="136">
         <v>4</v>
       </c>
-      <c r="T12" s="142">
+      <c r="T12" s="143">
         <v>-20.87</v>
       </c>
     </row>
@@ -8324,7 +8324,7 @@
       <c r="C13" t="str">
         <v>001306</v>
       </c>
-      <c r="D13" s="156" t="str">
+      <c r="D13" s="152" t="str">
         <v>净卖: -462.25万</v>
       </c>
       <c r="E13">
@@ -8339,40 +8339,40 @@
       <c r="H13">
         <v>0.03</v>
       </c>
-      <c r="I13" s="144">
+      <c r="I13" s="153">
         <v>6.62</v>
       </c>
-      <c r="J13" s="150">
+      <c r="J13" s="154">
         <v>17.29</v>
       </c>
-      <c r="K13" s="154">
+      <c r="K13" s="147">
         <v>22.79</v>
       </c>
-      <c r="L13" s="155">
+      <c r="L13" s="144">
         <v>28.15</v>
       </c>
-      <c r="M13" s="151">
+      <c r="M13" s="148">
         <v>23.18</v>
       </c>
-      <c r="N13" s="152">
+      <c r="N13" s="149">
         <v>22.64</v>
       </c>
-      <c r="O13" s="153">
+      <c r="O13" s="150">
         <v>27.89</v>
       </c>
-      <c r="P13" s="147">
+      <c r="P13" s="155">
         <v>23.34</v>
       </c>
       <c r="Q13" s="145">
         <v>24.33</v>
       </c>
-      <c r="R13" s="148">
+      <c r="R13" s="146">
         <v>22.68</v>
       </c>
-      <c r="S13" s="149">
+      <c r="S13" s="151">
         <v>28.62</v>
       </c>
-      <c r="T13" s="146">
+      <c r="T13" s="156">
         <v>-13.98</v>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       <c r="C14" t="str">
         <v>002953</v>
       </c>
-      <c r="D14" s="161" t="str">
+      <c r="D14" s="165" t="str">
         <v>净卖: -867.00万</v>
       </c>
       <c r="E14">
@@ -8401,40 +8401,40 @@
       <c r="H14">
         <v>-2.07</v>
       </c>
-      <c r="I14" s="157">
+      <c r="I14" s="169">
         <v>12.29</v>
       </c>
-      <c r="J14" s="162">
+      <c r="J14" s="157">
         <v>17.19</v>
       </c>
-      <c r="K14" s="158">
+      <c r="K14" s="166">
         <v>10.41</v>
       </c>
-      <c r="L14" s="163">
+      <c r="L14" s="167">
         <v>21.42</v>
       </c>
-      <c r="M14" s="159">
+      <c r="M14" s="160">
         <v>15.91</v>
       </c>
       <c r="N14" s="168">
         <v>4.3</v>
       </c>
-      <c r="O14" s="164">
+      <c r="O14" s="163">
         <v>-1.96</v>
       </c>
-      <c r="P14" s="169">
+      <c r="P14" s="158">
         <v>-1.06</v>
       </c>
-      <c r="Q14" s="160">
+      <c r="Q14" s="161">
         <v>-0.75</v>
       </c>
-      <c r="R14" s="165">
+      <c r="R14" s="164">
         <v>-0.98</v>
       </c>
-      <c r="S14" s="166">
+      <c r="S14" s="159">
         <v>-4.68</v>
       </c>
-      <c r="T14" s="167">
+      <c r="T14" s="162">
         <v>-6.03</v>
       </c>
     </row>
@@ -8448,7 +8448,7 @@
       <c r="C15" t="str">
         <v>605133</v>
       </c>
-      <c r="D15" s="180" t="str">
+      <c r="D15" s="179" t="str">
         <v>净买: 3043.68万</v>
       </c>
       <c r="E15">
@@ -8463,40 +8463,40 @@
       <c r="H15">
         <v>-0.11</v>
       </c>
-      <c r="I15" s="177">
+      <c r="I15" s="180">
         <v>10.11</v>
       </c>
-      <c r="J15" s="181">
+      <c r="J15" s="170">
         <v>6.15</v>
       </c>
-      <c r="K15" s="182">
+      <c r="K15" s="171">
         <v>-4.46</v>
       </c>
-      <c r="L15" s="170">
+      <c r="L15" s="174">
         <v>-0.27</v>
       </c>
-      <c r="M15" s="179">
+      <c r="M15" s="175">
         <v>3.14</v>
       </c>
-      <c r="N15" s="174">
+      <c r="N15" s="176">
         <v>1.53</v>
       </c>
-      <c r="O15" s="171">
+      <c r="O15" s="172">
         <v>-1.62</v>
       </c>
-      <c r="P15" s="172">
+      <c r="P15" s="173">
         <v>-0.46</v>
       </c>
-      <c r="Q15" s="173">
+      <c r="Q15" s="177">
         <v>-2.94</v>
       </c>
-      <c r="R15" s="175">
+      <c r="R15" s="178">
         <v>-0.55</v>
       </c>
-      <c r="S15" s="178">
+      <c r="S15" s="181">
         <v>9.41</v>
       </c>
-      <c r="T15" s="176">
+      <c r="T15" s="182">
         <v>-26.38</v>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       <c r="C16" t="str">
         <v>301533</v>
       </c>
-      <c r="D16" s="190" t="str">
+      <c r="D16" s="194" t="str">
         <v>净卖: -733.04万</v>
       </c>
       <c r="E16">
@@ -8525,40 +8525,40 @@
       <c r="H16">
         <v>2.26</v>
       </c>
-      <c r="I16" s="191">
+      <c r="I16" s="188">
         <v>3.46</v>
       </c>
-      <c r="J16" s="186">
+      <c r="J16" s="192">
         <v>8.33</v>
       </c>
-      <c r="K16" s="187">
+      <c r="K16" s="195">
         <v>10.64</v>
       </c>
-      <c r="L16" s="192">
+      <c r="L16" s="183">
         <v>7.14</v>
       </c>
-      <c r="M16" s="193">
+      <c r="M16" s="189">
         <v>11.64</v>
       </c>
-      <c r="N16" s="194">
+      <c r="N16" s="184">
         <v>6.19</v>
       </c>
-      <c r="O16" s="188">
+      <c r="O16" s="190">
         <v>3.76</v>
       </c>
-      <c r="P16" s="183">
+      <c r="P16" s="191">
         <v>0.97</v>
       </c>
-      <c r="Q16" s="184">
+      <c r="Q16" s="185">
         <v>-1.04</v>
       </c>
-      <c r="R16" s="195">
+      <c r="R16" s="186">
         <v>-2.01</v>
       </c>
-      <c r="S16" s="185">
+      <c r="S16" s="187">
         <v>-5.7</v>
       </c>
-      <c r="T16" s="189">
+      <c r="T16" s="193">
         <v>-18.85</v>
       </c>
     </row>
@@ -8572,7 +8572,7 @@
       <c r="C17" t="str">
         <v>688148</v>
       </c>
-      <c r="D17" s="202" t="str">
+      <c r="D17" s="198" t="str">
         <v>净卖: -1051.47万</v>
       </c>
       <c r="E17">
@@ -8590,37 +8590,37 @@
       <c r="I17" s="199">
         <v>15.03</v>
       </c>
-      <c r="J17" s="200">
+      <c r="J17" s="197">
         <v>37.63</v>
       </c>
-      <c r="K17" s="201">
+      <c r="K17" s="207">
         <v>33.37</v>
       </c>
-      <c r="L17" s="208">
+      <c r="L17" s="200">
         <v>33.9</v>
       </c>
-      <c r="M17" s="203">
+      <c r="M17" s="201">
         <v>29</v>
       </c>
-      <c r="N17" s="196">
+      <c r="N17" s="204">
         <v>24.95</v>
       </c>
-      <c r="O17" s="197">
+      <c r="O17" s="208">
         <v>20.36</v>
       </c>
-      <c r="P17" s="204">
+      <c r="P17" s="205">
         <v>18.44</v>
       </c>
-      <c r="Q17" s="205">
+      <c r="Q17" s="196">
         <v>13.11</v>
       </c>
-      <c r="R17" s="206">
+      <c r="R17" s="202">
         <v>1.49</v>
       </c>
-      <c r="S17" s="198">
+      <c r="S17" s="203">
         <v>-1.39</v>
       </c>
-      <c r="T17" s="207">
+      <c r="T17" s="206">
         <v>-0.43</v>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       <c r="C18" t="str">
         <v>688148</v>
       </c>
-      <c r="D18" s="212" t="str">
+      <c r="D18" s="218" t="str">
         <v>净卖: -2325.34万</v>
       </c>
       <c r="E18">
@@ -8652,37 +8652,37 @@
       <c r="I18" s="217">
         <v>13.35</v>
       </c>
-      <c r="J18" s="209">
+      <c r="J18" s="221">
         <v>9.83</v>
       </c>
-      <c r="K18" s="218">
+      <c r="K18" s="219">
         <v>10.27</v>
       </c>
-      <c r="L18" s="214">
+      <c r="L18" s="212">
         <v>6.23</v>
       </c>
-      <c r="M18" s="219">
+      <c r="M18" s="213">
         <v>2.9</v>
       </c>
-      <c r="N18" s="220">
+      <c r="N18" s="209">
         <v>-0.88</v>
       </c>
-      <c r="O18" s="221">
+      <c r="O18" s="214">
         <v>-2.46</v>
       </c>
-      <c r="P18" s="210">
+      <c r="P18" s="215">
         <v>-6.85</v>
       </c>
-      <c r="Q18" s="213">
+      <c r="Q18" s="210">
         <v>-16.42</v>
       </c>
-      <c r="R18" s="215">
+      <c r="R18" s="216">
         <v>-18.79</v>
       </c>
-      <c r="S18" s="211">
+      <c r="S18" s="220">
         <v>-16.86</v>
       </c>
-      <c r="T18" s="216">
+      <c r="T18" s="211">
         <v>-18</v>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       <c r="C19" t="str">
         <v>002506</v>
       </c>
-      <c r="D19" s="233" t="str">
+      <c r="D19" s="229" t="str">
         <v>净卖: -1046.77万</v>
       </c>
       <c r="E19">
@@ -8711,40 +8711,40 @@
       <c r="H19">
         <v>1.86</v>
       </c>
-      <c r="I19" s="230">
+      <c r="I19" s="222">
         <v>8.03</v>
       </c>
-      <c r="J19" s="234">
+      <c r="J19" s="223">
         <v>14.23</v>
       </c>
-      <c r="K19" s="227">
+      <c r="K19" s="230">
         <v>15.69</v>
       </c>
-      <c r="L19" s="224">
+      <c r="L19" s="231">
         <v>17.52</v>
       </c>
-      <c r="M19" s="225">
+      <c r="M19" s="224">
         <v>14.6</v>
       </c>
-      <c r="N19" s="226">
+      <c r="N19" s="227">
         <v>8.39</v>
       </c>
-      <c r="O19" s="222">
+      <c r="O19" s="232">
         <v>4.74</v>
       </c>
-      <c r="P19" s="228">
+      <c r="P19" s="225">
         <v>1.46</v>
       </c>
-      <c r="Q19" s="231">
+      <c r="Q19" s="228">
         <v>-6.93</v>
       </c>
-      <c r="R19" s="229">
+      <c r="R19" s="226">
         <v>-7.3</v>
       </c>
-      <c r="S19" s="232">
+      <c r="S19" s="233">
         <v>-6.57</v>
       </c>
-      <c r="T19" s="223">
+      <c r="T19" s="234">
         <v>62.41</v>
       </c>
     </row>
@@ -8758,7 +8758,7 @@
       <c r="C20" t="str">
         <v>603778</v>
       </c>
-      <c r="D20" s="244" t="str">
+      <c r="D20" s="241" t="str">
         <v>净卖: -3366.51万</v>
       </c>
       <c r="E20">
@@ -8773,37 +8773,37 @@
       <c r="H20">
         <v>6.69</v>
       </c>
-      <c r="I20" s="245">
+      <c r="I20" s="242">
         <v>3.07</v>
       </c>
-      <c r="J20" s="246">
+      <c r="J20" s="243">
         <v>13.33</v>
       </c>
-      <c r="K20" s="237">
+      <c r="K20" s="236">
         <v>5.33</v>
       </c>
-      <c r="L20" s="247">
+      <c r="L20" s="246">
         <v>8.67</v>
       </c>
-      <c r="M20" s="240">
+      <c r="M20" s="247">
         <v>19.6</v>
       </c>
-      <c r="N20" s="238">
+      <c r="N20" s="244">
         <v>7.6</v>
       </c>
-      <c r="O20" s="236">
+      <c r="O20" s="240">
         <v>-2</v>
       </c>
-      <c r="P20" s="241">
+      <c r="P20" s="235">
         <v>7.87</v>
       </c>
-      <c r="Q20" s="242">
+      <c r="Q20" s="237">
         <v>18.67</v>
       </c>
-      <c r="R20" s="235">
+      <c r="R20" s="245">
         <v>27.73</v>
       </c>
-      <c r="S20" s="243">
+      <c r="S20" s="238">
         <v>40.53</v>
       </c>
       <c r="T20" s="239">
@@ -8820,7 +8820,7 @@
       <c r="C21" t="str">
         <v>600252</v>
       </c>
-      <c r="D21" s="258" t="str">
+      <c r="D21" s="254" t="str">
         <v>净卖: -331.54万</v>
       </c>
       <c r="E21">
@@ -8835,40 +8835,40 @@
       <c r="H21">
         <v>0.37</v>
       </c>
-      <c r="I21" s="259">
+      <c r="I21" s="248">
         <v>9.67</v>
       </c>
-      <c r="J21" s="249">
+      <c r="J21" s="257">
         <v>6.32</v>
       </c>
-      <c r="K21" s="260">
+      <c r="K21" s="258">
         <v>7.81</v>
       </c>
-      <c r="L21" s="250">
+      <c r="L21" s="259">
         <v>10.41</v>
       </c>
-      <c r="M21" s="253">
+      <c r="M21" s="255">
         <v>9.29</v>
       </c>
-      <c r="N21" s="254">
+      <c r="N21" s="249">
         <v>11.9</v>
       </c>
-      <c r="O21" s="255">
+      <c r="O21" s="256">
         <v>10.78</v>
       </c>
-      <c r="P21" s="251">
+      <c r="P21" s="250">
         <v>11.52</v>
       </c>
-      <c r="Q21" s="256">
+      <c r="Q21" s="260">
         <v>10.04</v>
       </c>
-      <c r="R21" s="257">
+      <c r="R21" s="251">
         <v>6.32</v>
       </c>
-      <c r="S21" s="248">
+      <c r="S21" s="252">
         <v>5.58</v>
       </c>
-      <c r="T21" s="252">
+      <c r="T21" s="253">
         <v>-6.69</v>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       <c r="C22" t="str">
         <v>003018</v>
       </c>
-      <c r="D22" s="261" t="str">
+      <c r="D22" s="271" t="str">
         <v>净卖: -1172.31万</v>
       </c>
       <c r="E22">
@@ -8897,40 +8897,40 @@
       <c r="H22">
         <v>10.01</v>
       </c>
-      <c r="I22" s="270">
+      <c r="I22" s="263">
         <v>0</v>
       </c>
-      <c r="J22" s="271">
+      <c r="J22" s="272">
         <v>-9.99</v>
       </c>
-      <c r="K22" s="272">
+      <c r="K22" s="273">
         <v>-18.85</v>
       </c>
-      <c r="L22" s="266">
+      <c r="L22" s="264">
         <v>-18.77</v>
       </c>
-      <c r="M22" s="262">
+      <c r="M22" s="268">
         <v>-15.14</v>
       </c>
-      <c r="N22" s="263">
+      <c r="N22" s="265">
         <v>-23.48</v>
       </c>
-      <c r="O22" s="267">
+      <c r="O22" s="266">
         <v>-18.81</v>
       </c>
-      <c r="P22" s="268">
+      <c r="P22" s="261">
         <v>-22.71</v>
       </c>
-      <c r="Q22" s="269">
+      <c r="Q22" s="267">
         <v>-25.49</v>
       </c>
-      <c r="R22" s="264">
+      <c r="R22" s="269">
         <v>-25.49</v>
       </c>
-      <c r="S22" s="265">
+      <c r="S22" s="270">
         <v>-29.4</v>
       </c>
-      <c r="T22" s="273">
+      <c r="T22" s="262">
         <v>57.95</v>
       </c>
     </row>
@@ -8944,7 +8944,7 @@
       <c r="C23" t="str">
         <v>603958</v>
       </c>
-      <c r="D23" s="280" t="str">
+      <c r="D23" s="286" t="str">
         <v>净买: 48.48万</v>
       </c>
       <c r="E23">
@@ -8959,40 +8959,40 @@
       <c r="H23">
         <v>-5.98</v>
       </c>
-      <c r="I23" s="282">
+      <c r="I23" s="279">
         <v>-4.29</v>
       </c>
-      <c r="J23" s="281">
+      <c r="J23" s="274">
         <v>-7.64</v>
       </c>
-      <c r="K23" s="274">
+      <c r="K23" s="281">
         <v>-8.21</v>
       </c>
-      <c r="L23" s="283">
+      <c r="L23" s="280">
         <v>-4.29</v>
       </c>
-      <c r="M23" s="284">
+      <c r="M23" s="275">
         <v>-7.5</v>
       </c>
-      <c r="N23" s="275">
+      <c r="N23" s="282">
         <v>-8.36</v>
       </c>
       <c r="O23" s="276">
         <v>-10.57</v>
       </c>
-      <c r="P23" s="277">
+      <c r="P23" s="284">
         <v>-8.86</v>
       </c>
-      <c r="Q23" s="278">
+      <c r="Q23" s="283">
         <v>-7.43</v>
       </c>
-      <c r="R23" s="285">
+      <c r="R23" s="277">
         <v>-8</v>
       </c>
-      <c r="S23" s="279">
+      <c r="S23" s="278">
         <v>-8.71</v>
       </c>
-      <c r="T23" s="286">
+      <c r="T23" s="285">
         <v>81.64</v>
       </c>
     </row>
@@ -9006,7 +9006,7 @@
       <c r="C24" t="str">
         <v>002187</v>
       </c>
-      <c r="D24" s="294" t="str">
+      <c r="D24" s="290" t="str">
         <v>净卖: -1062.98万</v>
       </c>
       <c r="E24">
@@ -9021,40 +9021,40 @@
       <c r="H24">
         <v>2</v>
       </c>
-      <c r="I24" s="297">
+      <c r="I24" s="298">
         <v>7.83</v>
       </c>
       <c r="J24" s="291">
         <v>3.92</v>
       </c>
-      <c r="K24" s="292">
+      <c r="K24" s="294">
         <v>3.26</v>
       </c>
-      <c r="L24" s="298">
+      <c r="L24" s="292">
         <v>7.57</v>
       </c>
       <c r="M24" s="299">
         <v>10.05</v>
       </c>
-      <c r="N24" s="295">
+      <c r="N24" s="293">
         <v>8.88</v>
       </c>
-      <c r="O24" s="287">
+      <c r="O24" s="296">
         <v>4.96</v>
       </c>
-      <c r="P24" s="288">
+      <c r="P24" s="297">
         <v>7.83</v>
       </c>
-      <c r="Q24" s="296">
+      <c r="Q24" s="287">
         <v>6.4</v>
       </c>
-      <c r="R24" s="289">
+      <c r="R24" s="288">
         <v>17.1</v>
       </c>
-      <c r="S24" s="293">
+      <c r="S24" s="289">
         <v>5.61</v>
       </c>
-      <c r="T24" s="290">
+      <c r="T24" s="295">
         <v>-18.54</v>
       </c>
     </row>
@@ -9068,7 +9068,7 @@
       <c r="C25" t="str">
         <v>688273</v>
       </c>
-      <c r="D25" s="300" t="str">
+      <c r="D25" s="303" t="str">
         <v>净卖: -963.67万</v>
       </c>
       <c r="E25">
@@ -9083,40 +9083,40 @@
       <c r="H25">
         <v>-1.99</v>
       </c>
-      <c r="I25" s="311">
+      <c r="I25" s="310">
         <v>-8.57</v>
       </c>
-      <c r="J25" s="303">
+      <c r="J25" s="301">
         <v>-8.03</v>
       </c>
-      <c r="K25" s="306">
+      <c r="K25" s="304">
         <v>-11.27</v>
       </c>
-      <c r="L25" s="312">
+      <c r="L25" s="311">
         <v>-8.63</v>
       </c>
-      <c r="M25" s="304">
+      <c r="M25" s="302">
         <v>-13</v>
       </c>
       <c r="N25" s="305">
         <v>-13.83</v>
       </c>
-      <c r="O25" s="301">
+      <c r="O25" s="308">
         <v>-17.22</v>
       </c>
-      <c r="P25" s="307">
+      <c r="P25" s="306">
         <v>-20.37</v>
       </c>
-      <c r="Q25" s="308">
+      <c r="Q25" s="307">
         <v>-20.43</v>
       </c>
-      <c r="R25" s="309">
+      <c r="R25" s="312">
         <v>-22.83</v>
       </c>
-      <c r="S25" s="302">
+      <c r="S25" s="300">
         <v>-23.42</v>
       </c>
-      <c r="T25" s="310">
+      <c r="T25" s="309">
         <v>-18.5</v>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       <c r="C26" t="str">
         <v>688523</v>
       </c>
-      <c r="D26" s="324" t="str">
+      <c r="D26" s="315" t="str">
         <v>净卖: -2032.96万</v>
       </c>
       <c r="E26">
@@ -9145,40 +9145,40 @@
       <c r="H26">
         <v>-6.9</v>
       </c>
-      <c r="I26" s="320">
+      <c r="I26" s="316">
         <v>-12.28</v>
       </c>
-      <c r="J26" s="315">
+      <c r="J26" s="317">
         <v>-15.94</v>
       </c>
-      <c r="K26" s="316">
+      <c r="K26" s="313">
         <v>-22.53</v>
       </c>
-      <c r="L26" s="322">
+      <c r="L26" s="318">
         <v>-23.98</v>
       </c>
-      <c r="M26" s="323">
+      <c r="M26" s="319">
         <v>-21.69</v>
       </c>
-      <c r="N26" s="325">
+      <c r="N26" s="314">
         <v>-28.64</v>
       </c>
-      <c r="O26" s="313">
+      <c r="O26" s="320">
         <v>-29.76</v>
       </c>
       <c r="P26" s="321">
         <v>-23.74</v>
       </c>
-      <c r="Q26" s="314">
+      <c r="Q26" s="322">
         <v>-13.62</v>
       </c>
-      <c r="R26" s="317">
+      <c r="R26" s="323">
         <v>-23.24</v>
       </c>
-      <c r="S26" s="318">
+      <c r="S26" s="324">
         <v>-24.4</v>
       </c>
-      <c r="T26" s="319">
+      <c r="T26" s="325">
         <v>-17.28</v>
       </c>
     </row>
@@ -9192,7 +9192,7 @@
       <c r="C27" t="str">
         <v>002131</v>
       </c>
-      <c r="D27" s="327" t="str">
+      <c r="D27" s="332" t="str">
         <v>净买: 384.51万</v>
       </c>
       <c r="E27">
@@ -9207,37 +9207,37 @@
       <c r="H27">
         <v>-10</v>
       </c>
-      <c r="I27" s="328">
+      <c r="I27" s="326">
         <v>0</v>
       </c>
-      <c r="J27" s="333">
+      <c r="J27" s="330">
         <v>-10.04</v>
       </c>
-      <c r="K27" s="330">
+      <c r="K27" s="333">
         <v>-10.26</v>
       </c>
-      <c r="L27" s="334">
+      <c r="L27" s="327">
         <v>-14.53</v>
       </c>
-      <c r="M27" s="329">
+      <c r="M27" s="331">
         <v>-9.19</v>
       </c>
-      <c r="N27" s="335">
+      <c r="N27" s="328">
         <v>-6.3</v>
       </c>
-      <c r="O27" s="331">
+      <c r="O27" s="334">
         <v>2.24</v>
       </c>
-      <c r="P27" s="332">
+      <c r="P27" s="337">
         <v>-0.43</v>
       </c>
-      <c r="Q27" s="336">
+      <c r="Q27" s="335">
         <v>5.88</v>
       </c>
-      <c r="R27" s="326">
+      <c r="R27" s="329">
         <v>8.76</v>
       </c>
-      <c r="S27" s="337">
+      <c r="S27" s="336">
         <v>-1.07</v>
       </c>
       <c r="T27" s="338">
@@ -9254,7 +9254,7 @@
       <c r="C28" t="str">
         <v>603698</v>
       </c>
-      <c r="D28" s="344" t="str">
+      <c r="D28" s="346" t="str">
         <v>净卖: -1965.64万</v>
       </c>
       <c r="E28">
@@ -9269,40 +9269,40 @@
       <c r="H28">
         <v>-1.78</v>
       </c>
-      <c r="I28" s="345">
+      <c r="I28" s="340">
         <v>-8.38</v>
       </c>
-      <c r="J28" s="339">
+      <c r="J28" s="341">
         <v>-9.03</v>
       </c>
-      <c r="K28" s="349">
+      <c r="K28" s="347">
         <v>-9.19</v>
       </c>
-      <c r="L28" s="346">
+      <c r="L28" s="348">
         <v>-8.54</v>
       </c>
-      <c r="M28" s="350">
+      <c r="M28" s="342">
         <v>-7.3</v>
       </c>
-      <c r="N28" s="340">
+      <c r="N28" s="349">
         <v>-6.49</v>
       </c>
-      <c r="O28" s="342">
+      <c r="O28" s="351">
         <v>0.59</v>
       </c>
-      <c r="P28" s="343">
+      <c r="P28" s="350">
         <v>2.27</v>
       </c>
-      <c r="Q28" s="347">
+      <c r="Q28" s="344">
         <v>2.54</v>
       </c>
-      <c r="R28" s="341">
+      <c r="R28" s="343">
         <v>4.92</v>
       </c>
-      <c r="S28" s="348">
+      <c r="S28" s="339">
         <v>10.54</v>
       </c>
-      <c r="T28" s="351">
+      <c r="T28" s="345">
         <v>24.84</v>
       </c>
     </row>
@@ -9316,7 +9316,7 @@
       <c r="C29" t="str">
         <v>603619</v>
       </c>
-      <c r="D29" s="359" t="str">
+      <c r="D29" s="357" t="str">
         <v>净买: 3411.20万</v>
       </c>
       <c r="E29">
@@ -9331,40 +9331,40 @@
       <c r="H29">
         <v>1.96</v>
       </c>
-      <c r="I29" s="361">
+      <c r="I29" s="358">
         <v>-8.71</v>
       </c>
-      <c r="J29" s="354">
+      <c r="J29" s="359">
         <v>-17.84</v>
       </c>
-      <c r="K29" s="355">
+      <c r="K29" s="360">
         <v>-20.82</v>
       </c>
-      <c r="L29" s="360">
+      <c r="L29" s="352">
         <v>-14.71</v>
       </c>
-      <c r="M29" s="356">
+      <c r="M29" s="355">
         <v>-18.76</v>
       </c>
-      <c r="N29" s="362">
+      <c r="N29" s="361">
         <v>-14.24</v>
       </c>
-      <c r="O29" s="363">
+      <c r="O29" s="353">
         <v>-16.47</v>
       </c>
-      <c r="P29" s="357">
+      <c r="P29" s="363">
         <v>-12.61</v>
       </c>
-      <c r="Q29" s="364">
+      <c r="Q29" s="354">
         <v>-7.45</v>
       </c>
-      <c r="R29" s="358">
+      <c r="R29" s="356">
         <v>-9.16</v>
       </c>
-      <c r="S29" s="352">
+      <c r="S29" s="362">
         <v>-12.42</v>
       </c>
-      <c r="T29" s="353">
+      <c r="T29" s="364">
         <v>-11.71</v>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       <c r="C30" t="str">
         <v>688530</v>
       </c>
-      <c r="D30" s="370" t="str">
+      <c r="D30" s="375" t="str">
         <v>净卖: -1311.39万</v>
       </c>
       <c r="E30">
@@ -9393,40 +9393,40 @@
       <c r="H30">
         <v>-2.23</v>
       </c>
-      <c r="I30" s="371">
+      <c r="I30" s="376">
         <v>15.5</v>
       </c>
-      <c r="J30" s="375">
+      <c r="J30" s="374">
         <v>11.55</v>
       </c>
-      <c r="K30" s="376">
+      <c r="K30" s="371">
         <v>20.14</v>
       </c>
-      <c r="L30" s="365">
+      <c r="L30" s="377">
         <v>15.82</v>
       </c>
-      <c r="M30" s="366">
+      <c r="M30" s="365">
         <v>32.04</v>
       </c>
-      <c r="N30" s="367">
+      <c r="N30" s="372">
         <v>29.72</v>
       </c>
       <c r="O30" s="368">
         <v>28.01</v>
       </c>
-      <c r="P30" s="369">
+      <c r="P30" s="373">
         <v>31.8</v>
       </c>
-      <c r="Q30" s="377">
+      <c r="Q30" s="366">
         <v>58.17</v>
       </c>
-      <c r="R30" s="372">
+      <c r="R30" s="367">
         <v>66.44</v>
       </c>
-      <c r="S30" s="373">
+      <c r="S30" s="369">
         <v>58.53</v>
       </c>
-      <c r="T30" s="374">
+      <c r="T30" s="370">
         <v>42.83</v>
       </c>
     </row>
@@ -9440,7 +9440,7 @@
       <c r="C31" t="str">
         <v>688530</v>
       </c>
-      <c r="D31" s="389" t="str">
+      <c r="D31" s="379" t="str">
         <v>净卖: -4653.87万</v>
       </c>
       <c r="E31">
@@ -9455,40 +9455,40 @@
       <c r="H31">
         <v>-1.06</v>
       </c>
-      <c r="I31" s="384">
+      <c r="I31" s="387">
         <v>21.29</v>
       </c>
       <c r="J31" s="380">
         <v>27.63</v>
       </c>
-      <c r="K31" s="390">
+      <c r="K31" s="381">
         <v>21.57</v>
       </c>
-      <c r="L31" s="381">
+      <c r="L31" s="389">
         <v>13.14</v>
       </c>
-      <c r="M31" s="378">
+      <c r="M31" s="386">
         <v>8.21</v>
       </c>
-      <c r="N31" s="379">
+      <c r="N31" s="382">
         <v>6.59</v>
       </c>
-      <c r="O31" s="385">
+      <c r="O31" s="388">
         <v>1.78</v>
       </c>
-      <c r="P31" s="386">
+      <c r="P31" s="390">
         <v>0.09</v>
       </c>
-      <c r="Q31" s="387">
+      <c r="Q31" s="378">
         <v>6.43</v>
       </c>
-      <c r="R31" s="382">
+      <c r="R31" s="383">
         <v>1.5</v>
       </c>
-      <c r="S31" s="388">
+      <c r="S31" s="384">
         <v>5.55</v>
       </c>
-      <c r="T31" s="383">
+      <c r="T31" s="385">
         <v>9.53</v>
       </c>
     </row>
@@ -9502,7 +9502,7 @@
       <c r="C32" t="str">
         <v>600367</v>
       </c>
-      <c r="D32" s="396" t="str">
+      <c r="D32" s="399" t="str">
         <v>净买: 7875.30万</v>
       </c>
       <c r="E32">
@@ -9517,37 +9517,37 @@
       <c r="H32">
         <v>6.88</v>
       </c>
-      <c r="I32" s="398">
+      <c r="I32" s="400">
         <v>2.94</v>
       </c>
-      <c r="J32" s="399">
+      <c r="J32" s="392">
         <v>-0.72</v>
       </c>
-      <c r="K32" s="400">
+      <c r="K32" s="393">
         <v>-2.86</v>
       </c>
-      <c r="L32" s="401">
+      <c r="L32" s="396">
         <v>-5.36</v>
       </c>
-      <c r="M32" s="392">
+      <c r="M32" s="397">
         <v>-7.83</v>
       </c>
-      <c r="N32" s="402">
+      <c r="N32" s="395">
         <v>-11.24</v>
       </c>
-      <c r="O32" s="393">
+      <c r="O32" s="398">
         <v>-9.85</v>
       </c>
-      <c r="P32" s="403">
+      <c r="P32" s="394">
         <v>-6.2</v>
       </c>
-      <c r="Q32" s="394">
+      <c r="Q32" s="401">
         <v>-1.47</v>
       </c>
-      <c r="R32" s="397">
+      <c r="R32" s="402">
         <v>6.52</v>
       </c>
-      <c r="S32" s="395">
+      <c r="S32" s="403">
         <v>13.79</v>
       </c>
       <c r="T32" s="391">
@@ -9579,40 +9579,40 @@
       <c r="H33">
         <v>0.8</v>
       </c>
-      <c r="I33" s="407">
+      <c r="I33" s="408">
         <v>9.21</v>
       </c>
-      <c r="J33" s="416">
+      <c r="J33" s="409">
         <v>6.83</v>
       </c>
-      <c r="K33" s="410">
+      <c r="K33" s="412">
         <v>5.87</v>
       </c>
-      <c r="L33" s="404">
+      <c r="L33" s="406">
         <v>7.46</v>
       </c>
-      <c r="M33" s="408">
+      <c r="M33" s="416">
         <v>10.32</v>
       </c>
       <c r="N33" s="413">
         <v>12.86</v>
       </c>
-      <c r="O33" s="405">
+      <c r="O33" s="404">
         <v>7.3</v>
       </c>
-      <c r="P33" s="411">
+      <c r="P33" s="410">
         <v>4.92</v>
       </c>
       <c r="Q33" s="414">
         <v>1.11</v>
       </c>
-      <c r="R33" s="412">
+      <c r="R33" s="405">
         <v>-1.59</v>
       </c>
-      <c r="S33" s="409">
+      <c r="S33" s="407">
         <v>-5.24</v>
       </c>
-      <c r="T33" s="406">
+      <c r="T33" s="411">
         <v>-11.27</v>
       </c>
     </row>
@@ -9626,7 +9626,7 @@
       <c r="C34" t="str">
         <v>300131</v>
       </c>
-      <c r="D34" s="422" t="str">
+      <c r="D34" s="428" t="str">
         <v>净卖: -9057.02万</v>
       </c>
       <c r="E34">
@@ -9641,40 +9641,40 @@
       <c r="H34">
         <v>2.57</v>
       </c>
-      <c r="I34" s="418">
+      <c r="I34" s="421">
         <v>-18.81</v>
       </c>
-      <c r="J34" s="427">
+      <c r="J34" s="424">
         <v>-16.59</v>
       </c>
-      <c r="K34" s="423">
+      <c r="K34" s="429">
         <v>-10.32</v>
       </c>
-      <c r="L34" s="424">
+      <c r="L34" s="422">
         <v>-11.8</v>
       </c>
-      <c r="M34" s="419">
+      <c r="M34" s="425">
         <v>-16.08</v>
       </c>
-      <c r="N34" s="428">
+      <c r="N34" s="417">
         <v>-14.6</v>
       </c>
-      <c r="O34" s="420">
+      <c r="O34" s="418">
         <v>-17.4</v>
       </c>
-      <c r="P34" s="421">
+      <c r="P34" s="423">
         <v>-16.22</v>
       </c>
-      <c r="Q34" s="425">
+      <c r="Q34" s="426">
         <v>-16.74</v>
       </c>
-      <c r="R34" s="426">
+      <c r="R34" s="420">
         <v>-9.44</v>
       </c>
-      <c r="S34" s="429">
+      <c r="S34" s="419">
         <v>-5.24</v>
       </c>
-      <c r="T34" s="417">
+      <c r="T34" s="427">
         <v>15.86</v>
       </c>
     </row>
@@ -9737,40 +9737,40 @@
       <c r="F36" t="str"/>
       <c r="G36" t="str"/>
       <c r="H36" t="str"/>
-      <c r="I36" s="436">
+      <c r="I36" s="433">
         <v>54.55</v>
       </c>
-      <c r="J36" s="439">
+      <c r="J36" s="437">
         <v>57.58</v>
       </c>
-      <c r="K36" s="437">
+      <c r="K36" s="434">
         <v>51.52</v>
       </c>
-      <c r="L36" s="430">
+      <c r="L36" s="438">
         <v>54.55</v>
       </c>
-      <c r="M36" s="433">
+      <c r="M36" s="435">
         <v>60.61</v>
       </c>
-      <c r="N36" s="440">
+      <c r="N36" s="441">
         <v>57.58</v>
       </c>
-      <c r="O36" s="434">
+      <c r="O36" s="436">
         <v>54.55</v>
       </c>
-      <c r="P36" s="435">
+      <c r="P36" s="439">
         <v>54.55</v>
       </c>
-      <c r="Q36" s="431">
+      <c r="Q36" s="430">
         <v>51.52</v>
       </c>
-      <c r="R36" s="438">
+      <c r="R36" s="440">
         <v>45.45</v>
       </c>
       <c r="S36" s="432">
         <v>45.45</v>
       </c>
-      <c r="T36" s="441">
+      <c r="T36" s="431">
         <v>45.45</v>
       </c>
     </row>
@@ -9785,40 +9785,40 @@
       <c r="F37" t="str"/>
       <c r="G37" t="str"/>
       <c r="H37" t="str"/>
-      <c r="I37" s="449">
+      <c r="I37" s="442">
         <v>2.72</v>
       </c>
-      <c r="J37" s="450">
+      <c r="J37" s="446">
         <v>3.68</v>
       </c>
-      <c r="K37" s="452">
+      <c r="K37" s="447">
         <v>3.17</v>
       </c>
-      <c r="L37" s="442">
+      <c r="L37" s="443">
         <v>4.28</v>
       </c>
       <c r="M37" s="444">
         <v>4.38</v>
       </c>
-      <c r="N37" s="445">
+      <c r="N37" s="449">
         <v>2.62</v>
       </c>
-      <c r="O37" s="446">
+      <c r="O37" s="448">
         <v>1.54</v>
       </c>
-      <c r="P37" s="443">
+      <c r="P37" s="450">
         <v>1.8</v>
       </c>
-      <c r="Q37" s="453">
+      <c r="Q37" s="445">
         <v>2.18</v>
       </c>
-      <c r="R37" s="447">
+      <c r="R37" s="451">
         <v>1.38</v>
       </c>
-      <c r="S37" s="448">
+      <c r="S37" s="452">
         <v>1.44</v>
       </c>
-      <c r="T37" s="451">
+      <c r="T37" s="453">
         <v>21.14</v>
       </c>
     </row>

--- a/youzi/新生代/index.xlsx
+++ b/youzi/新生代/index.xlsx
@@ -39,6 +39,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF29A746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF22903C"/>
         <bgColor/>
       </patternFill>
@@ -51,31 +93,2329 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF57BA6E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8B94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D0D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D0D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF8F0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF79C88B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1E2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35D6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF35AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1ECD7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAADCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C1C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3FB059"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA3D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8993"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3606D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3646"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0ECD7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA4AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD63242"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEC949D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF29A746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -87,13 +2427,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8891"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE3C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,12 +2559,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -135,12 +2577,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -153,6 +2589,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -165,487 +2613,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8B94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D0D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D0D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF8F0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
+        <fgColor rgb="FF9DD6AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD6AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46572"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46572"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD6AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4636F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -657,1825 +2709,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF79C88B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1E2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1ECD7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF35AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAADCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3FB059"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C1C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE6737E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8993"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3606D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3646"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0ECD7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8891"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBAE3C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
+        <fgColor rgb="FFE56D79"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2487,271 +2727,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46572"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46572"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4636F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -7642,7 +7642,7 @@
       <c r="C2" t="str">
         <v>002238</v>
       </c>
-      <c r="D2" s="9" t="str">
+      <c r="D2" s="4" t="str">
         <v>净卖: -808.36万</v>
       </c>
       <c r="E2">
@@ -7657,41 +7657,41 @@
       <c r="H2">
         <v>4.28</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="6">
         <v>5.53</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="7">
         <v>-4.96</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="5">
         <v>-1.72</v>
       </c>
-      <c r="L2" s="13">
+      <c r="L2" s="1">
         <v>-6.11</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2" s="8">
         <v>-6.87</v>
       </c>
-      <c r="N2" s="6">
+      <c r="N2" s="10">
         <v>-8.3</v>
       </c>
-      <c r="O2" s="7">
+      <c r="O2" s="2">
         <v>-8.78</v>
       </c>
-      <c r="P2" s="4">
+      <c r="P2" s="11">
         <v>-12.21</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="12">
         <v>-13.17</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="13">
         <v>-14.03</v>
       </c>
-      <c r="S2" s="11">
+      <c r="S2" s="9">
         <v>-13.84</v>
       </c>
-      <c r="T2" s="12">
-        <v>-30.15</v>
+      <c r="T2" s="3">
+        <v>-30.25</v>
       </c>
     </row>
     <row r="3">
@@ -7704,7 +7704,7 @@
       <c r="C3" t="str">
         <v>002238</v>
       </c>
-      <c r="D3" s="22" t="str">
+      <c r="D3" s="15" t="str">
         <v>净卖: -1634.66万</v>
       </c>
       <c r="E3">
@@ -7722,38 +7722,38 @@
       <c r="I3" s="17">
         <v>-9.45</v>
       </c>
-      <c r="J3" s="23">
+      <c r="J3" s="25">
         <v>-6.36</v>
       </c>
-      <c r="K3" s="25">
+      <c r="K3" s="18">
         <v>-10.55</v>
       </c>
-      <c r="L3" s="24">
+      <c r="L3" s="19">
         <v>-11.27</v>
       </c>
-      <c r="M3" s="26">
+      <c r="M3" s="16">
         <v>-12.64</v>
       </c>
-      <c r="N3" s="18">
+      <c r="N3" s="21">
         <v>-13.09</v>
       </c>
-      <c r="O3" s="19">
+      <c r="O3" s="20">
         <v>-16.36</v>
       </c>
-      <c r="P3" s="14">
+      <c r="P3" s="22">
         <v>-17.27</v>
       </c>
-      <c r="Q3" s="20">
+      <c r="Q3" s="26">
         <v>-18.09</v>
       </c>
-      <c r="R3" s="15">
+      <c r="R3" s="23">
         <v>-17.91</v>
       </c>
-      <c r="S3" s="21">
+      <c r="S3" s="24">
         <v>-17.55</v>
       </c>
-      <c r="T3" s="16">
-        <v>-33.45</v>
+      <c r="T3" s="14">
+        <v>-33.55</v>
       </c>
     </row>
     <row r="4">
@@ -7766,7 +7766,7 @@
       <c r="C4" t="str">
         <v>600540</v>
       </c>
-      <c r="D4" s="30" t="str">
+      <c r="D4" s="32" t="str">
         <v>净卖: -203.46万</v>
       </c>
       <c r="E4">
@@ -7781,41 +7781,41 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" s="27">
+      <c r="I4" s="38">
         <v>10.08</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="33">
         <v>21.19</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="34">
         <v>33.33</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="39">
         <v>46.77</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="29">
         <v>61.5</v>
       </c>
-      <c r="N4" s="37">
+      <c r="N4" s="35">
         <v>45.48</v>
       </c>
-      <c r="O4" s="38">
+      <c r="O4" s="27">
         <v>53.23</v>
       </c>
-      <c r="P4" s="34">
+      <c r="P4" s="36">
         <v>58.66</v>
       </c>
-      <c r="Q4" s="39">
+      <c r="Q4" s="28">
         <v>51.94</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="30">
         <v>36.69</v>
       </c>
-      <c r="S4" s="29">
+      <c r="S4" s="31">
         <v>23</v>
       </c>
-      <c r="T4" s="33">
-        <v>22.74</v>
+      <c r="T4" s="37">
+        <v>26.1</v>
       </c>
     </row>
     <row r="5">
@@ -7828,7 +7828,7 @@
       <c r="C5" t="str">
         <v>002041</v>
       </c>
-      <c r="D5" s="52" t="str">
+      <c r="D5" s="46" t="str">
         <v>净卖: -388.51万</v>
       </c>
       <c r="E5">
@@ -7843,41 +7843,41 @@
       <c r="H5">
         <v>4.75</v>
       </c>
-      <c r="I5" s="48">
+      <c r="I5" s="51">
         <v>4.91</v>
       </c>
-      <c r="J5" s="40">
+      <c r="J5" s="47">
         <v>15.37</v>
       </c>
-      <c r="K5" s="41">
+      <c r="K5" s="48">
         <v>10.56</v>
       </c>
-      <c r="L5" s="46">
+      <c r="L5" s="44">
         <v>11.76</v>
       </c>
-      <c r="M5" s="42">
+      <c r="M5" s="40">
         <v>4.07</v>
       </c>
       <c r="N5" s="49">
         <v>5.09</v>
       </c>
-      <c r="O5" s="43">
+      <c r="O5" s="50">
         <v>2.87</v>
       </c>
-      <c r="P5" s="50">
+      <c r="P5" s="41">
         <v>0.56</v>
       </c>
-      <c r="Q5" s="47">
+      <c r="Q5" s="52">
         <v>0.19</v>
       </c>
-      <c r="R5" s="44">
+      <c r="R5" s="42">
         <v>-3.15</v>
       </c>
-      <c r="S5" s="51">
+      <c r="S5" s="43">
         <v>-2.31</v>
       </c>
       <c r="T5" s="45">
-        <v>-4.35</v>
+        <v>-3.89</v>
       </c>
     </row>
     <row r="6">
@@ -7890,7 +7890,7 @@
       <c r="C6" t="str">
         <v>001368</v>
       </c>
-      <c r="D6" s="60" t="str">
+      <c r="D6" s="57" t="str">
         <v>净卖: -491.53万</v>
       </c>
       <c r="E6">
@@ -7905,41 +7905,41 @@
       <c r="H6">
         <v>9.99</v>
       </c>
-      <c r="I6" s="61">
+      <c r="I6" s="53">
         <v>0</v>
       </c>
-      <c r="J6" s="62">
+      <c r="J6" s="54">
         <v>-9.94</v>
       </c>
-      <c r="K6" s="63">
+      <c r="K6" s="58">
         <v>-12.52</v>
       </c>
-      <c r="L6" s="55">
+      <c r="L6" s="63">
         <v>-3.79</v>
       </c>
       <c r="M6" s="64">
         <v>-1.89</v>
       </c>
-      <c r="N6" s="57">
+      <c r="N6" s="59">
         <v>-5.64</v>
       </c>
-      <c r="O6" s="58">
+      <c r="O6" s="60">
         <v>-7.27</v>
       </c>
-      <c r="P6" s="65">
+      <c r="P6" s="55">
         <v>-8.13</v>
       </c>
-      <c r="Q6" s="53">
+      <c r="Q6" s="61">
         <v>-8.91</v>
       </c>
-      <c r="R6" s="54">
+      <c r="R6" s="65">
         <v>-8.61</v>
       </c>
       <c r="S6" s="56">
         <v>-5.85</v>
       </c>
-      <c r="T6" s="59">
-        <v>20.4</v>
+      <c r="T6" s="62">
+        <v>25.99</v>
       </c>
     </row>
     <row r="7">
@@ -7952,7 +7952,7 @@
       <c r="C7" t="str">
         <v>603516</v>
       </c>
-      <c r="D7" s="71" t="str">
+      <c r="D7" s="72" t="str">
         <v>净买: 374.25万</v>
       </c>
       <c r="E7">
@@ -7967,41 +7967,41 @@
       <c r="H7">
         <v>-10.01</v>
       </c>
-      <c r="I7" s="75">
+      <c r="I7" s="73">
         <v>0</v>
       </c>
-      <c r="J7" s="76">
+      <c r="J7" s="78">
         <v>4.02</v>
       </c>
-      <c r="K7" s="77">
+      <c r="K7" s="66">
         <v>2.06</v>
       </c>
-      <c r="L7" s="68">
+      <c r="L7" s="67">
         <v>3.75</v>
       </c>
-      <c r="M7" s="70">
+      <c r="M7" s="74">
         <v>7.52</v>
       </c>
-      <c r="N7" s="78">
+      <c r="N7" s="69">
         <v>6.86</v>
       </c>
-      <c r="O7" s="69">
+      <c r="O7" s="70">
         <v>11.67</v>
       </c>
-      <c r="P7" s="66">
+      <c r="P7" s="68">
         <v>9.4</v>
       </c>
-      <c r="Q7" s="72">
+      <c r="Q7" s="75">
         <v>11.63</v>
       </c>
-      <c r="R7" s="67">
+      <c r="R7" s="76">
         <v>11.12</v>
       </c>
-      <c r="S7" s="73">
+      <c r="S7" s="77">
         <v>9.79</v>
       </c>
-      <c r="T7" s="74">
-        <v>345.15</v>
+      <c r="T7" s="71">
+        <v>351.95</v>
       </c>
     </row>
     <row r="8">
@@ -8014,7 +8014,7 @@
       <c r="C8" t="str">
         <v>002510</v>
       </c>
-      <c r="D8" s="85" t="str">
+      <c r="D8" s="83" t="str">
         <v>净卖: -764.76万</v>
       </c>
       <c r="E8">
@@ -8029,41 +8029,41 @@
       <c r="H8">
         <v>10.06</v>
       </c>
-      <c r="I8" s="91">
+      <c r="I8" s="87">
         <v>0</v>
       </c>
-      <c r="J8" s="86">
+      <c r="J8" s="80">
         <v>10</v>
       </c>
-      <c r="K8" s="87">
+      <c r="K8" s="81">
         <v>21</v>
       </c>
-      <c r="L8" s="79">
+      <c r="L8" s="82">
         <v>17.57</v>
       </c>
-      <c r="M8" s="90">
+      <c r="M8" s="91">
         <v>5.86</v>
       </c>
-      <c r="N8" s="80">
+      <c r="N8" s="84">
         <v>1.57</v>
       </c>
-      <c r="O8" s="82">
+      <c r="O8" s="79">
         <v>3.57</v>
       </c>
-      <c r="P8" s="83">
+      <c r="P8" s="88">
         <v>1.14</v>
       </c>
-      <c r="Q8" s="88">
+      <c r="Q8" s="85">
         <v>1.14</v>
       </c>
       <c r="R8" s="89">
         <v>-4.57</v>
       </c>
-      <c r="S8" s="81">
+      <c r="S8" s="86">
         <v>-2.71</v>
       </c>
-      <c r="T8" s="84">
-        <v>1.29</v>
+      <c r="T8" s="90">
+        <v>1.57</v>
       </c>
     </row>
     <row r="9">
@@ -8076,7 +8076,7 @@
       <c r="C9" t="str">
         <v>600367</v>
       </c>
-      <c r="D9" s="101" t="str">
+      <c r="D9" s="98" t="str">
         <v>净买: 3583.76万</v>
       </c>
       <c r="E9">
@@ -8091,41 +8091,41 @@
       <c r="H9">
         <v>4.52</v>
       </c>
-      <c r="I9" s="94">
+      <c r="I9" s="102">
         <v>-0.98</v>
       </c>
-      <c r="J9" s="102">
+      <c r="J9" s="94">
         <v>-4.07</v>
       </c>
-      <c r="K9" s="98">
+      <c r="K9" s="99">
         <v>-0.39</v>
       </c>
       <c r="L9" s="103">
         <v>5.44</v>
       </c>
-      <c r="M9" s="104">
+      <c r="M9" s="95">
         <v>5.18</v>
       </c>
-      <c r="N9" s="92">
+      <c r="N9" s="104">
         <v>12.52</v>
       </c>
-      <c r="O9" s="95">
+      <c r="O9" s="92">
         <v>1.25</v>
       </c>
-      <c r="P9" s="96">
+      <c r="P9" s="97">
         <v>11.34</v>
       </c>
-      <c r="Q9" s="97">
+      <c r="Q9" s="96">
         <v>4.07</v>
       </c>
-      <c r="R9" s="99">
+      <c r="R9" s="93">
         <v>0.26</v>
       </c>
       <c r="S9" s="100">
         <v>2.89</v>
       </c>
-      <c r="T9" s="93">
-        <v>40.07</v>
+      <c r="T9" s="101">
+        <v>46.69</v>
       </c>
     </row>
     <row r="10">
@@ -8138,7 +8138,7 @@
       <c r="C10" t="str">
         <v>603585</v>
       </c>
-      <c r="D10" s="113" t="str">
+      <c r="D10" s="108" t="str">
         <v>净买: 620.83万</v>
       </c>
       <c r="E10">
@@ -8153,41 +8153,41 @@
       <c r="H10">
         <v>-7.49</v>
       </c>
-      <c r="I10" s="109">
+      <c r="I10" s="115">
         <v>-2.7</v>
       </c>
-      <c r="J10" s="114">
+      <c r="J10" s="109">
         <v>-7</v>
       </c>
-      <c r="K10" s="115">
+      <c r="K10" s="116">
         <v>-4.8</v>
       </c>
-      <c r="L10" s="116">
+      <c r="L10" s="110">
         <v>-5.45</v>
       </c>
-      <c r="M10" s="117">
+      <c r="M10" s="111">
         <v>-7.65</v>
       </c>
-      <c r="N10" s="105">
+      <c r="N10" s="117">
         <v>-8.8</v>
       </c>
-      <c r="O10" s="110">
+      <c r="O10" s="105">
         <v>-8.55</v>
       </c>
       <c r="P10" s="106">
         <v>-7.55</v>
       </c>
-      <c r="Q10" s="107">
+      <c r="Q10" s="112">
         <v>-1.95</v>
       </c>
-      <c r="R10" s="108">
+      <c r="R10" s="113">
         <v>-3.1</v>
       </c>
-      <c r="S10" s="111">
+      <c r="S10" s="107">
         <v>6.6</v>
       </c>
-      <c r="T10" s="112">
-        <v>20.3</v>
+      <c r="T10" s="114">
+        <v>17.95</v>
       </c>
     </row>
     <row r="11">
@@ -8200,7 +8200,7 @@
       <c r="C11" t="str">
         <v>600962</v>
       </c>
-      <c r="D11" s="120" t="str">
+      <c r="D11" s="122" t="str">
         <v>净卖: -17.88万</v>
       </c>
       <c r="E11">
@@ -8215,41 +8215,41 @@
       <c r="H11">
         <v>10.03</v>
       </c>
-      <c r="I11" s="121">
+      <c r="I11" s="130">
         <v>0</v>
       </c>
-      <c r="J11" s="129">
+      <c r="J11" s="118">
         <v>10.01</v>
       </c>
-      <c r="K11" s="122">
+      <c r="K11" s="119">
         <v>21.03</v>
       </c>
-      <c r="L11" s="123">
+      <c r="L11" s="127">
         <v>19.13</v>
       </c>
-      <c r="M11" s="130">
+      <c r="M11" s="123">
         <v>9.62</v>
       </c>
-      <c r="N11" s="128">
+      <c r="N11" s="120">
         <v>16.33</v>
       </c>
       <c r="O11" s="124">
         <v>18.74</v>
       </c>
-      <c r="P11" s="118">
+      <c r="P11" s="125">
         <v>18.01</v>
       </c>
-      <c r="Q11" s="126">
+      <c r="Q11" s="128">
         <v>14.09</v>
       </c>
-      <c r="R11" s="127">
+      <c r="R11" s="126">
         <v>10.91</v>
       </c>
-      <c r="S11" s="119">
+      <c r="S11" s="121">
         <v>10.29</v>
       </c>
-      <c r="T11" s="125">
-        <v>15.83</v>
+      <c r="T11" s="129">
+        <v>22.54</v>
       </c>
     </row>
     <row r="12">
@@ -8262,7 +8262,7 @@
       <c r="C12" t="str">
         <v>003037</v>
       </c>
-      <c r="D12" s="139" t="str">
+      <c r="D12" s="133" t="str">
         <v>净卖: -2233.11万</v>
       </c>
       <c r="E12">
@@ -8277,41 +8277,41 @@
       <c r="H12">
         <v>4.89</v>
       </c>
-      <c r="I12" s="142">
+      <c r="I12" s="139">
         <v>4.88</v>
       </c>
-      <c r="J12" s="131">
+      <c r="J12" s="134">
         <v>8.77</v>
       </c>
-      <c r="K12" s="140">
+      <c r="K12" s="142">
         <v>-1.89</v>
       </c>
-      <c r="L12" s="132">
+      <c r="L12" s="135">
         <v>-3.22</v>
       </c>
-      <c r="M12" s="133">
+      <c r="M12" s="138">
         <v>6.44</v>
       </c>
-      <c r="N12" s="134">
+      <c r="N12" s="143">
         <v>17.09</v>
       </c>
-      <c r="O12" s="137">
+      <c r="O12" s="131">
         <v>16.09</v>
       </c>
-      <c r="P12" s="138">
+      <c r="P12" s="136">
         <v>14.32</v>
       </c>
-      <c r="Q12" s="141">
+      <c r="Q12" s="140">
         <v>4.88</v>
       </c>
-      <c r="R12" s="135">
+      <c r="R12" s="141">
         <v>3.77</v>
       </c>
-      <c r="S12" s="136">
+      <c r="S12" s="137">
         <v>4</v>
       </c>
-      <c r="T12" s="143">
-        <v>-20.87</v>
+      <c r="T12" s="132">
+        <v>-19.98</v>
       </c>
     </row>
     <row r="13">
@@ -8339,25 +8339,25 @@
       <c r="H13">
         <v>0.03</v>
       </c>
-      <c r="I13" s="153">
+      <c r="I13" s="146">
         <v>6.62</v>
       </c>
-      <c r="J13" s="154">
+      <c r="J13" s="149">
         <v>17.29</v>
       </c>
       <c r="K13" s="147">
         <v>22.79</v>
       </c>
-      <c r="L13" s="144">
+      <c r="L13" s="150">
         <v>28.15</v>
       </c>
-      <c r="M13" s="148">
+      <c r="M13" s="153">
         <v>23.18</v>
       </c>
-      <c r="N13" s="149">
+      <c r="N13" s="148">
         <v>22.64</v>
       </c>
-      <c r="O13" s="150">
+      <c r="O13" s="154">
         <v>27.89</v>
       </c>
       <c r="P13" s="155">
@@ -8366,14 +8366,14 @@
       <c r="Q13" s="145">
         <v>24.33</v>
       </c>
-      <c r="R13" s="146">
+      <c r="R13" s="156">
         <v>22.68</v>
       </c>
       <c r="S13" s="151">
         <v>28.62</v>
       </c>
-      <c r="T13" s="156">
-        <v>-13.98</v>
+      <c r="T13" s="144">
+        <v>-12.35</v>
       </c>
     </row>
     <row r="14">
@@ -8386,7 +8386,7 @@
       <c r="C14" t="str">
         <v>002953</v>
       </c>
-      <c r="D14" s="165" t="str">
+      <c r="D14" s="161" t="str">
         <v>净卖: -867.00万</v>
       </c>
       <c r="E14">
@@ -8401,41 +8401,41 @@
       <c r="H14">
         <v>-2.07</v>
       </c>
-      <c r="I14" s="169">
+      <c r="I14" s="162">
         <v>12.29</v>
       </c>
-      <c r="J14" s="157">
+      <c r="J14" s="163">
         <v>17.19</v>
       </c>
-      <c r="K14" s="166">
+      <c r="K14" s="164">
         <v>10.41</v>
       </c>
-      <c r="L14" s="167">
+      <c r="L14" s="166">
         <v>21.42</v>
       </c>
-      <c r="M14" s="160">
+      <c r="M14" s="158">
         <v>15.91</v>
       </c>
-      <c r="N14" s="168">
+      <c r="N14" s="167">
         <v>4.3</v>
       </c>
-      <c r="O14" s="163">
+      <c r="O14" s="169">
         <v>-1.96</v>
       </c>
-      <c r="P14" s="158">
+      <c r="P14" s="168">
         <v>-1.06</v>
       </c>
-      <c r="Q14" s="161">
+      <c r="Q14" s="159">
         <v>-0.75</v>
       </c>
-      <c r="R14" s="164">
+      <c r="R14" s="165">
         <v>-0.98</v>
       </c>
-      <c r="S14" s="159">
+      <c r="S14" s="160">
         <v>-4.68</v>
       </c>
-      <c r="T14" s="162">
-        <v>-6.03</v>
+      <c r="T14" s="157">
+        <v>-5.66</v>
       </c>
     </row>
     <row r="15">
@@ -8448,7 +8448,7 @@
       <c r="C15" t="str">
         <v>605133</v>
       </c>
-      <c r="D15" s="179" t="str">
+      <c r="D15" s="181" t="str">
         <v>净买: 3043.68万</v>
       </c>
       <c r="E15">
@@ -8463,22 +8463,22 @@
       <c r="H15">
         <v>-0.11</v>
       </c>
-      <c r="I15" s="180">
+      <c r="I15" s="182">
         <v>10.11</v>
       </c>
-      <c r="J15" s="170">
+      <c r="J15" s="178">
         <v>6.15</v>
       </c>
-      <c r="K15" s="171">
+      <c r="K15" s="179">
         <v>-4.46</v>
       </c>
-      <c r="L15" s="174">
+      <c r="L15" s="175">
         <v>-0.27</v>
       </c>
-      <c r="M15" s="175">
+      <c r="M15" s="170">
         <v>3.14</v>
       </c>
-      <c r="N15" s="176">
+      <c r="N15" s="171">
         <v>1.53</v>
       </c>
       <c r="O15" s="172">
@@ -8490,14 +8490,14 @@
       <c r="Q15" s="177">
         <v>-2.94</v>
       </c>
-      <c r="R15" s="178">
+      <c r="R15" s="180">
         <v>-0.55</v>
       </c>
-      <c r="S15" s="181">
+      <c r="S15" s="176">
         <v>9.41</v>
       </c>
-      <c r="T15" s="182">
-        <v>-26.38</v>
+      <c r="T15" s="174">
+        <v>-25.83</v>
       </c>
     </row>
     <row r="16">
@@ -8525,28 +8525,28 @@
       <c r="H16">
         <v>2.26</v>
       </c>
-      <c r="I16" s="188">
+      <c r="I16" s="195">
         <v>3.46</v>
       </c>
-      <c r="J16" s="192">
+      <c r="J16" s="190">
         <v>8.33</v>
       </c>
-      <c r="K16" s="195">
+      <c r="K16" s="191">
         <v>10.64</v>
       </c>
-      <c r="L16" s="183">
+      <c r="L16" s="193">
         <v>7.14</v>
       </c>
-      <c r="M16" s="189">
+      <c r="M16" s="183">
         <v>11.64</v>
       </c>
       <c r="N16" s="184">
         <v>6.19</v>
       </c>
-      <c r="O16" s="190">
+      <c r="O16" s="187">
         <v>3.76</v>
       </c>
-      <c r="P16" s="191">
+      <c r="P16" s="188">
         <v>0.97</v>
       </c>
       <c r="Q16" s="185">
@@ -8555,11 +8555,11 @@
       <c r="R16" s="186">
         <v>-2.01</v>
       </c>
-      <c r="S16" s="187">
+      <c r="S16" s="192">
         <v>-5.7</v>
       </c>
-      <c r="T16" s="193">
-        <v>-18.85</v>
+      <c r="T16" s="189">
+        <v>-18.55</v>
       </c>
     </row>
     <row r="17">
@@ -8587,41 +8587,41 @@
       <c r="H17">
         <v>4.34</v>
       </c>
-      <c r="I17" s="199">
+      <c r="I17" s="205">
         <v>15.03</v>
       </c>
-      <c r="J17" s="197">
+      <c r="J17" s="202">
         <v>37.63</v>
       </c>
-      <c r="K17" s="207">
+      <c r="K17" s="199">
         <v>33.37</v>
       </c>
-      <c r="L17" s="200">
+      <c r="L17" s="206">
         <v>33.9</v>
       </c>
-      <c r="M17" s="201">
+      <c r="M17" s="207">
         <v>29</v>
       </c>
-      <c r="N17" s="204">
+      <c r="N17" s="196">
         <v>24.95</v>
       </c>
-      <c r="O17" s="208">
+      <c r="O17" s="197">
         <v>20.36</v>
       </c>
-      <c r="P17" s="205">
+      <c r="P17" s="208">
         <v>18.44</v>
       </c>
-      <c r="Q17" s="196">
+      <c r="Q17" s="200">
         <v>13.11</v>
       </c>
-      <c r="R17" s="202">
+      <c r="R17" s="203">
         <v>1.49</v>
       </c>
-      <c r="S17" s="203">
+      <c r="S17" s="201">
         <v>-1.39</v>
       </c>
-      <c r="T17" s="206">
-        <v>-0.43</v>
+      <c r="T17" s="204">
+        <v>-2.13</v>
       </c>
     </row>
     <row r="18">
@@ -8634,7 +8634,7 @@
       <c r="C18" t="str">
         <v>688148</v>
       </c>
-      <c r="D18" s="218" t="str">
+      <c r="D18" s="213" t="str">
         <v>净卖: -2325.34万</v>
       </c>
       <c r="E18">
@@ -8649,41 +8649,41 @@
       <c r="H18">
         <v>5.56</v>
       </c>
-      <c r="I18" s="217">
+      <c r="I18" s="214">
         <v>13.35</v>
       </c>
-      <c r="J18" s="221">
+      <c r="J18" s="215">
         <v>9.83</v>
       </c>
       <c r="K18" s="219">
         <v>10.27</v>
       </c>
-      <c r="L18" s="212">
+      <c r="L18" s="220">
         <v>6.23</v>
       </c>
-      <c r="M18" s="213">
+      <c r="M18" s="211">
         <v>2.9</v>
       </c>
-      <c r="N18" s="209">
+      <c r="N18" s="221">
         <v>-0.88</v>
       </c>
-      <c r="O18" s="214">
+      <c r="O18" s="209">
         <v>-2.46</v>
       </c>
-      <c r="P18" s="215">
+      <c r="P18" s="216">
         <v>-6.85</v>
       </c>
-      <c r="Q18" s="210">
+      <c r="Q18" s="217">
         <v>-16.42</v>
       </c>
-      <c r="R18" s="216">
+      <c r="R18" s="212">
         <v>-18.79</v>
       </c>
-      <c r="S18" s="220">
+      <c r="S18" s="210">
         <v>-16.86</v>
       </c>
-      <c r="T18" s="211">
-        <v>-18</v>
+      <c r="T18" s="218">
+        <v>-19.4</v>
       </c>
     </row>
     <row r="19">
@@ -8696,7 +8696,7 @@
       <c r="C19" t="str">
         <v>002506</v>
       </c>
-      <c r="D19" s="229" t="str">
+      <c r="D19" s="226" t="str">
         <v>净卖: -1046.77万</v>
       </c>
       <c r="E19">
@@ -8711,41 +8711,41 @@
       <c r="H19">
         <v>1.86</v>
       </c>
-      <c r="I19" s="222">
+      <c r="I19" s="227">
         <v>8.03</v>
       </c>
-      <c r="J19" s="223">
+      <c r="J19" s="222">
         <v>14.23</v>
       </c>
-      <c r="K19" s="230">
+      <c r="K19" s="232">
         <v>15.69</v>
       </c>
-      <c r="L19" s="231">
+      <c r="L19" s="223">
         <v>17.52</v>
       </c>
-      <c r="M19" s="224">
+      <c r="M19" s="229">
         <v>14.6</v>
       </c>
-      <c r="N19" s="227">
+      <c r="N19" s="228">
         <v>8.39</v>
       </c>
-      <c r="O19" s="232">
+      <c r="O19" s="230">
         <v>4.74</v>
       </c>
-      <c r="P19" s="225">
+      <c r="P19" s="224">
         <v>1.46</v>
       </c>
-      <c r="Q19" s="228">
+      <c r="Q19" s="233">
         <v>-6.93</v>
       </c>
-      <c r="R19" s="226">
+      <c r="R19" s="234">
         <v>-7.3</v>
       </c>
-      <c r="S19" s="233">
+      <c r="S19" s="225">
         <v>-6.57</v>
       </c>
-      <c r="T19" s="234">
-        <v>62.41</v>
+      <c r="T19" s="231">
+        <v>69.71</v>
       </c>
     </row>
     <row r="20">
@@ -8758,7 +8758,7 @@
       <c r="C20" t="str">
         <v>603778</v>
       </c>
-      <c r="D20" s="241" t="str">
+      <c r="D20" s="242" t="str">
         <v>净卖: -3366.51万</v>
       </c>
       <c r="E20">
@@ -8773,41 +8773,41 @@
       <c r="H20">
         <v>6.69</v>
       </c>
-      <c r="I20" s="242">
+      <c r="I20" s="245">
         <v>3.07</v>
       </c>
-      <c r="J20" s="243">
+      <c r="J20" s="238">
         <v>13.33</v>
       </c>
-      <c r="K20" s="236">
+      <c r="K20" s="246">
         <v>5.33</v>
       </c>
-      <c r="L20" s="246">
+      <c r="L20" s="235">
         <v>8.67</v>
       </c>
-      <c r="M20" s="247">
+      <c r="M20" s="236">
         <v>19.6</v>
       </c>
-      <c r="N20" s="244">
+      <c r="N20" s="247">
         <v>7.6</v>
       </c>
-      <c r="O20" s="240">
+      <c r="O20" s="237">
         <v>-2</v>
       </c>
-      <c r="P20" s="235">
+      <c r="P20" s="243">
         <v>7.87</v>
       </c>
-      <c r="Q20" s="237">
+      <c r="Q20" s="239">
         <v>18.67</v>
       </c>
-      <c r="R20" s="245">
+      <c r="R20" s="240">
         <v>27.73</v>
       </c>
-      <c r="S20" s="238">
+      <c r="S20" s="244">
         <v>40.53</v>
       </c>
-      <c r="T20" s="239">
-        <v>223.33</v>
+      <c r="T20" s="241">
+        <v>255.73</v>
       </c>
     </row>
     <row r="21">
@@ -8820,7 +8820,7 @@
       <c r="C21" t="str">
         <v>600252</v>
       </c>
-      <c r="D21" s="254" t="str">
+      <c r="D21" s="248" t="str">
         <v>净卖: -331.54万</v>
       </c>
       <c r="E21">
@@ -8835,40 +8835,40 @@
       <c r="H21">
         <v>0.37</v>
       </c>
-      <c r="I21" s="248">
+      <c r="I21" s="258">
         <v>9.67</v>
       </c>
-      <c r="J21" s="257">
+      <c r="J21" s="260">
         <v>6.32</v>
       </c>
-      <c r="K21" s="258">
+      <c r="K21" s="252">
         <v>7.81</v>
       </c>
-      <c r="L21" s="259">
+      <c r="L21" s="253">
         <v>10.41</v>
       </c>
-      <c r="M21" s="255">
+      <c r="M21" s="249">
         <v>9.29</v>
       </c>
-      <c r="N21" s="249">
+      <c r="N21" s="259">
         <v>11.9</v>
       </c>
-      <c r="O21" s="256">
+      <c r="O21" s="254">
         <v>10.78</v>
       </c>
       <c r="P21" s="250">
         <v>11.52</v>
       </c>
-      <c r="Q21" s="260">
+      <c r="Q21" s="255">
         <v>10.04</v>
       </c>
-      <c r="R21" s="251">
+      <c r="R21" s="256">
         <v>6.32</v>
       </c>
-      <c r="S21" s="252">
+      <c r="S21" s="257">
         <v>5.58</v>
       </c>
-      <c r="T21" s="253">
+      <c r="T21" s="251">
         <v>-6.69</v>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       <c r="C22" t="str">
         <v>003018</v>
       </c>
-      <c r="D22" s="271" t="str">
+      <c r="D22" s="270" t="str">
         <v>净卖: -1172.31万</v>
       </c>
       <c r="E22">
@@ -8897,41 +8897,41 @@
       <c r="H22">
         <v>10.01</v>
       </c>
-      <c r="I22" s="263">
+      <c r="I22" s="264">
         <v>0</v>
       </c>
-      <c r="J22" s="272">
+      <c r="J22" s="261">
         <v>-9.99</v>
       </c>
-      <c r="K22" s="273">
+      <c r="K22" s="262">
         <v>-18.85</v>
       </c>
-      <c r="L22" s="264">
+      <c r="L22" s="266">
         <v>-18.77</v>
       </c>
-      <c r="M22" s="268">
+      <c r="M22" s="263">
         <v>-15.14</v>
       </c>
       <c r="N22" s="265">
         <v>-23.48</v>
       </c>
-      <c r="O22" s="266">
+      <c r="O22" s="271">
         <v>-18.81</v>
       </c>
-      <c r="P22" s="261">
+      <c r="P22" s="267">
         <v>-22.71</v>
       </c>
-      <c r="Q22" s="267">
+      <c r="Q22" s="268">
         <v>-25.49</v>
       </c>
-      <c r="R22" s="269">
+      <c r="R22" s="272">
         <v>-25.49</v>
       </c>
-      <c r="S22" s="270">
+      <c r="S22" s="269">
         <v>-29.4</v>
       </c>
-      <c r="T22" s="262">
-        <v>57.95</v>
+      <c r="T22" s="273">
+        <v>73.74</v>
       </c>
     </row>
     <row r="23">
@@ -8944,7 +8944,7 @@
       <c r="C23" t="str">
         <v>603958</v>
       </c>
-      <c r="D23" s="286" t="str">
+      <c r="D23" s="285" t="str">
         <v>净买: 48.48万</v>
       </c>
       <c r="E23">
@@ -8959,41 +8959,41 @@
       <c r="H23">
         <v>-5.98</v>
       </c>
-      <c r="I23" s="279">
+      <c r="I23" s="286">
         <v>-4.29</v>
       </c>
-      <c r="J23" s="274">
+      <c r="J23" s="278">
         <v>-7.64</v>
       </c>
       <c r="K23" s="281">
         <v>-8.21</v>
       </c>
-      <c r="L23" s="280">
+      <c r="L23" s="279">
         <v>-4.29</v>
       </c>
-      <c r="M23" s="275">
+      <c r="M23" s="284">
         <v>-7.5</v>
       </c>
-      <c r="N23" s="282">
+      <c r="N23" s="274">
         <v>-8.36</v>
       </c>
-      <c r="O23" s="276">
+      <c r="O23" s="280">
         <v>-10.57</v>
       </c>
-      <c r="P23" s="284">
+      <c r="P23" s="275">
         <v>-8.86</v>
       </c>
-      <c r="Q23" s="283">
+      <c r="Q23" s="282">
         <v>-7.43</v>
       </c>
-      <c r="R23" s="277">
+      <c r="R23" s="276">
         <v>-8</v>
       </c>
-      <c r="S23" s="278">
+      <c r="S23" s="283">
         <v>-8.71</v>
       </c>
-      <c r="T23" s="285">
-        <v>81.64</v>
+      <c r="T23" s="277">
+        <v>79.5</v>
       </c>
     </row>
     <row r="24">
@@ -9006,7 +9006,7 @@
       <c r="C24" t="str">
         <v>002187</v>
       </c>
-      <c r="D24" s="290" t="str">
+      <c r="D24" s="287" t="str">
         <v>净卖: -1062.98万</v>
       </c>
       <c r="E24">
@@ -9021,41 +9021,41 @@
       <c r="H24">
         <v>2</v>
       </c>
-      <c r="I24" s="298">
+      <c r="I24" s="295">
         <v>7.83</v>
       </c>
-      <c r="J24" s="291">
+      <c r="J24" s="288">
         <v>3.92</v>
       </c>
-      <c r="K24" s="294">
+      <c r="K24" s="291">
         <v>3.26</v>
       </c>
-      <c r="L24" s="292">
+      <c r="L24" s="297">
         <v>7.57</v>
       </c>
-      <c r="M24" s="299">
+      <c r="M24" s="298">
         <v>10.05</v>
       </c>
-      <c r="N24" s="293">
+      <c r="N24" s="292">
         <v>8.88</v>
       </c>
       <c r="O24" s="296">
         <v>4.96</v>
       </c>
-      <c r="P24" s="297">
+      <c r="P24" s="289">
         <v>7.83</v>
       </c>
-      <c r="Q24" s="287">
+      <c r="Q24" s="299">
         <v>6.4</v>
       </c>
-      <c r="R24" s="288">
+      <c r="R24" s="293">
         <v>17.1</v>
       </c>
-      <c r="S24" s="289">
+      <c r="S24" s="294">
         <v>5.61</v>
       </c>
-      <c r="T24" s="295">
-        <v>-18.54</v>
+      <c r="T24" s="290">
+        <v>-18.15</v>
       </c>
     </row>
     <row r="25">
@@ -9068,7 +9068,7 @@
       <c r="C25" t="str">
         <v>688273</v>
       </c>
-      <c r="D25" s="303" t="str">
+      <c r="D25" s="304" t="str">
         <v>净卖: -963.67万</v>
       </c>
       <c r="E25">
@@ -9083,41 +9083,41 @@
       <c r="H25">
         <v>-1.99</v>
       </c>
-      <c r="I25" s="310">
+      <c r="I25" s="305">
         <v>-8.57</v>
       </c>
-      <c r="J25" s="301">
+      <c r="J25" s="306">
         <v>-8.03</v>
       </c>
-      <c r="K25" s="304">
+      <c r="K25" s="300">
         <v>-11.27</v>
       </c>
-      <c r="L25" s="311">
+      <c r="L25" s="307">
         <v>-8.63</v>
       </c>
-      <c r="M25" s="302">
+      <c r="M25" s="301">
         <v>-13</v>
       </c>
-      <c r="N25" s="305">
+      <c r="N25" s="308">
         <v>-13.83</v>
       </c>
-      <c r="O25" s="308">
+      <c r="O25" s="302">
         <v>-17.22</v>
       </c>
-      <c r="P25" s="306">
+      <c r="P25" s="309">
         <v>-20.37</v>
       </c>
-      <c r="Q25" s="307">
+      <c r="Q25" s="310">
         <v>-20.43</v>
       </c>
-      <c r="R25" s="312">
+      <c r="R25" s="311">
         <v>-22.83</v>
       </c>
-      <c r="S25" s="300">
+      <c r="S25" s="303">
         <v>-23.42</v>
       </c>
-      <c r="T25" s="309">
-        <v>-18.5</v>
+      <c r="T25" s="312">
+        <v>-20.55</v>
       </c>
     </row>
     <row r="26">
@@ -9130,7 +9130,7 @@
       <c r="C26" t="str">
         <v>688523</v>
       </c>
-      <c r="D26" s="315" t="str">
+      <c r="D26" s="317" t="str">
         <v>净卖: -2032.96万</v>
       </c>
       <c r="E26">
@@ -9145,41 +9145,41 @@
       <c r="H26">
         <v>-6.9</v>
       </c>
-      <c r="I26" s="316">
+      <c r="I26" s="321">
         <v>-12.28</v>
       </c>
-      <c r="J26" s="317">
+      <c r="J26" s="316">
         <v>-15.94</v>
       </c>
-      <c r="K26" s="313">
+      <c r="K26" s="322">
         <v>-22.53</v>
       </c>
-      <c r="L26" s="318">
+      <c r="L26" s="314">
         <v>-23.98</v>
       </c>
-      <c r="M26" s="319">
+      <c r="M26" s="315">
         <v>-21.69</v>
       </c>
-      <c r="N26" s="314">
+      <c r="N26" s="318">
         <v>-28.64</v>
       </c>
-      <c r="O26" s="320">
+      <c r="O26" s="319">
         <v>-29.76</v>
       </c>
-      <c r="P26" s="321">
+      <c r="P26" s="320">
         <v>-23.74</v>
       </c>
-      <c r="Q26" s="322">
+      <c r="Q26" s="323">
         <v>-13.62</v>
       </c>
-      <c r="R26" s="323">
+      <c r="R26" s="324">
         <v>-23.24</v>
       </c>
-      <c r="S26" s="324">
+      <c r="S26" s="325">
         <v>-24.4</v>
       </c>
-      <c r="T26" s="325">
-        <v>-17.28</v>
+      <c r="T26" s="313">
+        <v>-11.57</v>
       </c>
     </row>
     <row r="27">
@@ -9192,7 +9192,7 @@
       <c r="C27" t="str">
         <v>002131</v>
       </c>
-      <c r="D27" s="332" t="str">
+      <c r="D27" s="328" t="str">
         <v>净买: 384.51万</v>
       </c>
       <c r="E27">
@@ -9207,41 +9207,41 @@
       <c r="H27">
         <v>-10</v>
       </c>
-      <c r="I27" s="326">
+      <c r="I27" s="331">
         <v>0</v>
       </c>
-      <c r="J27" s="330">
+      <c r="J27" s="332">
         <v>-10.04</v>
       </c>
-      <c r="K27" s="333">
+      <c r="K27" s="337">
         <v>-10.26</v>
       </c>
-      <c r="L27" s="327">
+      <c r="L27" s="334">
         <v>-14.53</v>
       </c>
-      <c r="M27" s="331">
+      <c r="M27" s="338">
         <v>-9.19</v>
       </c>
-      <c r="N27" s="328">
+      <c r="N27" s="329">
         <v>-6.3</v>
       </c>
-      <c r="O27" s="334">
+      <c r="O27" s="335">
         <v>2.24</v>
       </c>
-      <c r="P27" s="337">
+      <c r="P27" s="330">
         <v>-0.43</v>
       </c>
-      <c r="Q27" s="335">
+      <c r="Q27" s="326">
         <v>5.88</v>
       </c>
-      <c r="R27" s="329">
+      <c r="R27" s="336">
         <v>8.76</v>
       </c>
-      <c r="S27" s="336">
+      <c r="S27" s="333">
         <v>-1.07</v>
       </c>
-      <c r="T27" s="338">
-        <v>-14.96</v>
+      <c r="T27" s="327">
+        <v>-11.22</v>
       </c>
     </row>
     <row r="28">
@@ -9254,7 +9254,7 @@
       <c r="C28" t="str">
         <v>603698</v>
       </c>
-      <c r="D28" s="346" t="str">
+      <c r="D28" s="351" t="str">
         <v>净卖: -1965.64万</v>
       </c>
       <c r="E28">
@@ -9269,41 +9269,41 @@
       <c r="H28">
         <v>-1.78</v>
       </c>
-      <c r="I28" s="340">
+      <c r="I28" s="343">
         <v>-8.38</v>
       </c>
-      <c r="J28" s="341">
+      <c r="J28" s="345">
         <v>-9.03</v>
       </c>
-      <c r="K28" s="347">
+      <c r="K28" s="346">
         <v>-9.19</v>
       </c>
-      <c r="L28" s="348">
+      <c r="L28" s="349">
         <v>-8.54</v>
       </c>
-      <c r="M28" s="342">
+      <c r="M28" s="350">
         <v>-7.3</v>
       </c>
-      <c r="N28" s="349">
+      <c r="N28" s="344">
         <v>-6.49</v>
       </c>
-      <c r="O28" s="351">
+      <c r="O28" s="339">
         <v>0.59</v>
       </c>
-      <c r="P28" s="350">
+      <c r="P28" s="340">
         <v>2.27</v>
       </c>
-      <c r="Q28" s="344">
+      <c r="Q28" s="341">
         <v>2.54</v>
       </c>
-      <c r="R28" s="343">
+      <c r="R28" s="342">
         <v>4.92</v>
       </c>
-      <c r="S28" s="339">
+      <c r="S28" s="347">
         <v>10.54</v>
       </c>
-      <c r="T28" s="345">
-        <v>24.84</v>
+      <c r="T28" s="348">
+        <v>23.51</v>
       </c>
     </row>
     <row r="29">
@@ -9316,7 +9316,7 @@
       <c r="C29" t="str">
         <v>603619</v>
       </c>
-      <c r="D29" s="357" t="str">
+      <c r="D29" s="352" t="str">
         <v>净买: 3411.20万</v>
       </c>
       <c r="E29">
@@ -9331,41 +9331,41 @@
       <c r="H29">
         <v>1.96</v>
       </c>
-      <c r="I29" s="358">
+      <c r="I29" s="356">
         <v>-8.71</v>
       </c>
-      <c r="J29" s="359">
+      <c r="J29" s="357">
         <v>-17.84</v>
       </c>
-      <c r="K29" s="360">
+      <c r="K29" s="362">
         <v>-20.82</v>
       </c>
-      <c r="L29" s="352">
+      <c r="L29" s="363">
         <v>-14.71</v>
       </c>
-      <c r="M29" s="355">
+      <c r="M29" s="353">
         <v>-18.76</v>
       </c>
-      <c r="N29" s="361">
+      <c r="N29" s="364">
         <v>-14.24</v>
       </c>
-      <c r="O29" s="353">
+      <c r="O29" s="358">
         <v>-16.47</v>
       </c>
-      <c r="P29" s="363">
+      <c r="P29" s="359">
         <v>-12.61</v>
       </c>
-      <c r="Q29" s="354">
+      <c r="Q29" s="360">
         <v>-7.45</v>
       </c>
-      <c r="R29" s="356">
+      <c r="R29" s="354">
         <v>-9.16</v>
       </c>
-      <c r="S29" s="362">
+      <c r="S29" s="355">
         <v>-12.42</v>
       </c>
-      <c r="T29" s="364">
-        <v>-11.71</v>
+      <c r="T29" s="361">
+        <v>-12.53</v>
       </c>
     </row>
     <row r="30">
@@ -9378,7 +9378,7 @@
       <c r="C30" t="str">
         <v>688530</v>
       </c>
-      <c r="D30" s="375" t="str">
+      <c r="D30" s="372" t="str">
         <v>净卖: -1311.39万</v>
       </c>
       <c r="E30">
@@ -9393,41 +9393,41 @@
       <c r="H30">
         <v>-2.23</v>
       </c>
-      <c r="I30" s="376">
+      <c r="I30" s="373">
         <v>15.5</v>
       </c>
-      <c r="J30" s="374">
+      <c r="J30" s="377">
         <v>11.55</v>
       </c>
-      <c r="K30" s="371">
+      <c r="K30" s="374">
         <v>20.14</v>
       </c>
-      <c r="L30" s="377">
+      <c r="L30" s="365">
         <v>15.82</v>
       </c>
-      <c r="M30" s="365">
+      <c r="M30" s="375">
         <v>32.04</v>
       </c>
-      <c r="N30" s="372">
+      <c r="N30" s="368">
         <v>29.72</v>
       </c>
-      <c r="O30" s="368">
+      <c r="O30" s="370">
         <v>28.01</v>
       </c>
-      <c r="P30" s="373">
+      <c r="P30" s="376">
         <v>31.8</v>
       </c>
-      <c r="Q30" s="366">
+      <c r="Q30" s="369">
         <v>58.17</v>
       </c>
-      <c r="R30" s="367">
+      <c r="R30" s="371">
         <v>66.44</v>
       </c>
-      <c r="S30" s="369">
+      <c r="S30" s="366">
         <v>58.53</v>
       </c>
-      <c r="T30" s="370">
-        <v>42.83</v>
+      <c r="T30" s="367">
+        <v>33.84</v>
       </c>
     </row>
     <row r="31">
@@ -9440,7 +9440,7 @@
       <c r="C31" t="str">
         <v>688530</v>
       </c>
-      <c r="D31" s="379" t="str">
+      <c r="D31" s="384" t="str">
         <v>净卖: -4653.87万</v>
       </c>
       <c r="E31">
@@ -9455,41 +9455,41 @@
       <c r="H31">
         <v>-1.06</v>
       </c>
-      <c r="I31" s="387">
+      <c r="I31" s="385">
         <v>21.29</v>
       </c>
       <c r="J31" s="380">
         <v>27.63</v>
       </c>
-      <c r="K31" s="381">
+      <c r="K31" s="378">
         <v>21.57</v>
       </c>
-      <c r="L31" s="389">
+      <c r="L31" s="382">
         <v>13.14</v>
       </c>
       <c r="M31" s="386">
         <v>8.21</v>
       </c>
-      <c r="N31" s="382">
+      <c r="N31" s="379">
         <v>6.59</v>
       </c>
-      <c r="O31" s="388">
+      <c r="O31" s="387">
         <v>1.78</v>
       </c>
-      <c r="P31" s="390">
+      <c r="P31" s="383">
         <v>0.09</v>
       </c>
-      <c r="Q31" s="378">
+      <c r="Q31" s="381">
         <v>6.43</v>
       </c>
-      <c r="R31" s="383">
+      <c r="R31" s="388">
         <v>1.5</v>
       </c>
-      <c r="S31" s="384">
+      <c r="S31" s="389">
         <v>5.55</v>
       </c>
-      <c r="T31" s="385">
-        <v>9.53</v>
+      <c r="T31" s="390">
+        <v>2.63</v>
       </c>
     </row>
     <row r="32">
@@ -9502,7 +9502,7 @@
       <c r="C32" t="str">
         <v>600367</v>
       </c>
-      <c r="D32" s="399" t="str">
+      <c r="D32" s="396" t="str">
         <v>净买: 7875.30万</v>
       </c>
       <c r="E32">
@@ -9517,41 +9517,41 @@
       <c r="H32">
         <v>6.88</v>
       </c>
-      <c r="I32" s="400">
+      <c r="I32" s="403">
         <v>2.94</v>
       </c>
-      <c r="J32" s="392">
+      <c r="J32" s="401">
         <v>-0.72</v>
       </c>
-      <c r="K32" s="393">
+      <c r="K32" s="391">
         <v>-2.86</v>
       </c>
-      <c r="L32" s="396">
+      <c r="L32" s="397">
         <v>-5.36</v>
       </c>
-      <c r="M32" s="397">
+      <c r="M32" s="402">
         <v>-7.83</v>
       </c>
-      <c r="N32" s="395">
+      <c r="N32" s="398">
         <v>-11.24</v>
       </c>
-      <c r="O32" s="398">
+      <c r="O32" s="392">
         <v>-9.85</v>
       </c>
-      <c r="P32" s="394">
+      <c r="P32" s="393">
         <v>-6.2</v>
       </c>
-      <c r="Q32" s="401">
+      <c r="Q32" s="399">
         <v>-1.47</v>
       </c>
-      <c r="R32" s="402">
+      <c r="R32" s="394">
         <v>6.52</v>
       </c>
-      <c r="S32" s="403">
+      <c r="S32" s="400">
         <v>13.79</v>
       </c>
-      <c r="T32" s="391">
-        <v>-15.14</v>
+      <c r="T32" s="395">
+        <v>-11.12</v>
       </c>
     </row>
     <row r="33">
@@ -9564,7 +9564,7 @@
       <c r="C33" t="str">
         <v>600516</v>
       </c>
-      <c r="D33" s="415" t="str">
+      <c r="D33" s="407" t="str">
         <v>净卖: -4735.13万</v>
       </c>
       <c r="E33">
@@ -9585,34 +9585,34 @@
       <c r="J33" s="409">
         <v>6.83</v>
       </c>
-      <c r="K33" s="412">
+      <c r="K33" s="410">
         <v>5.87</v>
       </c>
-      <c r="L33" s="406">
+      <c r="L33" s="411">
         <v>7.46</v>
       </c>
-      <c r="M33" s="416">
+      <c r="M33" s="412">
         <v>10.32</v>
       </c>
       <c r="N33" s="413">
         <v>12.86</v>
       </c>
-      <c r="O33" s="404">
+      <c r="O33" s="414">
         <v>7.3</v>
       </c>
-      <c r="P33" s="410">
+      <c r="P33" s="415">
         <v>4.92</v>
       </c>
-      <c r="Q33" s="414">
+      <c r="Q33" s="404">
         <v>1.11</v>
       </c>
-      <c r="R33" s="405">
+      <c r="R33" s="416">
         <v>-1.59</v>
       </c>
-      <c r="S33" s="407">
+      <c r="S33" s="405">
         <v>-5.24</v>
       </c>
-      <c r="T33" s="411">
+      <c r="T33" s="406">
         <v>-11.27</v>
       </c>
     </row>
@@ -9626,7 +9626,7 @@
       <c r="C34" t="str">
         <v>300131</v>
       </c>
-      <c r="D34" s="428" t="str">
+      <c r="D34" s="427" t="str">
         <v>净卖: -9057.02万</v>
       </c>
       <c r="E34">
@@ -9641,41 +9641,41 @@
       <c r="H34">
         <v>2.57</v>
       </c>
-      <c r="I34" s="421">
+      <c r="I34" s="428">
         <v>-18.81</v>
       </c>
       <c r="J34" s="424">
         <v>-16.59</v>
       </c>
-      <c r="K34" s="429">
+      <c r="K34" s="422">
         <v>-10.32</v>
       </c>
-      <c r="L34" s="422">
+      <c r="L34" s="429">
         <v>-11.8</v>
       </c>
-      <c r="M34" s="425">
+      <c r="M34" s="419">
         <v>-16.08</v>
       </c>
-      <c r="N34" s="417">
+      <c r="N34" s="423">
         <v>-14.6</v>
       </c>
-      <c r="O34" s="418">
+      <c r="O34" s="425">
         <v>-17.4</v>
       </c>
-      <c r="P34" s="423">
+      <c r="P34" s="420">
         <v>-16.22</v>
       </c>
-      <c r="Q34" s="426">
+      <c r="Q34" s="421">
         <v>-16.74</v>
       </c>
-      <c r="R34" s="420">
+      <c r="R34" s="417">
         <v>-9.44</v>
       </c>
-      <c r="S34" s="419">
+      <c r="S34" s="418">
         <v>-5.24</v>
       </c>
-      <c r="T34" s="427">
-        <v>15.86</v>
+      <c r="T34" s="426">
+        <v>19.32</v>
       </c>
     </row>
     <row r="35">
@@ -9737,40 +9737,40 @@
       <c r="F36" t="str"/>
       <c r="G36" t="str"/>
       <c r="H36" t="str"/>
-      <c r="I36" s="433">
+      <c r="I36" s="431">
         <v>54.55</v>
       </c>
-      <c r="J36" s="437">
+      <c r="J36" s="438">
         <v>57.58</v>
       </c>
-      <c r="K36" s="434">
+      <c r="K36" s="439">
         <v>51.52</v>
       </c>
-      <c r="L36" s="438">
+      <c r="L36" s="432">
         <v>54.55</v>
       </c>
-      <c r="M36" s="435">
+      <c r="M36" s="433">
         <v>60.61</v>
       </c>
-      <c r="N36" s="441">
+      <c r="N36" s="437">
         <v>57.58</v>
       </c>
-      <c r="O36" s="436">
+      <c r="O36" s="434">
         <v>54.55</v>
       </c>
-      <c r="P36" s="439">
+      <c r="P36" s="435">
         <v>54.55</v>
       </c>
-      <c r="Q36" s="430">
+      <c r="Q36" s="440">
         <v>51.52</v>
       </c>
-      <c r="R36" s="440">
+      <c r="R36" s="441">
         <v>45.45</v>
       </c>
-      <c r="S36" s="432">
+      <c r="S36" s="430">
         <v>45.45</v>
       </c>
-      <c r="T36" s="431">
+      <c r="T36" s="436">
         <v>45.45</v>
       </c>
     </row>
@@ -9785,41 +9785,41 @@
       <c r="F37" t="str"/>
       <c r="G37" t="str"/>
       <c r="H37" t="str"/>
-      <c r="I37" s="442">
+      <c r="I37" s="453">
         <v>2.72</v>
       </c>
-      <c r="J37" s="446">
+      <c r="J37" s="448">
         <v>3.68</v>
       </c>
-      <c r="K37" s="447">
+      <c r="K37" s="442">
         <v>3.17</v>
       </c>
-      <c r="L37" s="443">
+      <c r="L37" s="449">
         <v>4.28</v>
       </c>
-      <c r="M37" s="444">
+      <c r="M37" s="450">
         <v>4.38</v>
       </c>
-      <c r="N37" s="449">
+      <c r="N37" s="443">
         <v>2.62</v>
       </c>
-      <c r="O37" s="448">
+      <c r="O37" s="444">
         <v>1.54</v>
       </c>
-      <c r="P37" s="450">
+      <c r="P37" s="451">
         <v>1.8</v>
       </c>
       <c r="Q37" s="445">
         <v>2.18</v>
       </c>
-      <c r="R37" s="451">
+      <c r="R37" s="446">
         <v>1.38</v>
       </c>
-      <c r="S37" s="452">
+      <c r="S37" s="447">
         <v>1.44</v>
       </c>
-      <c r="T37" s="453">
-        <v>21.14</v>
+      <c r="T37" s="452">
+        <v>23.52</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/新生代/index.xlsx
+++ b/youzi/新生代/index.xlsx
@@ -39,31 +39,2293 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF29A746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF24993F"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8B94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D0D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D0D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF8F0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF79C88B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1C7A33"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1E2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35D6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1ECD7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAADCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF35AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C1C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3FB059"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8993"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3606D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3646"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0ECD7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA4AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -75,13 +2337,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF29A746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -93,7 +2391,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -105,12 +2409,132 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8891"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE3C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -123,529 +2547,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF57BA6E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8B94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D0D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D0D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF8F0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
+        <fgColor rgb="FF9DD6AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46572"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46572"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD6AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD6AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4636F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -657,2101 +2721,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF79C88B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1E2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF35AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1ECD7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAADCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C1C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3FB059"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA3D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8993"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3606D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3646"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0ECD7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8891"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
+        <fgColor rgb="FFE56D79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBAE3C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46572"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46572"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4636F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -7657,41 +7657,41 @@
       <c r="H2">
         <v>4.28</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="12">
         <v>5.53</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="5">
         <v>-4.96</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="1">
         <v>-1.72</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="9">
         <v>-6.11</v>
       </c>
-      <c r="M2" s="8">
+      <c r="M2" s="6">
         <v>-6.87</v>
       </c>
       <c r="N2" s="10">
         <v>-8.3</v>
       </c>
-      <c r="O2" s="2">
+      <c r="O2" s="7">
         <v>-8.78</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="2">
         <v>-12.21</v>
       </c>
-      <c r="Q2" s="12">
+      <c r="Q2" s="8">
         <v>-13.17</v>
       </c>
-      <c r="R2" s="13">
+      <c r="R2" s="11">
         <v>-14.03</v>
       </c>
-      <c r="S2" s="9">
+      <c r="S2" s="13">
         <v>-13.84</v>
       </c>
       <c r="T2" s="3">
-        <v>-30.25</v>
+        <v>-31.39</v>
       </c>
     </row>
     <row r="3">
@@ -7704,7 +7704,7 @@
       <c r="C3" t="str">
         <v>002238</v>
       </c>
-      <c r="D3" s="15" t="str">
+      <c r="D3" s="23" t="str">
         <v>净卖: -1634.66万</v>
       </c>
       <c r="E3">
@@ -7719,41 +7719,41 @@
       <c r="H3">
         <v>-0.54</v>
       </c>
-      <c r="I3" s="17">
+      <c r="I3" s="19">
         <v>-9.45</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="16">
         <v>-6.36</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="17">
         <v>-10.55</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="24">
         <v>-11.27</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="25">
         <v>-12.64</v>
       </c>
-      <c r="N3" s="21">
+      <c r="N3" s="26">
         <v>-13.09</v>
       </c>
       <c r="O3" s="20">
         <v>-16.36</v>
       </c>
-      <c r="P3" s="22">
+      <c r="P3" s="14">
         <v>-17.27</v>
       </c>
-      <c r="Q3" s="26">
+      <c r="Q3" s="22">
         <v>-18.09</v>
       </c>
-      <c r="R3" s="23">
+      <c r="R3" s="15">
         <v>-17.91</v>
       </c>
-      <c r="S3" s="24">
+      <c r="S3" s="18">
         <v>-17.55</v>
       </c>
-      <c r="T3" s="14">
-        <v>-33.55</v>
+      <c r="T3" s="21">
+        <v>-34.64</v>
       </c>
     </row>
     <row r="4">
@@ -7766,7 +7766,7 @@
       <c r="C4" t="str">
         <v>600540</v>
       </c>
-      <c r="D4" s="32" t="str">
+      <c r="D4" s="27" t="str">
         <v>净卖: -203.46万</v>
       </c>
       <c r="E4">
@@ -7781,41 +7781,41 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" s="38">
+      <c r="I4" s="28">
         <v>10.08</v>
       </c>
-      <c r="J4" s="33">
+      <c r="J4" s="36">
         <v>21.19</v>
       </c>
-      <c r="K4" s="34">
+      <c r="K4" s="29">
         <v>33.33</v>
       </c>
-      <c r="L4" s="39">
+      <c r="L4" s="30">
         <v>46.77</v>
       </c>
-      <c r="M4" s="29">
+      <c r="M4" s="31">
         <v>61.5</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="37">
         <v>45.48</v>
       </c>
-      <c r="O4" s="27">
+      <c r="O4" s="38">
         <v>53.23</v>
       </c>
-      <c r="P4" s="36">
+      <c r="P4" s="35">
         <v>58.66</v>
       </c>
-      <c r="Q4" s="28">
+      <c r="Q4" s="32">
         <v>51.94</v>
       </c>
-      <c r="R4" s="30">
+      <c r="R4" s="39">
         <v>36.69</v>
       </c>
-      <c r="S4" s="31">
+      <c r="S4" s="33">
         <v>23</v>
       </c>
-      <c r="T4" s="37">
-        <v>26.1</v>
+      <c r="T4" s="34">
+        <v>25.06</v>
       </c>
     </row>
     <row r="5">
@@ -7828,7 +7828,7 @@
       <c r="C5" t="str">
         <v>002041</v>
       </c>
-      <c r="D5" s="46" t="str">
+      <c r="D5" s="49" t="str">
         <v>净卖: -388.51万</v>
       </c>
       <c r="E5">
@@ -7843,41 +7843,41 @@
       <c r="H5">
         <v>4.75</v>
       </c>
-      <c r="I5" s="51">
+      <c r="I5" s="46">
         <v>4.91</v>
       </c>
-      <c r="J5" s="47">
+      <c r="J5" s="42">
         <v>15.37</v>
       </c>
-      <c r="K5" s="48">
+      <c r="K5" s="47">
         <v>10.56</v>
       </c>
-      <c r="L5" s="44">
+      <c r="L5" s="50">
         <v>11.76</v>
       </c>
-      <c r="M5" s="40">
+      <c r="M5" s="43">
         <v>4.07</v>
       </c>
-      <c r="N5" s="49">
+      <c r="N5" s="44">
         <v>5.09</v>
       </c>
-      <c r="O5" s="50">
+      <c r="O5" s="48">
         <v>2.87</v>
       </c>
-      <c r="P5" s="41">
+      <c r="P5" s="45">
         <v>0.56</v>
       </c>
-      <c r="Q5" s="52">
+      <c r="Q5" s="41">
         <v>0.19</v>
       </c>
-      <c r="R5" s="42">
+      <c r="R5" s="51">
         <v>-3.15</v>
       </c>
-      <c r="S5" s="43">
+      <c r="S5" s="52">
         <v>-2.31</v>
       </c>
-      <c r="T5" s="45">
-        <v>-3.89</v>
+      <c r="T5" s="40">
+        <v>-5.46</v>
       </c>
     </row>
     <row r="6">
@@ -7890,7 +7890,7 @@
       <c r="C6" t="str">
         <v>001368</v>
       </c>
-      <c r="D6" s="57" t="str">
+      <c r="D6" s="55" t="str">
         <v>净卖: -491.53万</v>
       </c>
       <c r="E6">
@@ -7905,41 +7905,41 @@
       <c r="H6">
         <v>9.99</v>
       </c>
-      <c r="I6" s="53">
+      <c r="I6" s="60">
         <v>0</v>
       </c>
-      <c r="J6" s="54">
+      <c r="J6" s="64">
         <v>-9.94</v>
       </c>
-      <c r="K6" s="58">
+      <c r="K6" s="56">
         <v>-12.52</v>
       </c>
-      <c r="L6" s="63">
+      <c r="L6" s="61">
         <v>-3.79</v>
       </c>
-      <c r="M6" s="64">
+      <c r="M6" s="62">
         <v>-1.89</v>
       </c>
-      <c r="N6" s="59">
+      <c r="N6" s="54">
         <v>-5.64</v>
       </c>
-      <c r="O6" s="60">
+      <c r="O6" s="65">
         <v>-7.27</v>
       </c>
-      <c r="P6" s="55">
+      <c r="P6" s="53">
         <v>-8.13</v>
       </c>
-      <c r="Q6" s="61">
+      <c r="Q6" s="57">
         <v>-8.91</v>
       </c>
-      <c r="R6" s="65">
+      <c r="R6" s="58">
         <v>-8.61</v>
       </c>
-      <c r="S6" s="56">
+      <c r="S6" s="63">
         <v>-5.85</v>
       </c>
-      <c r="T6" s="62">
-        <v>25.99</v>
+      <c r="T6" s="59">
+        <v>26.46</v>
       </c>
     </row>
     <row r="7">
@@ -7952,7 +7952,7 @@
       <c r="C7" t="str">
         <v>603516</v>
       </c>
-      <c r="D7" s="72" t="str">
+      <c r="D7" s="70" t="str">
         <v>净买: 374.25万</v>
       </c>
       <c r="E7">
@@ -7967,41 +7967,41 @@
       <c r="H7">
         <v>-10.01</v>
       </c>
-      <c r="I7" s="73">
+      <c r="I7" s="74">
         <v>0</v>
       </c>
-      <c r="J7" s="78">
+      <c r="J7" s="77">
         <v>4.02</v>
       </c>
-      <c r="K7" s="66">
+      <c r="K7" s="71">
         <v>2.06</v>
       </c>
-      <c r="L7" s="67">
+      <c r="L7" s="78">
         <v>3.75</v>
       </c>
-      <c r="M7" s="74">
+      <c r="M7" s="75">
         <v>7.52</v>
       </c>
-      <c r="N7" s="69">
+      <c r="N7" s="66">
         <v>6.86</v>
       </c>
-      <c r="O7" s="70">
+      <c r="O7" s="67">
         <v>11.67</v>
       </c>
-      <c r="P7" s="68">
+      <c r="P7" s="72">
         <v>9.4</v>
       </c>
-      <c r="Q7" s="75">
+      <c r="Q7" s="68">
         <v>11.63</v>
       </c>
-      <c r="R7" s="76">
+      <c r="R7" s="73">
         <v>11.12</v>
       </c>
-      <c r="S7" s="77">
+      <c r="S7" s="69">
         <v>9.79</v>
       </c>
-      <c r="T7" s="71">
-        <v>351.95</v>
+      <c r="T7" s="76">
+        <v>344.24</v>
       </c>
     </row>
     <row r="8">
@@ -8014,7 +8014,7 @@
       <c r="C8" t="str">
         <v>002510</v>
       </c>
-      <c r="D8" s="83" t="str">
+      <c r="D8" s="85" t="str">
         <v>净卖: -764.76万</v>
       </c>
       <c r="E8">
@@ -8029,41 +8029,41 @@
       <c r="H8">
         <v>10.06</v>
       </c>
-      <c r="I8" s="87">
+      <c r="I8" s="79">
         <v>0</v>
       </c>
-      <c r="J8" s="80">
+      <c r="J8" s="86">
         <v>10</v>
       </c>
-      <c r="K8" s="81">
+      <c r="K8" s="89">
         <v>21</v>
       </c>
-      <c r="L8" s="82">
+      <c r="L8" s="80">
         <v>17.57</v>
       </c>
-      <c r="M8" s="91">
+      <c r="M8" s="87">
         <v>5.86</v>
       </c>
-      <c r="N8" s="84">
+      <c r="N8" s="81">
         <v>1.57</v>
       </c>
-      <c r="O8" s="79">
+      <c r="O8" s="83">
         <v>3.57</v>
       </c>
-      <c r="P8" s="88">
+      <c r="P8" s="90">
         <v>1.14</v>
       </c>
-      <c r="Q8" s="85">
+      <c r="Q8" s="84">
         <v>1.14</v>
       </c>
-      <c r="R8" s="89">
+      <c r="R8" s="82">
         <v>-4.57</v>
       </c>
-      <c r="S8" s="86">
+      <c r="S8" s="91">
         <v>-2.71</v>
       </c>
-      <c r="T8" s="90">
-        <v>1.57</v>
+      <c r="T8" s="88">
+        <v>-1.29</v>
       </c>
     </row>
     <row r="9">
@@ -8076,7 +8076,7 @@
       <c r="C9" t="str">
         <v>600367</v>
       </c>
-      <c r="D9" s="98" t="str">
+      <c r="D9" s="101" t="str">
         <v>净买: 3583.76万</v>
       </c>
       <c r="E9">
@@ -8094,38 +8094,38 @@
       <c r="I9" s="102">
         <v>-0.98</v>
       </c>
-      <c r="J9" s="94">
+      <c r="J9" s="93">
         <v>-4.07</v>
       </c>
-      <c r="K9" s="99">
+      <c r="K9" s="92">
         <v>-0.39</v>
       </c>
-      <c r="L9" s="103">
+      <c r="L9" s="94">
         <v>5.44</v>
       </c>
       <c r="M9" s="95">
         <v>5.18</v>
       </c>
-      <c r="N9" s="104">
+      <c r="N9" s="103">
         <v>12.52</v>
       </c>
-      <c r="O9" s="92">
+      <c r="O9" s="96">
         <v>1.25</v>
       </c>
-      <c r="P9" s="97">
+      <c r="P9" s="98">
         <v>11.34</v>
       </c>
-      <c r="Q9" s="96">
+      <c r="Q9" s="99">
         <v>4.07</v>
       </c>
-      <c r="R9" s="93">
+      <c r="R9" s="97">
         <v>0.26</v>
       </c>
-      <c r="S9" s="100">
+      <c r="S9" s="104">
         <v>2.89</v>
       </c>
-      <c r="T9" s="101">
-        <v>46.69</v>
+      <c r="T9" s="100">
+        <v>48.2</v>
       </c>
     </row>
     <row r="10">
@@ -8138,7 +8138,7 @@
       <c r="C10" t="str">
         <v>603585</v>
       </c>
-      <c r="D10" s="108" t="str">
+      <c r="D10" s="105" t="str">
         <v>净买: 620.83万</v>
       </c>
       <c r="E10">
@@ -8156,38 +8156,38 @@
       <c r="I10" s="115">
         <v>-2.7</v>
       </c>
-      <c r="J10" s="109">
+      <c r="J10" s="116">
         <v>-7</v>
       </c>
-      <c r="K10" s="116">
+      <c r="K10" s="106">
         <v>-4.8</v>
       </c>
-      <c r="L10" s="110">
+      <c r="L10" s="112">
         <v>-5.45</v>
       </c>
-      <c r="M10" s="111">
+      <c r="M10" s="110">
         <v>-7.65</v>
       </c>
-      <c r="N10" s="117">
+      <c r="N10" s="113">
         <v>-8.8</v>
       </c>
-      <c r="O10" s="105">
+      <c r="O10" s="107">
         <v>-8.55</v>
       </c>
-      <c r="P10" s="106">
+      <c r="P10" s="108">
         <v>-7.55</v>
       </c>
-      <c r="Q10" s="112">
+      <c r="Q10" s="114">
         <v>-1.95</v>
       </c>
-      <c r="R10" s="113">
+      <c r="R10" s="111">
         <v>-3.1</v>
       </c>
-      <c r="S10" s="107">
+      <c r="S10" s="109">
         <v>6.6</v>
       </c>
-      <c r="T10" s="114">
-        <v>17.95</v>
+      <c r="T10" s="117">
+        <v>16.65</v>
       </c>
     </row>
     <row r="11">
@@ -8200,7 +8200,7 @@
       <c r="C11" t="str">
         <v>600962</v>
       </c>
-      <c r="D11" s="122" t="str">
+      <c r="D11" s="124" t="str">
         <v>净卖: -17.88万</v>
       </c>
       <c r="E11">
@@ -8215,41 +8215,41 @@
       <c r="H11">
         <v>10.03</v>
       </c>
-      <c r="I11" s="130">
+      <c r="I11" s="118">
         <v>0</v>
       </c>
-      <c r="J11" s="118">
+      <c r="J11" s="123">
         <v>10.01</v>
       </c>
-      <c r="K11" s="119">
+      <c r="K11" s="121">
         <v>21.03</v>
       </c>
-      <c r="L11" s="127">
+      <c r="L11" s="125">
         <v>19.13</v>
       </c>
-      <c r="M11" s="123">
+      <c r="M11" s="126">
         <v>9.62</v>
       </c>
-      <c r="N11" s="120">
+      <c r="N11" s="127">
         <v>16.33</v>
       </c>
-      <c r="O11" s="124">
+      <c r="O11" s="119">
         <v>18.74</v>
       </c>
-      <c r="P11" s="125">
+      <c r="P11" s="128">
         <v>18.01</v>
       </c>
-      <c r="Q11" s="128">
+      <c r="Q11" s="120">
         <v>14.09</v>
       </c>
-      <c r="R11" s="126">
+      <c r="R11" s="122">
         <v>10.91</v>
       </c>
-      <c r="S11" s="121">
+      <c r="S11" s="129">
         <v>10.29</v>
       </c>
-      <c r="T11" s="129">
-        <v>22.54</v>
+      <c r="T11" s="130">
+        <v>20.97</v>
       </c>
     </row>
     <row r="12">
@@ -8262,7 +8262,7 @@
       <c r="C12" t="str">
         <v>003037</v>
       </c>
-      <c r="D12" s="133" t="str">
+      <c r="D12" s="137" t="str">
         <v>净卖: -2233.11万</v>
       </c>
       <c r="E12">
@@ -8277,41 +8277,41 @@
       <c r="H12">
         <v>4.89</v>
       </c>
-      <c r="I12" s="139">
+      <c r="I12" s="141">
         <v>4.88</v>
       </c>
-      <c r="J12" s="134">
+      <c r="J12" s="142">
         <v>8.77</v>
       </c>
-      <c r="K12" s="142">
+      <c r="K12" s="143">
         <v>-1.89</v>
       </c>
-      <c r="L12" s="135">
+      <c r="L12" s="138">
         <v>-3.22</v>
       </c>
-      <c r="M12" s="138">
+      <c r="M12" s="131">
         <v>6.44</v>
       </c>
-      <c r="N12" s="143">
+      <c r="N12" s="139">
         <v>17.09</v>
       </c>
-      <c r="O12" s="131">
+      <c r="O12" s="132">
         <v>16.09</v>
       </c>
-      <c r="P12" s="136">
+      <c r="P12" s="133">
         <v>14.32</v>
       </c>
-      <c r="Q12" s="140">
+      <c r="Q12" s="134">
         <v>4.88</v>
       </c>
-      <c r="R12" s="141">
+      <c r="R12" s="135">
         <v>3.77</v>
       </c>
-      <c r="S12" s="137">
+      <c r="S12" s="136">
         <v>4</v>
       </c>
-      <c r="T12" s="132">
-        <v>-19.98</v>
+      <c r="T12" s="140">
+        <v>-20.31</v>
       </c>
     </row>
     <row r="13">
@@ -8324,7 +8324,7 @@
       <c r="C13" t="str">
         <v>001306</v>
       </c>
-      <c r="D13" s="152" t="str">
+      <c r="D13" s="153" t="str">
         <v>净卖: -462.25万</v>
       </c>
       <c r="E13">
@@ -8339,41 +8339,41 @@
       <c r="H13">
         <v>0.03</v>
       </c>
-      <c r="I13" s="146">
+      <c r="I13" s="145">
         <v>6.62</v>
       </c>
-      <c r="J13" s="149">
+      <c r="J13" s="154">
         <v>17.29</v>
       </c>
-      <c r="K13" s="147">
+      <c r="K13" s="155">
         <v>22.79</v>
       </c>
-      <c r="L13" s="150">
+      <c r="L13" s="146">
         <v>28.15</v>
       </c>
-      <c r="M13" s="153">
+      <c r="M13" s="147">
         <v>23.18</v>
       </c>
       <c r="N13" s="148">
         <v>22.64</v>
       </c>
-      <c r="O13" s="154">
+      <c r="O13" s="149">
         <v>27.89</v>
       </c>
-      <c r="P13" s="155">
+      <c r="P13" s="152">
         <v>23.34</v>
       </c>
-      <c r="Q13" s="145">
+      <c r="Q13" s="150">
         <v>24.33</v>
       </c>
-      <c r="R13" s="156">
+      <c r="R13" s="151">
         <v>22.68</v>
       </c>
-      <c r="S13" s="151">
+      <c r="S13" s="156">
         <v>28.62</v>
       </c>
       <c r="T13" s="144">
-        <v>-12.35</v>
+        <v>-10.37</v>
       </c>
     </row>
     <row r="14">
@@ -8386,7 +8386,7 @@
       <c r="C14" t="str">
         <v>002953</v>
       </c>
-      <c r="D14" s="161" t="str">
+      <c r="D14" s="164" t="str">
         <v>净卖: -867.00万</v>
       </c>
       <c r="E14">
@@ -8401,41 +8401,41 @@
       <c r="H14">
         <v>-2.07</v>
       </c>
-      <c r="I14" s="162">
+      <c r="I14" s="157">
         <v>12.29</v>
       </c>
-      <c r="J14" s="163">
+      <c r="J14" s="165">
         <v>17.19</v>
       </c>
-      <c r="K14" s="164">
+      <c r="K14" s="166">
         <v>10.41</v>
       </c>
-      <c r="L14" s="166">
+      <c r="L14" s="160">
         <v>21.42</v>
       </c>
-      <c r="M14" s="158">
+      <c r="M14" s="167">
         <v>15.91</v>
       </c>
-      <c r="N14" s="167">
+      <c r="N14" s="168">
         <v>4.3</v>
       </c>
-      <c r="O14" s="169">
+      <c r="O14" s="161">
         <v>-1.96</v>
       </c>
-      <c r="P14" s="168">
+      <c r="P14" s="158">
         <v>-1.06</v>
       </c>
       <c r="Q14" s="159">
         <v>-0.75</v>
       </c>
-      <c r="R14" s="165">
+      <c r="R14" s="162">
         <v>-0.98</v>
       </c>
-      <c r="S14" s="160">
+      <c r="S14" s="169">
         <v>-4.68</v>
       </c>
-      <c r="T14" s="157">
-        <v>-5.66</v>
+      <c r="T14" s="163">
+        <v>-7.47</v>
       </c>
     </row>
     <row r="15">
@@ -8448,7 +8448,7 @@
       <c r="C15" t="str">
         <v>605133</v>
       </c>
-      <c r="D15" s="181" t="str">
+      <c r="D15" s="182" t="str">
         <v>净买: 3043.68万</v>
       </c>
       <c r="E15">
@@ -8463,41 +8463,41 @@
       <c r="H15">
         <v>-0.11</v>
       </c>
-      <c r="I15" s="182">
+      <c r="I15" s="170">
         <v>10.11</v>
       </c>
-      <c r="J15" s="178">
+      <c r="J15" s="171">
         <v>6.15</v>
       </c>
-      <c r="K15" s="179">
+      <c r="K15" s="181">
         <v>-4.46</v>
       </c>
-      <c r="L15" s="175">
+      <c r="L15" s="176">
         <v>-0.27</v>
       </c>
-      <c r="M15" s="170">
+      <c r="M15" s="177">
         <v>3.14</v>
       </c>
-      <c r="N15" s="171">
+      <c r="N15" s="178">
         <v>1.53</v>
       </c>
-      <c r="O15" s="172">
+      <c r="O15" s="179">
         <v>-1.62</v>
       </c>
-      <c r="P15" s="173">
+      <c r="P15" s="180">
         <v>-0.46</v>
       </c>
-      <c r="Q15" s="177">
+      <c r="Q15" s="172">
         <v>-2.94</v>
       </c>
-      <c r="R15" s="180">
+      <c r="R15" s="173">
         <v>-0.55</v>
       </c>
-      <c r="S15" s="176">
+      <c r="S15" s="174">
         <v>9.41</v>
       </c>
-      <c r="T15" s="174">
-        <v>-25.83</v>
+      <c r="T15" s="175">
+        <v>-25.31</v>
       </c>
     </row>
     <row r="16">
@@ -8510,7 +8510,7 @@
       <c r="C16" t="str">
         <v>301533</v>
       </c>
-      <c r="D16" s="194" t="str">
+      <c r="D16" s="190" t="str">
         <v>净卖: -733.04万</v>
       </c>
       <c r="E16">
@@ -8525,41 +8525,41 @@
       <c r="H16">
         <v>2.26</v>
       </c>
-      <c r="I16" s="195">
+      <c r="I16" s="188">
         <v>3.46</v>
       </c>
-      <c r="J16" s="190">
+      <c r="J16" s="195">
         <v>8.33</v>
       </c>
-      <c r="K16" s="191">
+      <c r="K16" s="183">
         <v>10.64</v>
       </c>
-      <c r="L16" s="193">
+      <c r="L16" s="191">
         <v>7.14</v>
       </c>
-      <c r="M16" s="183">
+      <c r="M16" s="186">
         <v>11.64</v>
       </c>
       <c r="N16" s="184">
         <v>6.19</v>
       </c>
-      <c r="O16" s="187">
+      <c r="O16" s="192">
         <v>3.76</v>
       </c>
-      <c r="P16" s="188">
+      <c r="P16" s="185">
         <v>0.97</v>
       </c>
-      <c r="Q16" s="185">
+      <c r="Q16" s="193">
         <v>-1.04</v>
       </c>
-      <c r="R16" s="186">
+      <c r="R16" s="194">
         <v>-2.01</v>
       </c>
-      <c r="S16" s="192">
+      <c r="S16" s="189">
         <v>-5.7</v>
       </c>
-      <c r="T16" s="189">
-        <v>-18.55</v>
+      <c r="T16" s="187">
+        <v>-19.22</v>
       </c>
     </row>
     <row r="17">
@@ -8572,7 +8572,7 @@
       <c r="C17" t="str">
         <v>688148</v>
       </c>
-      <c r="D17" s="198" t="str">
+      <c r="D17" s="206" t="str">
         <v>净卖: -1051.47万</v>
       </c>
       <c r="E17">
@@ -8587,41 +8587,41 @@
       <c r="H17">
         <v>4.34</v>
       </c>
-      <c r="I17" s="205">
+      <c r="I17" s="197">
         <v>15.03</v>
       </c>
-      <c r="J17" s="202">
+      <c r="J17" s="207">
         <v>37.63</v>
       </c>
-      <c r="K17" s="199">
+      <c r="K17" s="203">
         <v>33.37</v>
       </c>
-      <c r="L17" s="206">
+      <c r="L17" s="198">
         <v>33.9</v>
       </c>
-      <c r="M17" s="207">
+      <c r="M17" s="204">
         <v>29</v>
       </c>
-      <c r="N17" s="196">
+      <c r="N17" s="200">
         <v>24.95</v>
       </c>
-      <c r="O17" s="197">
+      <c r="O17" s="201">
         <v>20.36</v>
       </c>
       <c r="P17" s="208">
         <v>18.44</v>
       </c>
-      <c r="Q17" s="200">
+      <c r="Q17" s="199">
         <v>13.11</v>
       </c>
-      <c r="R17" s="203">
+      <c r="R17" s="196">
         <v>1.49</v>
       </c>
-      <c r="S17" s="201">
+      <c r="S17" s="205">
         <v>-1.39</v>
       </c>
-      <c r="T17" s="204">
-        <v>-2.13</v>
+      <c r="T17" s="202">
+        <v>1.81</v>
       </c>
     </row>
     <row r="18">
@@ -8634,7 +8634,7 @@
       <c r="C18" t="str">
         <v>688148</v>
       </c>
-      <c r="D18" s="213" t="str">
+      <c r="D18" s="209" t="str">
         <v>净卖: -2325.34万</v>
       </c>
       <c r="E18">
@@ -8649,41 +8649,41 @@
       <c r="H18">
         <v>5.56</v>
       </c>
-      <c r="I18" s="214">
+      <c r="I18" s="210">
         <v>13.35</v>
       </c>
       <c r="J18" s="215">
         <v>9.83</v>
       </c>
-      <c r="K18" s="219">
+      <c r="K18" s="216">
         <v>10.27</v>
       </c>
-      <c r="L18" s="220">
+      <c r="L18" s="211">
         <v>6.23</v>
       </c>
-      <c r="M18" s="211">
+      <c r="M18" s="219">
         <v>2.9</v>
       </c>
-      <c r="N18" s="221">
+      <c r="N18" s="217">
         <v>-0.88</v>
       </c>
-      <c r="O18" s="209">
+      <c r="O18" s="220">
         <v>-2.46</v>
       </c>
-      <c r="P18" s="216">
+      <c r="P18" s="212">
         <v>-6.85</v>
       </c>
-      <c r="Q18" s="217">
+      <c r="Q18" s="213">
         <v>-16.42</v>
       </c>
-      <c r="R18" s="212">
+      <c r="R18" s="221">
         <v>-18.79</v>
       </c>
-      <c r="S18" s="210">
+      <c r="S18" s="218">
         <v>-16.86</v>
       </c>
-      <c r="T18" s="218">
-        <v>-19.4</v>
+      <c r="T18" s="214">
+        <v>-16.15</v>
       </c>
     </row>
     <row r="19">
@@ -8696,7 +8696,7 @@
       <c r="C19" t="str">
         <v>002506</v>
       </c>
-      <c r="D19" s="226" t="str">
+      <c r="D19" s="228" t="str">
         <v>净卖: -1046.77万</v>
       </c>
       <c r="E19">
@@ -8711,41 +8711,41 @@
       <c r="H19">
         <v>1.86</v>
       </c>
-      <c r="I19" s="227">
+      <c r="I19" s="229">
         <v>8.03</v>
       </c>
-      <c r="J19" s="222">
+      <c r="J19" s="234">
         <v>14.23</v>
       </c>
-      <c r="K19" s="232">
+      <c r="K19" s="230">
         <v>15.69</v>
       </c>
-      <c r="L19" s="223">
+      <c r="L19" s="224">
         <v>17.52</v>
       </c>
-      <c r="M19" s="229">
+      <c r="M19" s="225">
         <v>14.6</v>
       </c>
-      <c r="N19" s="228">
+      <c r="N19" s="232">
         <v>8.39</v>
       </c>
-      <c r="O19" s="230">
+      <c r="O19" s="226">
         <v>4.74</v>
       </c>
-      <c r="P19" s="224">
+      <c r="P19" s="222">
         <v>1.46</v>
       </c>
-      <c r="Q19" s="233">
+      <c r="Q19" s="227">
         <v>-6.93</v>
       </c>
-      <c r="R19" s="234">
+      <c r="R19" s="223">
         <v>-7.3</v>
       </c>
-      <c r="S19" s="225">
+      <c r="S19" s="231">
         <v>-6.57</v>
       </c>
-      <c r="T19" s="231">
-        <v>69.71</v>
+      <c r="T19" s="233">
+        <v>78.1</v>
       </c>
     </row>
     <row r="20">
@@ -8758,7 +8758,7 @@
       <c r="C20" t="str">
         <v>603778</v>
       </c>
-      <c r="D20" s="242" t="str">
+      <c r="D20" s="246" t="str">
         <v>净卖: -3366.51万</v>
       </c>
       <c r="E20">
@@ -8773,41 +8773,41 @@
       <c r="H20">
         <v>6.69</v>
       </c>
-      <c r="I20" s="245">
+      <c r="I20" s="247">
         <v>3.07</v>
       </c>
-      <c r="J20" s="238">
+      <c r="J20" s="237">
         <v>13.33</v>
       </c>
-      <c r="K20" s="246">
+      <c r="K20" s="235">
         <v>5.33</v>
       </c>
-      <c r="L20" s="235">
+      <c r="L20" s="238">
         <v>8.67</v>
       </c>
-      <c r="M20" s="236">
+      <c r="M20" s="243">
         <v>19.6</v>
       </c>
-      <c r="N20" s="247">
+      <c r="N20" s="245">
         <v>7.6</v>
       </c>
-      <c r="O20" s="237">
+      <c r="O20" s="239">
         <v>-2</v>
       </c>
-      <c r="P20" s="243">
+      <c r="P20" s="244">
         <v>7.87</v>
       </c>
-      <c r="Q20" s="239">
+      <c r="Q20" s="236">
         <v>18.67</v>
       </c>
       <c r="R20" s="240">
         <v>27.73</v>
       </c>
-      <c r="S20" s="244">
+      <c r="S20" s="241">
         <v>40.53</v>
       </c>
-      <c r="T20" s="241">
-        <v>255.73</v>
+      <c r="T20" s="242">
+        <v>286.67</v>
       </c>
     </row>
     <row r="21">
@@ -8820,7 +8820,7 @@
       <c r="C21" t="str">
         <v>600252</v>
       </c>
-      <c r="D21" s="248" t="str">
+      <c r="D21" s="251" t="str">
         <v>净卖: -331.54万</v>
       </c>
       <c r="E21">
@@ -8835,41 +8835,41 @@
       <c r="H21">
         <v>0.37</v>
       </c>
-      <c r="I21" s="258">
+      <c r="I21" s="252">
         <v>9.67</v>
       </c>
-      <c r="J21" s="260">
+      <c r="J21" s="253">
         <v>6.32</v>
       </c>
-      <c r="K21" s="252">
+      <c r="K21" s="254">
         <v>7.81</v>
       </c>
-      <c r="L21" s="253">
+      <c r="L21" s="255">
         <v>10.41</v>
       </c>
-      <c r="M21" s="249">
+      <c r="M21" s="259">
         <v>9.29</v>
       </c>
-      <c r="N21" s="259">
+      <c r="N21" s="256">
         <v>11.9</v>
       </c>
-      <c r="O21" s="254">
+      <c r="O21" s="257">
         <v>10.78</v>
       </c>
-      <c r="P21" s="250">
+      <c r="P21" s="258">
         <v>11.52</v>
       </c>
-      <c r="Q21" s="255">
+      <c r="Q21" s="260">
         <v>10.04</v>
       </c>
-      <c r="R21" s="256">
+      <c r="R21" s="248">
         <v>6.32</v>
       </c>
-      <c r="S21" s="257">
+      <c r="S21" s="249">
         <v>5.58</v>
       </c>
-      <c r="T21" s="251">
-        <v>-6.69</v>
+      <c r="T21" s="250">
+        <v>-7.43</v>
       </c>
     </row>
     <row r="22">
@@ -8882,7 +8882,7 @@
       <c r="C22" t="str">
         <v>003018</v>
       </c>
-      <c r="D22" s="270" t="str">
+      <c r="D22" s="273" t="str">
         <v>净卖: -1172.31万</v>
       </c>
       <c r="E22">
@@ -8897,41 +8897,41 @@
       <c r="H22">
         <v>10.01</v>
       </c>
-      <c r="I22" s="264">
+      <c r="I22" s="266">
         <v>0</v>
       </c>
-      <c r="J22" s="261">
+      <c r="J22" s="267">
         <v>-9.99</v>
       </c>
-      <c r="K22" s="262">
+      <c r="K22" s="268">
         <v>-18.85</v>
       </c>
-      <c r="L22" s="266">
+      <c r="L22" s="270">
         <v>-18.77</v>
       </c>
-      <c r="M22" s="263">
+      <c r="M22" s="261">
         <v>-15.14</v>
       </c>
-      <c r="N22" s="265">
+      <c r="N22" s="269">
         <v>-23.48</v>
       </c>
-      <c r="O22" s="271">
+      <c r="O22" s="265">
         <v>-18.81</v>
       </c>
-      <c r="P22" s="267">
+      <c r="P22" s="262">
         <v>-22.71</v>
       </c>
-      <c r="Q22" s="268">
+      <c r="Q22" s="263">
         <v>-25.49</v>
       </c>
-      <c r="R22" s="272">
+      <c r="R22" s="264">
         <v>-25.49</v>
       </c>
-      <c r="S22" s="269">
+      <c r="S22" s="271">
         <v>-29.4</v>
       </c>
-      <c r="T22" s="273">
-        <v>73.74</v>
+      <c r="T22" s="272">
+        <v>91.1</v>
       </c>
     </row>
     <row r="23">
@@ -8962,38 +8962,38 @@
       <c r="I23" s="286">
         <v>-4.29</v>
       </c>
-      <c r="J23" s="278">
+      <c r="J23" s="275">
         <v>-7.64</v>
       </c>
-      <c r="K23" s="281">
+      <c r="K23" s="276">
         <v>-8.21</v>
       </c>
-      <c r="L23" s="279">
+      <c r="L23" s="282">
         <v>-4.29</v>
       </c>
-      <c r="M23" s="284">
+      <c r="M23" s="279">
         <v>-7.5</v>
       </c>
-      <c r="N23" s="274">
+      <c r="N23" s="277">
         <v>-8.36</v>
       </c>
-      <c r="O23" s="280">
+      <c r="O23" s="283">
         <v>-10.57</v>
       </c>
-      <c r="P23" s="275">
+      <c r="P23" s="274">
         <v>-8.86</v>
       </c>
-      <c r="Q23" s="282">
+      <c r="Q23" s="280">
         <v>-7.43</v>
       </c>
-      <c r="R23" s="276">
+      <c r="R23" s="278">
         <v>-8</v>
       </c>
-      <c r="S23" s="283">
+      <c r="S23" s="281">
         <v>-8.71</v>
       </c>
-      <c r="T23" s="277">
-        <v>79.5</v>
+      <c r="T23" s="284">
+        <v>90.21</v>
       </c>
     </row>
     <row r="24">
@@ -9006,7 +9006,7 @@
       <c r="C24" t="str">
         <v>002187</v>
       </c>
-      <c r="D24" s="287" t="str">
+      <c r="D24" s="295" t="str">
         <v>净卖: -1062.98万</v>
       </c>
       <c r="E24">
@@ -9021,41 +9021,41 @@
       <c r="H24">
         <v>2</v>
       </c>
-      <c r="I24" s="295">
+      <c r="I24" s="292">
         <v>7.83</v>
       </c>
-      <c r="J24" s="288">
+      <c r="J24" s="296">
         <v>3.92</v>
       </c>
-      <c r="K24" s="291">
+      <c r="K24" s="299">
         <v>3.26</v>
       </c>
-      <c r="L24" s="297">
+      <c r="L24" s="287">
         <v>7.57</v>
       </c>
-      <c r="M24" s="298">
+      <c r="M24" s="288">
         <v>10.05</v>
       </c>
-      <c r="N24" s="292">
+      <c r="N24" s="293">
         <v>8.88</v>
       </c>
-      <c r="O24" s="296">
+      <c r="O24" s="297">
         <v>4.96</v>
       </c>
-      <c r="P24" s="289">
+      <c r="P24" s="298">
         <v>7.83</v>
       </c>
-      <c r="Q24" s="299">
+      <c r="Q24" s="289">
         <v>6.4</v>
       </c>
-      <c r="R24" s="293">
+      <c r="R24" s="294">
         <v>17.1</v>
       </c>
-      <c r="S24" s="294">
+      <c r="S24" s="290">
         <v>5.61</v>
       </c>
-      <c r="T24" s="290">
-        <v>-18.15</v>
+      <c r="T24" s="291">
+        <v>-19.19</v>
       </c>
     </row>
     <row r="25">
@@ -9086,16 +9086,16 @@
       <c r="I25" s="305">
         <v>-8.57</v>
       </c>
-      <c r="J25" s="306">
+      <c r="J25" s="301">
         <v>-8.03</v>
       </c>
       <c r="K25" s="300">
         <v>-11.27</v>
       </c>
-      <c r="L25" s="307">
+      <c r="L25" s="306">
         <v>-8.63</v>
       </c>
-      <c r="M25" s="301">
+      <c r="M25" s="307">
         <v>-13</v>
       </c>
       <c r="N25" s="308">
@@ -9104,20 +9104,20 @@
       <c r="O25" s="302">
         <v>-17.22</v>
       </c>
-      <c r="P25" s="309">
+      <c r="P25" s="311">
         <v>-20.37</v>
       </c>
-      <c r="Q25" s="310">
+      <c r="Q25" s="309">
         <v>-20.43</v>
       </c>
-      <c r="R25" s="311">
+      <c r="R25" s="303">
         <v>-22.83</v>
       </c>
-      <c r="S25" s="303">
+      <c r="S25" s="310">
         <v>-23.42</v>
       </c>
       <c r="T25" s="312">
-        <v>-20.55</v>
+        <v>-19.88</v>
       </c>
     </row>
     <row r="26">
@@ -9130,7 +9130,7 @@
       <c r="C26" t="str">
         <v>688523</v>
       </c>
-      <c r="D26" s="317" t="str">
+      <c r="D26" s="324" t="str">
         <v>净卖: -2032.96万</v>
       </c>
       <c r="E26">
@@ -9145,22 +9145,22 @@
       <c r="H26">
         <v>-6.9</v>
       </c>
-      <c r="I26" s="321">
+      <c r="I26" s="318">
         <v>-12.28</v>
       </c>
-      <c r="J26" s="316">
+      <c r="J26" s="325">
         <v>-15.94</v>
       </c>
-      <c r="K26" s="322">
+      <c r="K26" s="315">
         <v>-22.53</v>
       </c>
-      <c r="L26" s="314">
+      <c r="L26" s="322">
         <v>-23.98</v>
       </c>
-      <c r="M26" s="315">
+      <c r="M26" s="316">
         <v>-21.69</v>
       </c>
-      <c r="N26" s="318">
+      <c r="N26" s="313">
         <v>-28.64</v>
       </c>
       <c r="O26" s="319">
@@ -9172,14 +9172,14 @@
       <c r="Q26" s="323">
         <v>-13.62</v>
       </c>
-      <c r="R26" s="324">
+      <c r="R26" s="321">
         <v>-23.24</v>
       </c>
-      <c r="S26" s="325">
+      <c r="S26" s="314">
         <v>-24.4</v>
       </c>
-      <c r="T26" s="313">
-        <v>-11.57</v>
+      <c r="T26" s="317">
+        <v>-13.73</v>
       </c>
     </row>
     <row r="27">
@@ -9207,41 +9207,41 @@
       <c r="H27">
         <v>-10</v>
       </c>
-      <c r="I27" s="331">
+      <c r="I27" s="338">
         <v>0</v>
       </c>
-      <c r="J27" s="332">
+      <c r="J27" s="326">
         <v>-10.04</v>
       </c>
-      <c r="K27" s="337">
+      <c r="K27" s="329">
         <v>-10.26</v>
       </c>
-      <c r="L27" s="334">
+      <c r="L27" s="330">
         <v>-14.53</v>
       </c>
-      <c r="M27" s="338">
+      <c r="M27" s="335">
         <v>-9.19</v>
       </c>
-      <c r="N27" s="329">
+      <c r="N27" s="327">
         <v>-6.3</v>
       </c>
-      <c r="O27" s="335">
+      <c r="O27" s="333">
         <v>2.24</v>
       </c>
-      <c r="P27" s="330">
+      <c r="P27" s="331">
         <v>-0.43</v>
       </c>
-      <c r="Q27" s="326">
+      <c r="Q27" s="336">
         <v>5.88</v>
       </c>
-      <c r="R27" s="336">
+      <c r="R27" s="337">
         <v>8.76</v>
       </c>
-      <c r="S27" s="333">
+      <c r="S27" s="332">
         <v>-1.07</v>
       </c>
-      <c r="T27" s="327">
-        <v>-11.22</v>
+      <c r="T27" s="334">
+        <v>-14.42</v>
       </c>
     </row>
     <row r="28">
@@ -9254,7 +9254,7 @@
       <c r="C28" t="str">
         <v>603698</v>
       </c>
-      <c r="D28" s="351" t="str">
+      <c r="D28" s="342" t="str">
         <v>净卖: -1965.64万</v>
       </c>
       <c r="E28">
@@ -9269,41 +9269,41 @@
       <c r="H28">
         <v>-1.78</v>
       </c>
-      <c r="I28" s="343">
+      <c r="I28" s="350">
         <v>-8.38</v>
       </c>
-      <c r="J28" s="345">
+      <c r="J28" s="347">
         <v>-9.03</v>
       </c>
-      <c r="K28" s="346">
+      <c r="K28" s="343">
         <v>-9.19</v>
       </c>
-      <c r="L28" s="349">
+      <c r="L28" s="351">
         <v>-8.54</v>
       </c>
-      <c r="M28" s="350">
+      <c r="M28" s="348">
         <v>-7.3</v>
       </c>
-      <c r="N28" s="344">
+      <c r="N28" s="339">
         <v>-6.49</v>
       </c>
-      <c r="O28" s="339">
+      <c r="O28" s="349">
         <v>0.59</v>
       </c>
-      <c r="P28" s="340">
+      <c r="P28" s="344">
         <v>2.27</v>
       </c>
-      <c r="Q28" s="341">
+      <c r="Q28" s="345">
         <v>2.54</v>
       </c>
-      <c r="R28" s="342">
+      <c r="R28" s="346">
         <v>4.92</v>
       </c>
-      <c r="S28" s="347">
+      <c r="S28" s="340">
         <v>10.54</v>
       </c>
-      <c r="T28" s="348">
-        <v>23.51</v>
+      <c r="T28" s="341">
+        <v>24.89</v>
       </c>
     </row>
     <row r="29">
@@ -9316,7 +9316,7 @@
       <c r="C29" t="str">
         <v>603619</v>
       </c>
-      <c r="D29" s="352" t="str">
+      <c r="D29" s="353" t="str">
         <v>净买: 3411.20万</v>
       </c>
       <c r="E29">
@@ -9331,41 +9331,41 @@
       <c r="H29">
         <v>1.96</v>
       </c>
-      <c r="I29" s="356">
+      <c r="I29" s="354">
         <v>-8.71</v>
       </c>
-      <c r="J29" s="357">
+      <c r="J29" s="364">
         <v>-17.84</v>
       </c>
-      <c r="K29" s="362">
+      <c r="K29" s="355">
         <v>-20.82</v>
       </c>
-      <c r="L29" s="363">
+      <c r="L29" s="362">
         <v>-14.71</v>
       </c>
-      <c r="M29" s="353">
+      <c r="M29" s="363">
         <v>-18.76</v>
       </c>
-      <c r="N29" s="364">
+      <c r="N29" s="356">
         <v>-14.24</v>
       </c>
-      <c r="O29" s="358">
+      <c r="O29" s="357">
         <v>-16.47</v>
       </c>
-      <c r="P29" s="359">
+      <c r="P29" s="358">
         <v>-12.61</v>
       </c>
-      <c r="Q29" s="360">
+      <c r="Q29" s="359">
         <v>-7.45</v>
       </c>
-      <c r="R29" s="354">
+      <c r="R29" s="360">
         <v>-9.16</v>
       </c>
-      <c r="S29" s="355">
+      <c r="S29" s="361">
         <v>-12.42</v>
       </c>
-      <c r="T29" s="361">
-        <v>-12.53</v>
+      <c r="T29" s="352">
+        <v>-14.97</v>
       </c>
     </row>
     <row r="30">
@@ -9378,7 +9378,7 @@
       <c r="C30" t="str">
         <v>688530</v>
       </c>
-      <c r="D30" s="372" t="str">
+      <c r="D30" s="366" t="str">
         <v>净卖: -1311.39万</v>
       </c>
       <c r="E30">
@@ -9393,41 +9393,41 @@
       <c r="H30">
         <v>-2.23</v>
       </c>
-      <c r="I30" s="373">
+      <c r="I30" s="370">
         <v>15.5</v>
       </c>
-      <c r="J30" s="377">
+      <c r="J30" s="371">
         <v>11.55</v>
       </c>
-      <c r="K30" s="374">
+      <c r="K30" s="367">
         <v>20.14</v>
       </c>
-      <c r="L30" s="365">
+      <c r="L30" s="377">
         <v>15.82</v>
       </c>
-      <c r="M30" s="375">
+      <c r="M30" s="368">
         <v>32.04</v>
       </c>
-      <c r="N30" s="368">
+      <c r="N30" s="375">
         <v>29.72</v>
       </c>
-      <c r="O30" s="370">
+      <c r="O30" s="365">
         <v>28.01</v>
       </c>
-      <c r="P30" s="376">
+      <c r="P30" s="372">
         <v>31.8</v>
       </c>
       <c r="Q30" s="369">
         <v>58.17</v>
       </c>
-      <c r="R30" s="371">
+      <c r="R30" s="373">
         <v>66.44</v>
       </c>
-      <c r="S30" s="366">
+      <c r="S30" s="374">
         <v>58.53</v>
       </c>
-      <c r="T30" s="367">
-        <v>33.84</v>
+      <c r="T30" s="376">
+        <v>39.79</v>
       </c>
     </row>
     <row r="31">
@@ -9440,7 +9440,7 @@
       <c r="C31" t="str">
         <v>688530</v>
       </c>
-      <c r="D31" s="384" t="str">
+      <c r="D31" s="379" t="str">
         <v>净卖: -4653.87万</v>
       </c>
       <c r="E31">
@@ -9455,41 +9455,41 @@
       <c r="H31">
         <v>-1.06</v>
       </c>
-      <c r="I31" s="385">
+      <c r="I31" s="380">
         <v>21.29</v>
       </c>
-      <c r="J31" s="380">
+      <c r="J31" s="385">
         <v>27.63</v>
       </c>
-      <c r="K31" s="378">
+      <c r="K31" s="387">
         <v>21.57</v>
       </c>
-      <c r="L31" s="382">
+      <c r="L31" s="390">
         <v>13.14</v>
       </c>
-      <c r="M31" s="386">
+      <c r="M31" s="381">
         <v>8.21</v>
       </c>
-      <c r="N31" s="379">
+      <c r="N31" s="382">
         <v>6.59</v>
       </c>
-      <c r="O31" s="387">
+      <c r="O31" s="378">
         <v>1.78</v>
       </c>
-      <c r="P31" s="383">
+      <c r="P31" s="388">
         <v>0.09</v>
       </c>
-      <c r="Q31" s="381">
+      <c r="Q31" s="386">
         <v>6.43</v>
       </c>
-      <c r="R31" s="388">
+      <c r="R31" s="389">
         <v>1.5</v>
       </c>
-      <c r="S31" s="389">
+      <c r="S31" s="383">
         <v>5.55</v>
       </c>
-      <c r="T31" s="390">
-        <v>2.63</v>
+      <c r="T31" s="384">
+        <v>7.2</v>
       </c>
     </row>
     <row r="32">
@@ -9517,41 +9517,41 @@
       <c r="H32">
         <v>6.88</v>
       </c>
-      <c r="I32" s="403">
+      <c r="I32" s="397">
         <v>2.94</v>
       </c>
-      <c r="J32" s="401">
+      <c r="J32" s="391">
         <v>-0.72</v>
       </c>
-      <c r="K32" s="391">
+      <c r="K32" s="393">
         <v>-2.86</v>
       </c>
-      <c r="L32" s="397">
+      <c r="L32" s="400">
         <v>-5.36</v>
       </c>
-      <c r="M32" s="402">
+      <c r="M32" s="394">
         <v>-7.83</v>
       </c>
-      <c r="N32" s="398">
+      <c r="N32" s="395">
         <v>-11.24</v>
       </c>
-      <c r="O32" s="392">
+      <c r="O32" s="401">
         <v>-9.85</v>
       </c>
-      <c r="P32" s="393">
+      <c r="P32" s="402">
         <v>-6.2</v>
       </c>
-      <c r="Q32" s="399">
+      <c r="Q32" s="398">
         <v>-1.47</v>
       </c>
-      <c r="R32" s="394">
+      <c r="R32" s="403">
         <v>6.52</v>
       </c>
-      <c r="S32" s="400">
+      <c r="S32" s="399">
         <v>13.79</v>
       </c>
-      <c r="T32" s="395">
-        <v>-11.12</v>
+      <c r="T32" s="392">
+        <v>-10.21</v>
       </c>
     </row>
     <row r="33">
@@ -9564,7 +9564,7 @@
       <c r="C33" t="str">
         <v>600516</v>
       </c>
-      <c r="D33" s="407" t="str">
+      <c r="D33" s="413" t="str">
         <v>净卖: -4735.13万</v>
       </c>
       <c r="E33">
@@ -9579,41 +9579,41 @@
       <c r="H33">
         <v>0.8</v>
       </c>
-      <c r="I33" s="408">
+      <c r="I33" s="404">
         <v>9.21</v>
       </c>
-      <c r="J33" s="409">
+      <c r="J33" s="410">
         <v>6.83</v>
       </c>
-      <c r="K33" s="410">
+      <c r="K33" s="416">
         <v>5.87</v>
       </c>
       <c r="L33" s="411">
         <v>7.46</v>
       </c>
-      <c r="M33" s="412">
+      <c r="M33" s="405">
         <v>10.32</v>
       </c>
-      <c r="N33" s="413">
+      <c r="N33" s="414">
         <v>12.86</v>
       </c>
-      <c r="O33" s="414">
+      <c r="O33" s="406">
         <v>7.3</v>
       </c>
-      <c r="P33" s="415">
+      <c r="P33" s="407">
         <v>4.92</v>
       </c>
-      <c r="Q33" s="404">
+      <c r="Q33" s="412">
         <v>1.11</v>
       </c>
-      <c r="R33" s="416">
+      <c r="R33" s="415">
         <v>-1.59</v>
       </c>
-      <c r="S33" s="405">
+      <c r="S33" s="408">
         <v>-5.24</v>
       </c>
-      <c r="T33" s="406">
-        <v>-11.27</v>
+      <c r="T33" s="409">
+        <v>-13.02</v>
       </c>
     </row>
     <row r="34">
@@ -9626,7 +9626,7 @@
       <c r="C34" t="str">
         <v>300131</v>
       </c>
-      <c r="D34" s="427" t="str">
+      <c r="D34" s="429" t="str">
         <v>净卖: -9057.02万</v>
       </c>
       <c r="E34">
@@ -9641,41 +9641,41 @@
       <c r="H34">
         <v>2.57</v>
       </c>
-      <c r="I34" s="428">
+      <c r="I34" s="418">
         <v>-18.81</v>
       </c>
-      <c r="J34" s="424">
+      <c r="J34" s="421">
         <v>-16.59</v>
       </c>
-      <c r="K34" s="422">
+      <c r="K34" s="425">
         <v>-10.32</v>
       </c>
-      <c r="L34" s="429">
+      <c r="L34" s="419">
         <v>-11.8</v>
       </c>
-      <c r="M34" s="419">
+      <c r="M34" s="417">
         <v>-16.08</v>
       </c>
-      <c r="N34" s="423">
+      <c r="N34" s="426">
         <v>-14.6</v>
       </c>
-      <c r="O34" s="425">
+      <c r="O34" s="422">
         <v>-17.4</v>
       </c>
-      <c r="P34" s="420">
+      <c r="P34" s="423">
         <v>-16.22</v>
       </c>
-      <c r="Q34" s="421">
+      <c r="Q34" s="420">
         <v>-16.74</v>
       </c>
-      <c r="R34" s="417">
+      <c r="R34" s="427">
         <v>-9.44</v>
       </c>
-      <c r="S34" s="418">
+      <c r="S34" s="428">
         <v>-5.24</v>
       </c>
-      <c r="T34" s="426">
-        <v>19.32</v>
+      <c r="T34" s="424">
+        <v>30.68</v>
       </c>
     </row>
     <row r="35">
@@ -9737,40 +9737,40 @@
       <c r="F36" t="str"/>
       <c r="G36" t="str"/>
       <c r="H36" t="str"/>
-      <c r="I36" s="431">
+      <c r="I36" s="436">
         <v>54.55</v>
       </c>
-      <c r="J36" s="438">
+      <c r="J36" s="437">
         <v>57.58</v>
       </c>
-      <c r="K36" s="439">
+      <c r="K36" s="432">
         <v>51.52</v>
       </c>
-      <c r="L36" s="432">
+      <c r="L36" s="438">
         <v>54.55</v>
       </c>
       <c r="M36" s="433">
         <v>60.61</v>
       </c>
-      <c r="N36" s="437">
+      <c r="N36" s="434">
         <v>57.58</v>
       </c>
-      <c r="O36" s="434">
+      <c r="O36" s="435">
         <v>54.55</v>
       </c>
-      <c r="P36" s="435">
+      <c r="P36" s="439">
         <v>54.55</v>
       </c>
-      <c r="Q36" s="440">
+      <c r="Q36" s="431">
         <v>51.52</v>
       </c>
       <c r="R36" s="441">
         <v>45.45</v>
       </c>
-      <c r="S36" s="430">
+      <c r="S36" s="440">
         <v>45.45</v>
       </c>
-      <c r="T36" s="436">
+      <c r="T36" s="430">
         <v>45.45</v>
       </c>
     </row>
@@ -9785,10 +9785,10 @@
       <c r="F37" t="str"/>
       <c r="G37" t="str"/>
       <c r="H37" t="str"/>
-      <c r="I37" s="453">
+      <c r="I37" s="450">
         <v>2.72</v>
       </c>
-      <c r="J37" s="448">
+      <c r="J37" s="453">
         <v>3.68</v>
       </c>
       <c r="K37" s="442">
@@ -9797,29 +9797,29 @@
       <c r="L37" s="449">
         <v>4.28</v>
       </c>
-      <c r="M37" s="450">
+      <c r="M37" s="451">
         <v>4.38</v>
       </c>
       <c r="N37" s="443">
         <v>2.62</v>
       </c>
-      <c r="O37" s="444">
+      <c r="O37" s="446">
         <v>1.54</v>
       </c>
-      <c r="P37" s="451">
+      <c r="P37" s="452">
         <v>1.8</v>
       </c>
-      <c r="Q37" s="445">
+      <c r="Q37" s="447">
         <v>2.18</v>
       </c>
-      <c r="R37" s="446">
+      <c r="R37" s="444">
         <v>1.38</v>
       </c>
-      <c r="S37" s="447">
+      <c r="S37" s="448">
         <v>1.44</v>
       </c>
-      <c r="T37" s="452">
-        <v>23.52</v>
+      <c r="T37" s="445">
+        <v>25.68</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/新生代/index.xlsx
+++ b/youzi/新生代/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="455">
+  <fills count="462">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,12 +39,84 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF29A746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB5E0BF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -57,13 +129,1243 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF29A746"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8B94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D0D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D0D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF71C584"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF8F0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF79C88B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1E2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35D6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF35AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAADCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1ECD7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3FB059"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C1C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8993"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -75,7 +1377,223 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -87,49 +1605,937 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3646"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3606D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA4AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0ECD7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD63242"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8891"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE3C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -147,301 +2553,199 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1A7230"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8B94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFE7747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C3C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46572"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD6AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD6AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C3C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4636F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -453,145 +2757,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D0D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D0D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF8F0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -601,2162 +2797,57 @@
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF79C88B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1E2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1ECD7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAADCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF35AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C1C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3FB059"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8993"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3606D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3646"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0ECD7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8891"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBAE3C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46572"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46572"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4636F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="454">
+  <borders count="461">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -5939,7 +6030,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="454">
+  <cellXfs count="461">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -7298,6 +7389,27 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="453" fillId="454" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="454" fillId="455" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="455" fillId="456" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="456" fillId="457" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="457" fillId="458" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="458" fillId="459" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="459" fillId="460" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="460" fillId="461" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -7642,7 +7754,7 @@
       <c r="C2" t="str">
         <v>002238</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="3" t="str">
         <v>净卖: -808.36万</v>
       </c>
       <c r="E2">
@@ -7657,41 +7769,41 @@
       <c r="H2">
         <v>4.28</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="13">
         <v>5.53</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="4">
         <v>-4.96</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="11">
         <v>-1.72</v>
       </c>
-      <c r="L2" s="9">
+      <c r="L2" s="12">
         <v>-6.11</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="1">
         <v>-6.87</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="5">
         <v>-8.3</v>
       </c>
-      <c r="O2" s="7">
+      <c r="O2" s="6">
         <v>-8.78</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="8">
         <v>-12.21</v>
       </c>
-      <c r="Q2" s="8">
+      <c r="Q2" s="7">
         <v>-13.17</v>
       </c>
-      <c r="R2" s="11">
+      <c r="R2" s="2">
         <v>-14.03</v>
       </c>
-      <c r="S2" s="13">
+      <c r="S2" s="9">
         <v>-13.84</v>
       </c>
-      <c r="T2" s="3">
-        <v>-31.39</v>
+      <c r="T2" s="10">
+        <v>-32.92</v>
       </c>
     </row>
     <row r="3">
@@ -7704,7 +7816,7 @@
       <c r="C3" t="str">
         <v>002238</v>
       </c>
-      <c r="D3" s="23" t="str">
+      <c r="D3" s="18" t="str">
         <v>净卖: -1634.66万</v>
       </c>
       <c r="E3">
@@ -7719,41 +7831,41 @@
       <c r="H3">
         <v>-0.54</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="23">
         <v>-9.45</v>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="24">
         <v>-6.36</v>
       </c>
-      <c r="K3" s="17">
+      <c r="K3" s="20">
         <v>-10.55</v>
       </c>
-      <c r="L3" s="24">
+      <c r="L3" s="25">
         <v>-11.27</v>
       </c>
-      <c r="M3" s="25">
+      <c r="M3" s="21">
         <v>-12.64</v>
       </c>
-      <c r="N3" s="26">
+      <c r="N3" s="15">
         <v>-13.09</v>
       </c>
-      <c r="O3" s="20">
+      <c r="O3" s="16">
         <v>-16.36</v>
       </c>
-      <c r="P3" s="14">
+      <c r="P3" s="19">
         <v>-17.27</v>
       </c>
       <c r="Q3" s="22">
         <v>-18.09</v>
       </c>
-      <c r="R3" s="15">
+      <c r="R3" s="26">
         <v>-17.91</v>
       </c>
-      <c r="S3" s="18">
+      <c r="S3" s="14">
         <v>-17.55</v>
       </c>
-      <c r="T3" s="21">
-        <v>-34.64</v>
+      <c r="T3" s="17">
+        <v>-36.09</v>
       </c>
     </row>
     <row r="4">
@@ -7781,41 +7893,41 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="37">
         <v>10.08</v>
       </c>
-      <c r="J4" s="36">
+      <c r="J4" s="28">
         <v>21.19</v>
       </c>
-      <c r="K4" s="29">
+      <c r="K4" s="36">
         <v>33.33</v>
       </c>
-      <c r="L4" s="30">
+      <c r="L4" s="29">
         <v>46.77</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="30">
         <v>61.5</v>
       </c>
-      <c r="N4" s="37">
+      <c r="N4" s="31">
         <v>45.48</v>
       </c>
-      <c r="O4" s="38">
+      <c r="O4" s="32">
         <v>53.23</v>
       </c>
-      <c r="P4" s="35">
+      <c r="P4" s="33">
         <v>58.66</v>
       </c>
-      <c r="Q4" s="32">
+      <c r="Q4" s="38">
         <v>51.94</v>
       </c>
-      <c r="R4" s="39">
+      <c r="R4" s="35">
         <v>36.69</v>
       </c>
-      <c r="S4" s="33">
+      <c r="S4" s="34">
         <v>23</v>
       </c>
-      <c r="T4" s="34">
-        <v>25.06</v>
+      <c r="T4" s="39">
+        <v>24.55</v>
       </c>
     </row>
     <row r="5">
@@ -7828,7 +7940,7 @@
       <c r="C5" t="str">
         <v>002041</v>
       </c>
-      <c r="D5" s="49" t="str">
+      <c r="D5" s="43" t="str">
         <v>净卖: -388.51万</v>
       </c>
       <c r="E5">
@@ -7843,41 +7955,41 @@
       <c r="H5">
         <v>4.75</v>
       </c>
-      <c r="I5" s="46">
+      <c r="I5" s="49">
         <v>4.91</v>
       </c>
-      <c r="J5" s="42">
+      <c r="J5" s="50">
         <v>15.37</v>
       </c>
-      <c r="K5" s="47">
+      <c r="K5" s="44">
         <v>10.56</v>
       </c>
-      <c r="L5" s="50">
+      <c r="L5" s="45">
         <v>11.76</v>
       </c>
-      <c r="M5" s="43">
+      <c r="M5" s="51">
         <v>4.07</v>
       </c>
-      <c r="N5" s="44">
+      <c r="N5" s="52">
         <v>5.09</v>
       </c>
-      <c r="O5" s="48">
+      <c r="O5" s="46">
         <v>2.87</v>
       </c>
-      <c r="P5" s="45">
+      <c r="P5" s="42">
         <v>0.56</v>
       </c>
-      <c r="Q5" s="41">
+      <c r="Q5" s="47">
         <v>0.19</v>
       </c>
-      <c r="R5" s="51">
+      <c r="R5" s="48">
         <v>-3.15</v>
       </c>
-      <c r="S5" s="52">
+      <c r="S5" s="40">
         <v>-2.31</v>
       </c>
-      <c r="T5" s="40">
-        <v>-5.46</v>
+      <c r="T5" s="41">
+        <v>-8.7</v>
       </c>
     </row>
     <row r="6">
@@ -7905,41 +8017,41 @@
       <c r="H6">
         <v>9.99</v>
       </c>
-      <c r="I6" s="60">
+      <c r="I6" s="64">
         <v>0</v>
       </c>
-      <c r="J6" s="64">
+      <c r="J6" s="65">
         <v>-9.94</v>
       </c>
       <c r="K6" s="56">
         <v>-12.52</v>
       </c>
-      <c r="L6" s="61">
+      <c r="L6" s="53">
         <v>-3.79</v>
       </c>
-      <c r="M6" s="62">
+      <c r="M6" s="60">
         <v>-1.89</v>
       </c>
-      <c r="N6" s="54">
+      <c r="N6" s="57">
         <v>-5.64</v>
       </c>
-      <c r="O6" s="65">
+      <c r="O6" s="61">
         <v>-7.27</v>
       </c>
-      <c r="P6" s="53">
+      <c r="P6" s="58">
         <v>-8.13</v>
       </c>
-      <c r="Q6" s="57">
+      <c r="Q6" s="59">
         <v>-8.91</v>
       </c>
-      <c r="R6" s="58">
+      <c r="R6" s="54">
         <v>-8.61</v>
       </c>
-      <c r="S6" s="63">
+      <c r="S6" s="62">
         <v>-5.85</v>
       </c>
-      <c r="T6" s="59">
-        <v>26.46</v>
+      <c r="T6" s="63">
+        <v>22.12</v>
       </c>
     </row>
     <row r="7">
@@ -7952,7 +8064,7 @@
       <c r="C7" t="str">
         <v>603516</v>
       </c>
-      <c r="D7" s="70" t="str">
+      <c r="D7" s="69" t="str">
         <v>净买: 374.25万</v>
       </c>
       <c r="E7">
@@ -7967,41 +8079,41 @@
       <c r="H7">
         <v>-10.01</v>
       </c>
-      <c r="I7" s="74">
+      <c r="I7" s="73">
         <v>0</v>
       </c>
-      <c r="J7" s="77">
+      <c r="J7" s="66">
         <v>4.02</v>
       </c>
-      <c r="K7" s="71">
+      <c r="K7" s="70">
         <v>2.06</v>
       </c>
-      <c r="L7" s="78">
+      <c r="L7" s="76">
         <v>3.75</v>
       </c>
-      <c r="M7" s="75">
+      <c r="M7" s="67">
         <v>7.52</v>
       </c>
-      <c r="N7" s="66">
+      <c r="N7" s="71">
         <v>6.86</v>
       </c>
-      <c r="O7" s="67">
+      <c r="O7" s="68">
         <v>11.67</v>
       </c>
-      <c r="P7" s="72">
+      <c r="P7" s="74">
         <v>9.4</v>
       </c>
-      <c r="Q7" s="68">
+      <c r="Q7" s="77">
         <v>11.63</v>
       </c>
-      <c r="R7" s="73">
+      <c r="R7" s="72">
         <v>11.12</v>
       </c>
-      <c r="S7" s="69">
+      <c r="S7" s="78">
         <v>9.79</v>
       </c>
-      <c r="T7" s="76">
-        <v>344.24</v>
+      <c r="T7" s="75">
+        <v>341.4</v>
       </c>
     </row>
     <row r="8">
@@ -8014,7 +8126,7 @@
       <c r="C8" t="str">
         <v>002510</v>
       </c>
-      <c r="D8" s="85" t="str">
+      <c r="D8" s="80" t="str">
         <v>净卖: -764.76万</v>
       </c>
       <c r="E8">
@@ -8032,38 +8144,38 @@
       <c r="I8" s="79">
         <v>0</v>
       </c>
-      <c r="J8" s="86">
+      <c r="J8" s="89">
         <v>10</v>
       </c>
-      <c r="K8" s="89">
+      <c r="K8" s="81">
         <v>21</v>
       </c>
-      <c r="L8" s="80">
+      <c r="L8" s="85">
         <v>17.57</v>
       </c>
-      <c r="M8" s="87">
+      <c r="M8" s="86">
         <v>5.86</v>
       </c>
-      <c r="N8" s="81">
+      <c r="N8" s="82">
         <v>1.57</v>
       </c>
-      <c r="O8" s="83">
+      <c r="O8" s="90">
         <v>3.57</v>
       </c>
-      <c r="P8" s="90">
+      <c r="P8" s="83">
         <v>1.14</v>
       </c>
-      <c r="Q8" s="84">
+      <c r="Q8" s="87">
         <v>1.14</v>
       </c>
-      <c r="R8" s="82">
+      <c r="R8" s="91">
         <v>-4.57</v>
       </c>
-      <c r="S8" s="91">
+      <c r="S8" s="84">
         <v>-2.71</v>
       </c>
       <c r="T8" s="88">
-        <v>-1.29</v>
+        <v>-3.29</v>
       </c>
     </row>
     <row r="9">
@@ -8076,7 +8188,7 @@
       <c r="C9" t="str">
         <v>600367</v>
       </c>
-      <c r="D9" s="101" t="str">
+      <c r="D9" s="95" t="str">
         <v>净买: 3583.76万</v>
       </c>
       <c r="E9">
@@ -8091,41 +8203,41 @@
       <c r="H9">
         <v>4.52</v>
       </c>
-      <c r="I9" s="102">
+      <c r="I9" s="96">
         <v>-0.98</v>
       </c>
       <c r="J9" s="93">
         <v>-4.07</v>
       </c>
-      <c r="K9" s="92">
+      <c r="K9" s="97">
         <v>-0.39</v>
       </c>
-      <c r="L9" s="94">
+      <c r="L9" s="98">
         <v>5.44</v>
       </c>
-      <c r="M9" s="95">
+      <c r="M9" s="104">
         <v>5.18</v>
       </c>
-      <c r="N9" s="103">
+      <c r="N9" s="99">
         <v>12.52</v>
       </c>
-      <c r="O9" s="96">
+      <c r="O9" s="100">
         <v>1.25</v>
       </c>
-      <c r="P9" s="98">
+      <c r="P9" s="102">
         <v>11.34</v>
       </c>
-      <c r="Q9" s="99">
+      <c r="Q9" s="101">
         <v>4.07</v>
       </c>
-      <c r="R9" s="97">
+      <c r="R9" s="92">
         <v>0.26</v>
       </c>
-      <c r="S9" s="104">
+      <c r="S9" s="103">
         <v>2.89</v>
       </c>
-      <c r="T9" s="100">
-        <v>48.2</v>
+      <c r="T9" s="94">
+        <v>48.66</v>
       </c>
     </row>
     <row r="10">
@@ -8138,7 +8250,7 @@
       <c r="C10" t="str">
         <v>603585</v>
       </c>
-      <c r="D10" s="105" t="str">
+      <c r="D10" s="107" t="str">
         <v>净买: 620.83万</v>
       </c>
       <c r="E10">
@@ -8153,41 +8265,41 @@
       <c r="H10">
         <v>-7.49</v>
       </c>
-      <c r="I10" s="115">
+      <c r="I10" s="113">
         <v>-2.7</v>
       </c>
-      <c r="J10" s="116">
+      <c r="J10" s="114">
         <v>-7</v>
       </c>
-      <c r="K10" s="106">
+      <c r="K10" s="108">
         <v>-4.8</v>
       </c>
-      <c r="L10" s="112">
+      <c r="L10" s="117">
         <v>-5.45</v>
       </c>
-      <c r="M10" s="110">
+      <c r="M10" s="105">
         <v>-7.65</v>
       </c>
-      <c r="N10" s="113">
+      <c r="N10" s="106">
         <v>-8.8</v>
       </c>
-      <c r="O10" s="107">
+      <c r="O10" s="112">
         <v>-8.55</v>
       </c>
-      <c r="P10" s="108">
+      <c r="P10" s="109">
         <v>-7.55</v>
       </c>
-      <c r="Q10" s="114">
+      <c r="Q10" s="110">
         <v>-1.95</v>
       </c>
-      <c r="R10" s="111">
+      <c r="R10" s="115">
         <v>-3.1</v>
       </c>
-      <c r="S10" s="109">
+      <c r="S10" s="116">
         <v>6.6</v>
       </c>
-      <c r="T10" s="117">
-        <v>16.65</v>
+      <c r="T10" s="111">
+        <v>0.15</v>
       </c>
     </row>
     <row r="11">
@@ -8200,7 +8312,7 @@
       <c r="C11" t="str">
         <v>600962</v>
       </c>
-      <c r="D11" s="124" t="str">
+      <c r="D11" s="128" t="str">
         <v>净卖: -17.88万</v>
       </c>
       <c r="E11">
@@ -8218,38 +8330,38 @@
       <c r="I11" s="118">
         <v>0</v>
       </c>
-      <c r="J11" s="123">
+      <c r="J11" s="120">
         <v>10.01</v>
       </c>
-      <c r="K11" s="121">
+      <c r="K11" s="125">
         <v>21.03</v>
       </c>
-      <c r="L11" s="125">
+      <c r="L11" s="126">
         <v>19.13</v>
       </c>
-      <c r="M11" s="126">
+      <c r="M11" s="119">
         <v>9.62</v>
       </c>
-      <c r="N11" s="127">
+      <c r="N11" s="121">
         <v>16.33</v>
       </c>
-      <c r="O11" s="119">
+      <c r="O11" s="122">
         <v>18.74</v>
       </c>
-      <c r="P11" s="128">
+      <c r="P11" s="127">
         <v>18.01</v>
       </c>
-      <c r="Q11" s="120">
+      <c r="Q11" s="129">
         <v>14.09</v>
       </c>
-      <c r="R11" s="122">
+      <c r="R11" s="130">
         <v>10.91</v>
       </c>
-      <c r="S11" s="129">
+      <c r="S11" s="123">
         <v>10.29</v>
       </c>
-      <c r="T11" s="130">
-        <v>20.97</v>
+      <c r="T11" s="124">
+        <v>16.5</v>
       </c>
     </row>
     <row r="12">
@@ -8262,7 +8374,7 @@
       <c r="C12" t="str">
         <v>003037</v>
       </c>
-      <c r="D12" s="137" t="str">
+      <c r="D12" s="139" t="str">
         <v>净卖: -2233.11万</v>
       </c>
       <c r="E12">
@@ -8277,41 +8389,41 @@
       <c r="H12">
         <v>4.89</v>
       </c>
-      <c r="I12" s="141">
+      <c r="I12" s="140">
         <v>4.88</v>
       </c>
-      <c r="J12" s="142">
+      <c r="J12" s="132">
         <v>8.77</v>
       </c>
-      <c r="K12" s="143">
+      <c r="K12" s="133">
         <v>-1.89</v>
       </c>
-      <c r="L12" s="138">
+      <c r="L12" s="143">
         <v>-3.22</v>
       </c>
-      <c r="M12" s="131">
+      <c r="M12" s="141">
         <v>6.44</v>
       </c>
-      <c r="N12" s="139">
+      <c r="N12" s="137">
         <v>17.09</v>
       </c>
-      <c r="O12" s="132">
+      <c r="O12" s="142">
         <v>16.09</v>
       </c>
-      <c r="P12" s="133">
+      <c r="P12" s="134">
         <v>14.32</v>
       </c>
-      <c r="Q12" s="134">
+      <c r="Q12" s="135">
         <v>4.88</v>
       </c>
-      <c r="R12" s="135">
+      <c r="R12" s="138">
         <v>3.77</v>
       </c>
-      <c r="S12" s="136">
+      <c r="S12" s="131">
         <v>4</v>
       </c>
-      <c r="T12" s="140">
-        <v>-20.31</v>
+      <c r="T12" s="136">
+        <v>-21.75</v>
       </c>
     </row>
     <row r="13">
@@ -8324,7 +8436,7 @@
       <c r="C13" t="str">
         <v>001306</v>
       </c>
-      <c r="D13" s="153" t="str">
+      <c r="D13" s="155" t="str">
         <v>净卖: -462.25万</v>
       </c>
       <c r="E13">
@@ -8339,13 +8451,13 @@
       <c r="H13">
         <v>0.03</v>
       </c>
-      <c r="I13" s="145">
+      <c r="I13" s="156">
         <v>6.62</v>
       </c>
-      <c r="J13" s="154">
+      <c r="J13" s="145">
         <v>17.29</v>
       </c>
-      <c r="K13" s="155">
+      <c r="K13" s="149">
         <v>22.79</v>
       </c>
       <c r="L13" s="146">
@@ -8354,26 +8466,26 @@
       <c r="M13" s="147">
         <v>23.18</v>
       </c>
-      <c r="N13" s="148">
+      <c r="N13" s="150">
         <v>22.64</v>
       </c>
-      <c r="O13" s="149">
+      <c r="O13" s="148">
         <v>27.89</v>
       </c>
-      <c r="P13" s="152">
+      <c r="P13" s="144">
         <v>23.34</v>
       </c>
-      <c r="Q13" s="150">
+      <c r="Q13" s="151">
         <v>24.33</v>
       </c>
-      <c r="R13" s="151">
+      <c r="R13" s="152">
         <v>22.68</v>
       </c>
-      <c r="S13" s="156">
+      <c r="S13" s="153">
         <v>28.62</v>
       </c>
-      <c r="T13" s="144">
-        <v>-10.37</v>
+      <c r="T13" s="154">
+        <v>-13.1</v>
       </c>
     </row>
     <row r="14">
@@ -8386,7 +8498,7 @@
       <c r="C14" t="str">
         <v>002953</v>
       </c>
-      <c r="D14" s="164" t="str">
+      <c r="D14" s="167" t="str">
         <v>净卖: -867.00万</v>
       </c>
       <c r="E14">
@@ -8401,41 +8513,41 @@
       <c r="H14">
         <v>-2.07</v>
       </c>
-      <c r="I14" s="157">
+      <c r="I14" s="168">
         <v>12.29</v>
       </c>
-      <c r="J14" s="165">
+      <c r="J14" s="160">
         <v>17.19</v>
       </c>
-      <c r="K14" s="166">
+      <c r="K14" s="165">
         <v>10.41</v>
       </c>
-      <c r="L14" s="160">
+      <c r="L14" s="169">
         <v>21.42</v>
       </c>
-      <c r="M14" s="167">
+      <c r="M14" s="161">
         <v>15.91</v>
       </c>
-      <c r="N14" s="168">
+      <c r="N14" s="162">
         <v>4.3</v>
       </c>
-      <c r="O14" s="161">
+      <c r="O14" s="163">
         <v>-1.96</v>
       </c>
-      <c r="P14" s="158">
+      <c r="P14" s="164">
         <v>-1.06</v>
       </c>
-      <c r="Q14" s="159">
+      <c r="Q14" s="166">
         <v>-0.75</v>
       </c>
-      <c r="R14" s="162">
+      <c r="R14" s="157">
         <v>-0.98</v>
       </c>
-      <c r="S14" s="169">
+      <c r="S14" s="158">
         <v>-4.68</v>
       </c>
-      <c r="T14" s="163">
-        <v>-7.47</v>
+      <c r="T14" s="159">
+        <v>-10.26</v>
       </c>
     </row>
     <row r="15">
@@ -8448,7 +8560,7 @@
       <c r="C15" t="str">
         <v>605133</v>
       </c>
-      <c r="D15" s="182" t="str">
+      <c r="D15" s="178" t="str">
         <v>净买: 3043.68万</v>
       </c>
       <c r="E15">
@@ -8469,35 +8581,35 @@
       <c r="J15" s="171">
         <v>6.15</v>
       </c>
-      <c r="K15" s="181">
+      <c r="K15" s="172">
         <v>-4.46</v>
       </c>
-      <c r="L15" s="176">
+      <c r="L15" s="175">
         <v>-0.27</v>
       </c>
-      <c r="M15" s="177">
+      <c r="M15" s="179">
         <v>3.14</v>
       </c>
-      <c r="N15" s="178">
+      <c r="N15" s="176">
         <v>1.53</v>
       </c>
-      <c r="O15" s="179">
+      <c r="O15" s="177">
         <v>-1.62</v>
       </c>
-      <c r="P15" s="180">
+      <c r="P15" s="173">
         <v>-0.46</v>
       </c>
-      <c r="Q15" s="172">
+      <c r="Q15" s="180">
         <v>-2.94</v>
       </c>
-      <c r="R15" s="173">
+      <c r="R15" s="181">
         <v>-0.55</v>
       </c>
-      <c r="S15" s="174">
+      <c r="S15" s="182">
         <v>9.41</v>
       </c>
-      <c r="T15" s="175">
-        <v>-25.31</v>
+      <c r="T15" s="174">
+        <v>-28</v>
       </c>
     </row>
     <row r="16">
@@ -8510,7 +8622,7 @@
       <c r="C16" t="str">
         <v>301533</v>
       </c>
-      <c r="D16" s="190" t="str">
+      <c r="D16" s="195" t="str">
         <v>净卖: -733.04万</v>
       </c>
       <c r="E16">
@@ -8525,41 +8637,41 @@
       <c r="H16">
         <v>2.26</v>
       </c>
-      <c r="I16" s="188">
+      <c r="I16" s="193">
         <v>3.46</v>
       </c>
-      <c r="J16" s="195">
+      <c r="J16" s="188">
         <v>8.33</v>
       </c>
-      <c r="K16" s="183">
+      <c r="K16" s="189">
         <v>10.64</v>
       </c>
-      <c r="L16" s="191">
+      <c r="L16" s="185">
         <v>7.14</v>
       </c>
-      <c r="M16" s="186">
+      <c r="M16" s="190">
         <v>11.64</v>
       </c>
-      <c r="N16" s="184">
+      <c r="N16" s="191">
         <v>6.19</v>
       </c>
-      <c r="O16" s="192">
+      <c r="O16" s="183">
         <v>3.76</v>
       </c>
-      <c r="P16" s="185">
+      <c r="P16" s="184">
         <v>0.97</v>
       </c>
-      <c r="Q16" s="193">
+      <c r="Q16" s="194">
         <v>-1.04</v>
       </c>
-      <c r="R16" s="194">
+      <c r="R16" s="192">
         <v>-2.01</v>
       </c>
-      <c r="S16" s="189">
+      <c r="S16" s="186">
         <v>-5.7</v>
       </c>
       <c r="T16" s="187">
-        <v>-19.22</v>
+        <v>-19.92</v>
       </c>
     </row>
     <row r="17">
@@ -8572,7 +8684,7 @@
       <c r="C17" t="str">
         <v>688148</v>
       </c>
-      <c r="D17" s="206" t="str">
+      <c r="D17" s="207" t="str">
         <v>净卖: -1051.47万</v>
       </c>
       <c r="E17">
@@ -8587,41 +8699,41 @@
       <c r="H17">
         <v>4.34</v>
       </c>
-      <c r="I17" s="197">
+      <c r="I17" s="199">
         <v>15.03</v>
       </c>
-      <c r="J17" s="207">
+      <c r="J17" s="204">
         <v>37.63</v>
       </c>
-      <c r="K17" s="203">
+      <c r="K17" s="208">
         <v>33.37</v>
       </c>
-      <c r="L17" s="198">
+      <c r="L17" s="200">
         <v>33.9</v>
       </c>
-      <c r="M17" s="204">
+      <c r="M17" s="205">
         <v>29</v>
       </c>
-      <c r="N17" s="200">
+      <c r="N17" s="201">
         <v>24.95</v>
       </c>
-      <c r="O17" s="201">
+      <c r="O17" s="202">
         <v>20.36</v>
       </c>
-      <c r="P17" s="208">
+      <c r="P17" s="196">
         <v>18.44</v>
       </c>
-      <c r="Q17" s="199">
+      <c r="Q17" s="203">
         <v>13.11</v>
       </c>
-      <c r="R17" s="196">
+      <c r="R17" s="197">
         <v>1.49</v>
       </c>
-      <c r="S17" s="205">
+      <c r="S17" s="206">
         <v>-1.39</v>
       </c>
-      <c r="T17" s="202">
-        <v>1.81</v>
+      <c r="T17" s="198">
+        <v>9.28</v>
       </c>
     </row>
     <row r="18">
@@ -8649,41 +8761,41 @@
       <c r="H18">
         <v>5.56</v>
       </c>
-      <c r="I18" s="210">
+      <c r="I18" s="216">
         <v>13.35</v>
       </c>
-      <c r="J18" s="215">
+      <c r="J18" s="219">
         <v>9.83</v>
       </c>
-      <c r="K18" s="216">
+      <c r="K18" s="220">
         <v>10.27</v>
       </c>
-      <c r="L18" s="211">
+      <c r="L18" s="210">
         <v>6.23</v>
       </c>
-      <c r="M18" s="219">
+      <c r="M18" s="211">
         <v>2.9</v>
       </c>
-      <c r="N18" s="217">
+      <c r="N18" s="221">
         <v>-0.88</v>
       </c>
-      <c r="O18" s="220">
+      <c r="O18" s="212">
         <v>-2.46</v>
       </c>
-      <c r="P18" s="212">
+      <c r="P18" s="217">
         <v>-6.85</v>
       </c>
       <c r="Q18" s="213">
         <v>-16.42</v>
       </c>
-      <c r="R18" s="221">
+      <c r="R18" s="214">
         <v>-18.79</v>
       </c>
-      <c r="S18" s="218">
+      <c r="S18" s="215">
         <v>-16.86</v>
       </c>
-      <c r="T18" s="214">
-        <v>-16.15</v>
+      <c r="T18" s="218">
+        <v>-10.01</v>
       </c>
     </row>
     <row r="19">
@@ -8696,7 +8808,7 @@
       <c r="C19" t="str">
         <v>002506</v>
       </c>
-      <c r="D19" s="228" t="str">
+      <c r="D19" s="224" t="str">
         <v>净卖: -1046.77万</v>
       </c>
       <c r="E19">
@@ -8711,41 +8823,41 @@
       <c r="H19">
         <v>1.86</v>
       </c>
-      <c r="I19" s="229">
+      <c r="I19" s="234">
         <v>8.03</v>
       </c>
-      <c r="J19" s="234">
+      <c r="J19" s="222">
         <v>14.23</v>
       </c>
-      <c r="K19" s="230">
+      <c r="K19" s="227">
         <v>15.69</v>
       </c>
-      <c r="L19" s="224">
+      <c r="L19" s="228">
         <v>17.52</v>
       </c>
-      <c r="M19" s="225">
+      <c r="M19" s="230">
         <v>14.6</v>
       </c>
-      <c r="N19" s="232">
+      <c r="N19" s="225">
         <v>8.39</v>
       </c>
-      <c r="O19" s="226">
+      <c r="O19" s="231">
         <v>4.74</v>
       </c>
-      <c r="P19" s="222">
+      <c r="P19" s="226">
         <v>1.46</v>
       </c>
-      <c r="Q19" s="227">
+      <c r="Q19" s="223">
         <v>-6.93</v>
       </c>
-      <c r="R19" s="223">
+      <c r="R19" s="229">
         <v>-7.3</v>
       </c>
-      <c r="S19" s="231">
+      <c r="S19" s="232">
         <v>-6.57</v>
       </c>
       <c r="T19" s="233">
-        <v>78.1</v>
+        <v>59.12</v>
       </c>
     </row>
     <row r="20">
@@ -8758,7 +8870,7 @@
       <c r="C20" t="str">
         <v>603778</v>
       </c>
-      <c r="D20" s="246" t="str">
+      <c r="D20" s="240" t="str">
         <v>净卖: -3366.51万</v>
       </c>
       <c r="E20">
@@ -8773,41 +8885,41 @@
       <c r="H20">
         <v>6.69</v>
       </c>
-      <c r="I20" s="247">
+      <c r="I20" s="235">
         <v>3.07</v>
       </c>
-      <c r="J20" s="237">
+      <c r="J20" s="241">
         <v>13.33</v>
       </c>
-      <c r="K20" s="235">
+      <c r="K20" s="236">
         <v>5.33</v>
       </c>
-      <c r="L20" s="238">
+      <c r="L20" s="242">
         <v>8.67</v>
       </c>
-      <c r="M20" s="243">
+      <c r="M20" s="237">
         <v>19.6</v>
       </c>
-      <c r="N20" s="245">
+      <c r="N20" s="243">
         <v>7.6</v>
       </c>
-      <c r="O20" s="239">
+      <c r="O20" s="245">
         <v>-2</v>
       </c>
-      <c r="P20" s="244">
+      <c r="P20" s="246">
         <v>7.87</v>
       </c>
-      <c r="Q20" s="236">
+      <c r="Q20" s="247">
         <v>18.67</v>
       </c>
-      <c r="R20" s="240">
+      <c r="R20" s="238">
         <v>27.73</v>
       </c>
-      <c r="S20" s="241">
+      <c r="S20" s="244">
         <v>40.53</v>
       </c>
-      <c r="T20" s="242">
-        <v>286.67</v>
+      <c r="T20" s="239">
+        <v>253.73</v>
       </c>
     </row>
     <row r="21">
@@ -8820,7 +8932,7 @@
       <c r="C21" t="str">
         <v>600252</v>
       </c>
-      <c r="D21" s="251" t="str">
+      <c r="D21" s="258" t="str">
         <v>净卖: -331.54万</v>
       </c>
       <c r="E21">
@@ -8835,41 +8947,41 @@
       <c r="H21">
         <v>0.37</v>
       </c>
-      <c r="I21" s="252">
+      <c r="I21" s="251">
         <v>9.67</v>
       </c>
-      <c r="J21" s="253">
+      <c r="J21" s="259">
         <v>6.32</v>
       </c>
-      <c r="K21" s="254">
+      <c r="K21" s="260">
         <v>7.81</v>
       </c>
-      <c r="L21" s="255">
+      <c r="L21" s="252">
         <v>10.41</v>
       </c>
-      <c r="M21" s="259">
+      <c r="M21" s="253">
         <v>9.29</v>
       </c>
       <c r="N21" s="256">
         <v>11.9</v>
       </c>
-      <c r="O21" s="257">
+      <c r="O21" s="254">
         <v>10.78</v>
       </c>
-      <c r="P21" s="258">
+      <c r="P21" s="248">
         <v>11.52</v>
       </c>
-      <c r="Q21" s="260">
+      <c r="Q21" s="249">
         <v>10.04</v>
       </c>
-      <c r="R21" s="248">
+      <c r="R21" s="250">
         <v>6.32</v>
       </c>
-      <c r="S21" s="249">
+      <c r="S21" s="257">
         <v>5.58</v>
       </c>
-      <c r="T21" s="250">
-        <v>-7.43</v>
+      <c r="T21" s="255">
+        <v>-7.81</v>
       </c>
     </row>
     <row r="22">
@@ -8882,7 +8994,7 @@
       <c r="C22" t="str">
         <v>003018</v>
       </c>
-      <c r="D22" s="273" t="str">
+      <c r="D22" s="266" t="str">
         <v>净卖: -1172.31万</v>
       </c>
       <c r="E22">
@@ -8897,41 +9009,41 @@
       <c r="H22">
         <v>10.01</v>
       </c>
-      <c r="I22" s="266">
+      <c r="I22" s="267">
         <v>0</v>
       </c>
-      <c r="J22" s="267">
+      <c r="J22" s="268">
         <v>-9.99</v>
       </c>
-      <c r="K22" s="268">
+      <c r="K22" s="273">
         <v>-18.85</v>
       </c>
-      <c r="L22" s="270">
+      <c r="L22" s="269">
         <v>-18.77</v>
       </c>
-      <c r="M22" s="261">
+      <c r="M22" s="263">
         <v>-15.14</v>
       </c>
-      <c r="N22" s="269">
+      <c r="N22" s="272">
         <v>-23.48</v>
       </c>
-      <c r="O22" s="265">
+      <c r="O22" s="270">
         <v>-18.81</v>
       </c>
-      <c r="P22" s="262">
+      <c r="P22" s="261">
         <v>-22.71</v>
       </c>
-      <c r="Q22" s="263">
+      <c r="Q22" s="264">
         <v>-25.49</v>
       </c>
-      <c r="R22" s="264">
+      <c r="R22" s="262">
         <v>-25.49</v>
       </c>
       <c r="S22" s="271">
         <v>-29.4</v>
       </c>
-      <c r="T22" s="272">
-        <v>91.1</v>
+      <c r="T22" s="265">
+        <v>130.69</v>
       </c>
     </row>
     <row r="23">
@@ -8944,7 +9056,7 @@
       <c r="C23" t="str">
         <v>603958</v>
       </c>
-      <c r="D23" s="285" t="str">
+      <c r="D23" s="277" t="str">
         <v>净买: 48.48万</v>
       </c>
       <c r="E23">
@@ -8959,41 +9071,41 @@
       <c r="H23">
         <v>-5.98</v>
       </c>
-      <c r="I23" s="286">
+      <c r="I23" s="274">
         <v>-4.29</v>
       </c>
-      <c r="J23" s="275">
+      <c r="J23" s="278">
         <v>-7.64</v>
       </c>
-      <c r="K23" s="276">
+      <c r="K23" s="284">
         <v>-8.21</v>
       </c>
-      <c r="L23" s="282">
+      <c r="L23" s="279">
         <v>-4.29</v>
       </c>
-      <c r="M23" s="279">
+      <c r="M23" s="280">
         <v>-7.5</v>
       </c>
-      <c r="N23" s="277">
+      <c r="N23" s="285">
         <v>-8.36</v>
       </c>
       <c r="O23" s="283">
         <v>-10.57</v>
       </c>
-      <c r="P23" s="274">
+      <c r="P23" s="275">
         <v>-8.86</v>
       </c>
-      <c r="Q23" s="280">
+      <c r="Q23" s="281">
         <v>-7.43</v>
       </c>
-      <c r="R23" s="278">
+      <c r="R23" s="276">
         <v>-8</v>
       </c>
-      <c r="S23" s="281">
+      <c r="S23" s="286">
         <v>-8.71</v>
       </c>
-      <c r="T23" s="284">
-        <v>90.21</v>
+      <c r="T23" s="282">
+        <v>77.36</v>
       </c>
     </row>
     <row r="24">
@@ -9006,7 +9118,7 @@
       <c r="C24" t="str">
         <v>002187</v>
       </c>
-      <c r="D24" s="295" t="str">
+      <c r="D24" s="296" t="str">
         <v>净卖: -1062.98万</v>
       </c>
       <c r="E24">
@@ -9021,41 +9133,41 @@
       <c r="H24">
         <v>2</v>
       </c>
-      <c r="I24" s="292">
+      <c r="I24" s="297">
         <v>7.83</v>
       </c>
-      <c r="J24" s="296">
+      <c r="J24" s="299">
         <v>3.92</v>
       </c>
-      <c r="K24" s="299">
+      <c r="K24" s="294">
         <v>3.26</v>
       </c>
-      <c r="L24" s="287">
+      <c r="L24" s="298">
         <v>7.57</v>
       </c>
-      <c r="M24" s="288">
+      <c r="M24" s="295">
         <v>10.05</v>
       </c>
-      <c r="N24" s="293">
+      <c r="N24" s="287">
         <v>8.88</v>
       </c>
-      <c r="O24" s="297">
+      <c r="O24" s="290">
         <v>4.96</v>
       </c>
-      <c r="P24" s="298">
+      <c r="P24" s="288">
         <v>7.83</v>
       </c>
       <c r="Q24" s="289">
         <v>6.4</v>
       </c>
-      <c r="R24" s="294">
+      <c r="R24" s="291">
         <v>17.1</v>
       </c>
-      <c r="S24" s="290">
+      <c r="S24" s="292">
         <v>5.61</v>
       </c>
-      <c r="T24" s="291">
-        <v>-19.19</v>
+      <c r="T24" s="293">
+        <v>-22.19</v>
       </c>
     </row>
     <row r="25">
@@ -9068,7 +9180,7 @@
       <c r="C25" t="str">
         <v>688273</v>
       </c>
-      <c r="D25" s="304" t="str">
+      <c r="D25" s="305" t="str">
         <v>净卖: -963.67万</v>
       </c>
       <c r="E25">
@@ -9083,41 +9195,41 @@
       <c r="H25">
         <v>-1.99</v>
       </c>
-      <c r="I25" s="305">
+      <c r="I25" s="308">
         <v>-8.57</v>
       </c>
-      <c r="J25" s="301">
+      <c r="J25" s="300">
         <v>-8.03</v>
       </c>
-      <c r="K25" s="300">
+      <c r="K25" s="306">
         <v>-11.27</v>
       </c>
-      <c r="L25" s="306">
+      <c r="L25" s="301">
         <v>-8.63</v>
       </c>
-      <c r="M25" s="307">
+      <c r="M25" s="309">
         <v>-13</v>
       </c>
-      <c r="N25" s="308">
+      <c r="N25" s="310">
         <v>-13.83</v>
       </c>
-      <c r="O25" s="302">
+      <c r="O25" s="307">
         <v>-17.22</v>
       </c>
-      <c r="P25" s="311">
+      <c r="P25" s="302">
         <v>-20.37</v>
       </c>
-      <c r="Q25" s="309">
+      <c r="Q25" s="304">
         <v>-20.43</v>
       </c>
-      <c r="R25" s="303">
+      <c r="R25" s="311">
         <v>-22.83</v>
       </c>
-      <c r="S25" s="310">
+      <c r="S25" s="312">
         <v>-23.42</v>
       </c>
-      <c r="T25" s="312">
-        <v>-19.88</v>
+      <c r="T25" s="303">
+        <v>-21.82</v>
       </c>
     </row>
     <row r="26">
@@ -9130,7 +9242,7 @@
       <c r="C26" t="str">
         <v>688523</v>
       </c>
-      <c r="D26" s="324" t="str">
+      <c r="D26" s="321" t="str">
         <v>净卖: -2032.96万</v>
       </c>
       <c r="E26">
@@ -9145,41 +9257,41 @@
       <c r="H26">
         <v>-6.9</v>
       </c>
-      <c r="I26" s="318">
+      <c r="I26" s="322">
         <v>-12.28</v>
       </c>
-      <c r="J26" s="325">
+      <c r="J26" s="323">
         <v>-15.94</v>
       </c>
-      <c r="K26" s="315">
+      <c r="K26" s="324">
         <v>-22.53</v>
       </c>
-      <c r="L26" s="322">
+      <c r="L26" s="325">
         <v>-23.98</v>
       </c>
-      <c r="M26" s="316">
+      <c r="M26" s="317">
         <v>-21.69</v>
       </c>
-      <c r="N26" s="313">
+      <c r="N26" s="314">
         <v>-28.64</v>
       </c>
-      <c r="O26" s="319">
+      <c r="O26" s="318">
         <v>-29.76</v>
       </c>
-      <c r="P26" s="320">
+      <c r="P26" s="315">
         <v>-23.74</v>
       </c>
-      <c r="Q26" s="323">
+      <c r="Q26" s="316">
         <v>-13.62</v>
       </c>
-      <c r="R26" s="321">
+      <c r="R26" s="319">
         <v>-23.24</v>
       </c>
-      <c r="S26" s="314">
+      <c r="S26" s="320">
         <v>-24.4</v>
       </c>
-      <c r="T26" s="317">
-        <v>-13.73</v>
+      <c r="T26" s="313">
+        <v>-22.08</v>
       </c>
     </row>
     <row r="27">
@@ -9192,7 +9304,7 @@
       <c r="C27" t="str">
         <v>002131</v>
       </c>
-      <c r="D27" s="328" t="str">
+      <c r="D27" s="338" t="str">
         <v>净买: 384.51万</v>
       </c>
       <c r="E27">
@@ -9207,41 +9319,41 @@
       <c r="H27">
         <v>-10</v>
       </c>
-      <c r="I27" s="338">
+      <c r="I27" s="337">
         <v>0</v>
       </c>
-      <c r="J27" s="326">
+      <c r="J27" s="335">
         <v>-10.04</v>
       </c>
-      <c r="K27" s="329">
+      <c r="K27" s="326">
         <v>-10.26</v>
       </c>
-      <c r="L27" s="330">
+      <c r="L27" s="332">
         <v>-14.53</v>
       </c>
-      <c r="M27" s="335">
+      <c r="M27" s="327">
         <v>-9.19</v>
       </c>
-      <c r="N27" s="327">
+      <c r="N27" s="328">
         <v>-6.3</v>
       </c>
-      <c r="O27" s="333">
+      <c r="O27" s="329">
         <v>2.24</v>
       </c>
-      <c r="P27" s="331">
+      <c r="P27" s="330">
         <v>-0.43</v>
       </c>
-      <c r="Q27" s="336">
+      <c r="Q27" s="333">
         <v>5.88</v>
       </c>
-      <c r="R27" s="337">
+      <c r="R27" s="331">
         <v>8.76</v>
       </c>
-      <c r="S27" s="332">
+      <c r="S27" s="334">
         <v>-1.07</v>
       </c>
-      <c r="T27" s="334">
-        <v>-14.42</v>
+      <c r="T27" s="336">
+        <v>-21.26</v>
       </c>
     </row>
     <row r="28">
@@ -9269,41 +9381,41 @@
       <c r="H28">
         <v>-1.78</v>
       </c>
-      <c r="I28" s="350">
+      <c r="I28" s="339">
         <v>-8.38</v>
       </c>
-      <c r="J28" s="347">
+      <c r="J28" s="343">
         <v>-9.03</v>
       </c>
-      <c r="K28" s="343">
+      <c r="K28" s="345">
         <v>-9.19</v>
       </c>
-      <c r="L28" s="351">
+      <c r="L28" s="344">
         <v>-8.54</v>
       </c>
       <c r="M28" s="348">
         <v>-7.3</v>
       </c>
-      <c r="N28" s="339">
+      <c r="N28" s="349">
         <v>-6.49</v>
       </c>
-      <c r="O28" s="349">
+      <c r="O28" s="350">
         <v>0.59</v>
       </c>
-      <c r="P28" s="344">
+      <c r="P28" s="351">
         <v>2.27</v>
       </c>
-      <c r="Q28" s="345">
+      <c r="Q28" s="340">
         <v>2.54</v>
       </c>
       <c r="R28" s="346">
         <v>4.92</v>
       </c>
-      <c r="S28" s="340">
+      <c r="S28" s="347">
         <v>10.54</v>
       </c>
       <c r="T28" s="341">
-        <v>24.89</v>
+        <v>9.46</v>
       </c>
     </row>
     <row r="29">
@@ -9316,7 +9428,7 @@
       <c r="C29" t="str">
         <v>603619</v>
       </c>
-      <c r="D29" s="353" t="str">
+      <c r="D29" s="356" t="str">
         <v>净买: 3411.20万</v>
       </c>
       <c r="E29">
@@ -9331,41 +9443,41 @@
       <c r="H29">
         <v>1.96</v>
       </c>
-      <c r="I29" s="354">
+      <c r="I29" s="357">
         <v>-8.71</v>
       </c>
-      <c r="J29" s="364">
+      <c r="J29" s="362">
         <v>-17.84</v>
       </c>
-      <c r="K29" s="355">
+      <c r="K29" s="364">
         <v>-20.82</v>
       </c>
-      <c r="L29" s="362">
+      <c r="L29" s="352">
         <v>-14.71</v>
       </c>
-      <c r="M29" s="363">
+      <c r="M29" s="358">
         <v>-18.76</v>
       </c>
-      <c r="N29" s="356">
+      <c r="N29" s="363">
         <v>-14.24</v>
       </c>
-      <c r="O29" s="357">
+      <c r="O29" s="353">
         <v>-16.47</v>
       </c>
-      <c r="P29" s="358">
+      <c r="P29" s="354">
         <v>-12.61</v>
       </c>
-      <c r="Q29" s="359">
+      <c r="Q29" s="355">
         <v>-7.45</v>
       </c>
-      <c r="R29" s="360">
+      <c r="R29" s="359">
         <v>-9.16</v>
       </c>
-      <c r="S29" s="361">
+      <c r="S29" s="360">
         <v>-12.42</v>
       </c>
-      <c r="T29" s="352">
-        <v>-14.97</v>
+      <c r="T29" s="361">
+        <v>-11.58</v>
       </c>
     </row>
     <row r="30">
@@ -9378,7 +9490,7 @@
       <c r="C30" t="str">
         <v>688530</v>
       </c>
-      <c r="D30" s="366" t="str">
+      <c r="D30" s="369" t="str">
         <v>净卖: -1311.39万</v>
       </c>
       <c r="E30">
@@ -9393,41 +9505,41 @@
       <c r="H30">
         <v>-2.23</v>
       </c>
-      <c r="I30" s="370">
+      <c r="I30" s="373">
         <v>15.5</v>
       </c>
-      <c r="J30" s="371">
+      <c r="J30" s="374">
         <v>11.55</v>
       </c>
-      <c r="K30" s="367">
+      <c r="K30" s="376">
         <v>20.14</v>
       </c>
       <c r="L30" s="377">
         <v>15.82</v>
       </c>
-      <c r="M30" s="368">
+      <c r="M30" s="365">
         <v>32.04</v>
       </c>
-      <c r="N30" s="375">
+      <c r="N30" s="370">
         <v>29.72</v>
       </c>
-      <c r="O30" s="365">
+      <c r="O30" s="366">
         <v>28.01</v>
       </c>
-      <c r="P30" s="372">
+      <c r="P30" s="368">
         <v>31.8</v>
       </c>
-      <c r="Q30" s="369">
+      <c r="Q30" s="367">
         <v>58.17</v>
       </c>
-      <c r="R30" s="373">
+      <c r="R30" s="371">
         <v>66.44</v>
       </c>
-      <c r="S30" s="374">
+      <c r="S30" s="375">
         <v>58.53</v>
       </c>
-      <c r="T30" s="376">
-        <v>39.79</v>
+      <c r="T30" s="372">
+        <v>53.82</v>
       </c>
     </row>
     <row r="31">
@@ -9440,7 +9552,7 @@
       <c r="C31" t="str">
         <v>688530</v>
       </c>
-      <c r="D31" s="379" t="str">
+      <c r="D31" s="388" t="str">
         <v>净卖: -4653.87万</v>
       </c>
       <c r="E31">
@@ -9455,41 +9567,41 @@
       <c r="H31">
         <v>-1.06</v>
       </c>
-      <c r="I31" s="380">
+      <c r="I31" s="383">
         <v>21.29</v>
       </c>
-      <c r="J31" s="385">
+      <c r="J31" s="380">
         <v>27.63</v>
       </c>
-      <c r="K31" s="387">
+      <c r="K31" s="389">
         <v>21.57</v>
       </c>
       <c r="L31" s="390">
         <v>13.14</v>
       </c>
-      <c r="M31" s="381">
+      <c r="M31" s="378">
         <v>8.21</v>
       </c>
-      <c r="N31" s="382">
+      <c r="N31" s="386">
         <v>6.59</v>
       </c>
-      <c r="O31" s="378">
+      <c r="O31" s="384">
         <v>1.78</v>
       </c>
-      <c r="P31" s="388">
+      <c r="P31" s="379">
         <v>0.09</v>
       </c>
-      <c r="Q31" s="386">
+      <c r="Q31" s="387">
         <v>6.43</v>
       </c>
-      <c r="R31" s="389">
+      <c r="R31" s="385">
         <v>1.5</v>
       </c>
-      <c r="S31" s="383">
+      <c r="S31" s="381">
         <v>5.55</v>
       </c>
-      <c r="T31" s="384">
-        <v>7.2</v>
+      <c r="T31" s="382">
+        <v>17.95</v>
       </c>
     </row>
     <row r="32">
@@ -9502,7 +9614,7 @@
       <c r="C32" t="str">
         <v>600367</v>
       </c>
-      <c r="D32" s="396" t="str">
+      <c r="D32" s="403" t="str">
         <v>净买: 7875.30万</v>
       </c>
       <c r="E32">
@@ -9517,41 +9629,41 @@
       <c r="H32">
         <v>6.88</v>
       </c>
-      <c r="I32" s="397">
+      <c r="I32" s="391">
         <v>2.94</v>
       </c>
-      <c r="J32" s="391">
+      <c r="J32" s="392">
         <v>-0.72</v>
       </c>
-      <c r="K32" s="393">
+      <c r="K32" s="401">
         <v>-2.86</v>
       </c>
-      <c r="L32" s="400">
+      <c r="L32" s="395">
         <v>-5.36</v>
       </c>
-      <c r="M32" s="394">
+      <c r="M32" s="396">
         <v>-7.83</v>
       </c>
-      <c r="N32" s="395">
+      <c r="N32" s="397">
         <v>-11.24</v>
       </c>
-      <c r="O32" s="401">
+      <c r="O32" s="398">
         <v>-9.85</v>
       </c>
-      <c r="P32" s="402">
+      <c r="P32" s="393">
         <v>-6.2</v>
       </c>
-      <c r="Q32" s="398">
+      <c r="Q32" s="399">
         <v>-1.47</v>
       </c>
-      <c r="R32" s="403">
+      <c r="R32" s="402">
         <v>6.52</v>
       </c>
-      <c r="S32" s="399">
+      <c r="S32" s="400">
         <v>13.79</v>
       </c>
-      <c r="T32" s="392">
-        <v>-10.21</v>
+      <c r="T32" s="394">
+        <v>-9.93</v>
       </c>
     </row>
     <row r="33">
@@ -9564,7 +9676,7 @@
       <c r="C33" t="str">
         <v>600516</v>
       </c>
-      <c r="D33" s="413" t="str">
+      <c r="D33" s="414" t="str">
         <v>净卖: -4735.13万</v>
       </c>
       <c r="E33">
@@ -9579,41 +9691,41 @@
       <c r="H33">
         <v>0.8</v>
       </c>
-      <c r="I33" s="404">
+      <c r="I33" s="415">
         <v>9.21</v>
       </c>
-      <c r="J33" s="410">
+      <c r="J33" s="408">
         <v>6.83</v>
       </c>
-      <c r="K33" s="416">
+      <c r="K33" s="412">
         <v>5.87</v>
       </c>
-      <c r="L33" s="411">
+      <c r="L33" s="409">
         <v>7.46</v>
       </c>
-      <c r="M33" s="405">
+      <c r="M33" s="416">
         <v>10.32</v>
       </c>
-      <c r="N33" s="414">
+      <c r="N33" s="413">
         <v>12.86</v>
       </c>
-      <c r="O33" s="406">
+      <c r="O33" s="410">
         <v>7.3</v>
       </c>
-      <c r="P33" s="407">
+      <c r="P33" s="411">
         <v>4.92</v>
       </c>
-      <c r="Q33" s="412">
+      <c r="Q33" s="404">
         <v>1.11</v>
       </c>
-      <c r="R33" s="415">
+      <c r="R33" s="405">
         <v>-1.59</v>
       </c>
-      <c r="S33" s="408">
+      <c r="S33" s="406">
         <v>-5.24</v>
       </c>
-      <c r="T33" s="409">
-        <v>-13.02</v>
+      <c r="T33" s="407">
+        <v>-12.22</v>
       </c>
     </row>
     <row r="34">
@@ -9626,7 +9738,7 @@
       <c r="C34" t="str">
         <v>300131</v>
       </c>
-      <c r="D34" s="429" t="str">
+      <c r="D34" s="417" t="str">
         <v>净卖: -9057.02万</v>
       </c>
       <c r="E34">
@@ -9641,94 +9753,96 @@
       <c r="H34">
         <v>2.57</v>
       </c>
-      <c r="I34" s="418">
+      <c r="I34" s="424">
         <v>-18.81</v>
       </c>
-      <c r="J34" s="421">
+      <c r="J34" s="427">
         <v>-16.59</v>
       </c>
-      <c r="K34" s="425">
+      <c r="K34" s="418">
         <v>-10.32</v>
       </c>
-      <c r="L34" s="419">
+      <c r="L34" s="421">
         <v>-11.8</v>
       </c>
-      <c r="M34" s="417">
+      <c r="M34" s="425">
         <v>-16.08</v>
       </c>
-      <c r="N34" s="426">
+      <c r="N34" s="419">
         <v>-14.6</v>
       </c>
       <c r="O34" s="422">
         <v>-17.4</v>
       </c>
-      <c r="P34" s="423">
+      <c r="P34" s="428">
         <v>-16.22</v>
       </c>
       <c r="Q34" s="420">
         <v>-16.74</v>
       </c>
-      <c r="R34" s="427">
+      <c r="R34" s="429">
         <v>-9.44</v>
       </c>
-      <c r="S34" s="428">
+      <c r="S34" s="426">
         <v>-5.24</v>
       </c>
-      <c r="T34" s="424">
-        <v>30.68</v>
+      <c r="T34" s="423">
+        <v>20.06</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>纪录总数</v>
-      </c>
-      <c r="B35" t="str"/>
-      <c r="C35" t="str"/>
-      <c r="D35" t="str"/>
-      <c r="E35" t="str"/>
-      <c r="F35" t="str"/>
-      <c r="G35" t="str"/>
-      <c r="H35" t="str"/>
-      <c r="I35">
-        <v>33</v>
-      </c>
-      <c r="J35">
-        <v>33</v>
-      </c>
-      <c r="K35">
-        <v>33</v>
-      </c>
-      <c r="L35">
-        <v>33</v>
-      </c>
-      <c r="M35">
-        <v>33</v>
-      </c>
-      <c r="N35">
-        <v>33</v>
-      </c>
-      <c r="O35">
-        <v>33</v>
-      </c>
-      <c r="P35">
-        <v>33</v>
-      </c>
-      <c r="Q35">
-        <v>33</v>
-      </c>
-      <c r="R35">
-        <v>33</v>
-      </c>
-      <c r="S35">
-        <v>33</v>
-      </c>
-      <c r="T35">
-        <v>33</v>
+        <v>2026-04-20</v>
+      </c>
+      <c r="B35" t="str">
+        <v>网达软件</v>
+      </c>
+      <c r="C35" t="str">
+        <v>603189</v>
+      </c>
+      <c r="D35" s="436" t="str">
+        <v>净买: 91.85万</v>
+      </c>
+      <c r="E35">
+        <v>13.73</v>
+      </c>
+      <c r="F35">
+        <v>13.73</v>
+      </c>
+      <c r="G35">
+        <v>13.73</v>
+      </c>
+      <c r="H35">
+        <v>-9.97</v>
+      </c>
+      <c r="I35" s="430">
+        <v>0</v>
+      </c>
+      <c r="J35" s="431">
+        <v>3.42</v>
+      </c>
+      <c r="K35" s="432">
+        <v>-6.85</v>
+      </c>
+      <c r="L35" s="433">
+        <v>-8.23</v>
+      </c>
+      <c r="M35" s="434">
+        <v>-8.01</v>
+      </c>
+      <c r="N35" t="str"/>
+      <c r="O35" t="str"/>
+      <c r="P35" t="str"/>
+      <c r="Q35" t="str"/>
+      <c r="R35" t="str"/>
+      <c r="S35" t="str"/>
+      <c r="T35" s="435">
+        <v>-8.01</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>上涨比例</v>
+        <v>纪录总数</v>
       </c>
       <c r="B36" t="str"/>
       <c r="C36" t="str"/>
@@ -9737,46 +9851,46 @@
       <c r="F36" t="str"/>
       <c r="G36" t="str"/>
       <c r="H36" t="str"/>
-      <c r="I36" s="436">
-        <v>54.55</v>
-      </c>
-      <c r="J36" s="437">
-        <v>57.58</v>
-      </c>
-      <c r="K36" s="432">
-        <v>51.52</v>
-      </c>
-      <c r="L36" s="438">
-        <v>54.55</v>
-      </c>
-      <c r="M36" s="433">
-        <v>60.61</v>
-      </c>
-      <c r="N36" s="434">
-        <v>57.58</v>
-      </c>
-      <c r="O36" s="435">
-        <v>54.55</v>
-      </c>
-      <c r="P36" s="439">
-        <v>54.55</v>
-      </c>
-      <c r="Q36" s="431">
-        <v>51.52</v>
-      </c>
-      <c r="R36" s="441">
-        <v>45.45</v>
-      </c>
-      <c r="S36" s="440">
-        <v>45.45</v>
-      </c>
-      <c r="T36" s="430">
-        <v>45.45</v>
+      <c r="I36">
+        <v>34</v>
+      </c>
+      <c r="J36">
+        <v>34</v>
+      </c>
+      <c r="K36">
+        <v>34</v>
+      </c>
+      <c r="L36">
+        <v>34</v>
+      </c>
+      <c r="M36">
+        <v>34</v>
+      </c>
+      <c r="N36">
+        <v>33</v>
+      </c>
+      <c r="O36">
+        <v>33</v>
+      </c>
+      <c r="P36">
+        <v>33</v>
+      </c>
+      <c r="Q36">
+        <v>33</v>
+      </c>
+      <c r="R36">
+        <v>33</v>
+      </c>
+      <c r="S36">
+        <v>33</v>
+      </c>
+      <c r="T36">
+        <v>34</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>平均涨幅</v>
+        <v>上涨比例</v>
       </c>
       <c r="B37" t="str"/>
       <c r="C37" t="str"/>
@@ -9785,41 +9899,89 @@
       <c r="F37" t="str"/>
       <c r="G37" t="str"/>
       <c r="H37" t="str"/>
-      <c r="I37" s="450">
-        <v>2.72</v>
-      </c>
-      <c r="J37" s="453">
-        <v>3.68</v>
+      <c r="I37" s="441">
+        <v>52.94</v>
+      </c>
+      <c r="J37" s="438">
+        <v>58.82</v>
       </c>
       <c r="K37" s="442">
-        <v>3.17</v>
-      </c>
-      <c r="L37" s="449">
-        <v>4.28</v>
-      </c>
-      <c r="M37" s="451">
-        <v>4.38</v>
+        <v>50</v>
+      </c>
+      <c r="L37" s="447">
+        <v>52.94</v>
+      </c>
+      <c r="M37" s="439">
+        <v>58.82</v>
       </c>
       <c r="N37" s="443">
+        <v>57.58</v>
+      </c>
+      <c r="O37" s="440">
+        <v>54.55</v>
+      </c>
+      <c r="P37" s="448">
+        <v>54.55</v>
+      </c>
+      <c r="Q37" s="445">
+        <v>51.52</v>
+      </c>
+      <c r="R37" s="444">
+        <v>45.45</v>
+      </c>
+      <c r="S37" s="446">
+        <v>45.45</v>
+      </c>
+      <c r="T37" s="437">
+        <v>44.12</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>平均涨幅</v>
+      </c>
+      <c r="B38" t="str"/>
+      <c r="C38" t="str"/>
+      <c r="D38" t="str"/>
+      <c r="E38" t="str"/>
+      <c r="F38" t="str"/>
+      <c r="G38" t="str"/>
+      <c r="H38" t="str"/>
+      <c r="I38" s="452">
+        <v>2.64</v>
+      </c>
+      <c r="J38" s="458">
+        <v>3.67</v>
+      </c>
+      <c r="K38" s="456">
+        <v>2.87</v>
+      </c>
+      <c r="L38" s="453">
+        <v>3.91</v>
+      </c>
+      <c r="M38" s="459">
+        <v>4.02</v>
+      </c>
+      <c r="N38" s="457">
         <v>2.62</v>
       </c>
-      <c r="O37" s="446">
+      <c r="O38" s="449">
         <v>1.54</v>
       </c>
-      <c r="P37" s="452">
+      <c r="P38" s="454">
         <v>1.8</v>
       </c>
-      <c r="Q37" s="447">
+      <c r="Q38" s="460">
         <v>2.18</v>
       </c>
-      <c r="R37" s="444">
+      <c r="R38" s="450">
         <v>1.38</v>
       </c>
-      <c r="S37" s="448">
+      <c r="S38" s="455">
         <v>1.44</v>
       </c>
-      <c r="T37" s="445">
-        <v>25.68</v>
+      <c r="T38" s="451">
+        <v>22.47</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/新生代/index.xlsx
+++ b/youzi/新生代/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="462">
+  <fills count="463">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,31 +39,673 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF22903C"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF29A746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF29A746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8B94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D0D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D0D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF71C584"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF8F0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF79C88B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -75,37 +717,1657 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1E2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35D6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAADCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1ECD7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF35AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C1C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3FB059"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8993"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3646"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3606D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA4AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0ECD7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -117,301 +2379,265 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8891"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE3C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8B94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -423,49 +2649,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFE7747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD6AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8891"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD6AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C3C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -477,25 +2721,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFF4C3C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -507,120 +2769,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D0D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D0D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF71C584"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF8F0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD73242"/>
         <bgColor/>
       </patternFill>
@@ -633,2095 +2781,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF79C88B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCB2D3C"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1E2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF35AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAADCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1ECD7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3FB059"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C1C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8993"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3646"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3606D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0ECD7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8891"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBAE3C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C3C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46572"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C3C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2733,72 +2799,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDF4957"/>
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="461">
+  <borders count="462">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -6030,7 +6043,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="461">
+  <cellXfs count="462">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -7410,6 +7423,9 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="460" fillId="461" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="461" fillId="462" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -7754,7 +7770,7 @@
       <c r="C2" t="str">
         <v>002238</v>
       </c>
-      <c r="D2" s="3" t="str">
+      <c r="D2" s="13" t="str">
         <v>净卖: -808.36万</v>
       </c>
       <c r="E2">
@@ -7769,41 +7785,41 @@
       <c r="H2">
         <v>4.28</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="7">
         <v>5.53</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="10">
         <v>-4.96</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="6">
         <v>-1.72</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="1">
         <v>-6.11</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2" s="2">
         <v>-6.87</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="3">
         <v>-8.3</v>
       </c>
-      <c r="O2" s="6">
+      <c r="O2" s="4">
         <v>-8.78</v>
       </c>
-      <c r="P2" s="8">
+      <c r="P2" s="5">
         <v>-12.21</v>
       </c>
-      <c r="Q2" s="7">
+      <c r="Q2" s="8">
         <v>-13.17</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="11">
         <v>-14.03</v>
       </c>
       <c r="S2" s="9">
         <v>-13.84</v>
       </c>
-      <c r="T2" s="10">
-        <v>-32.92</v>
+      <c r="T2" s="12">
+        <v>-31.97</v>
       </c>
     </row>
     <row r="3">
@@ -7834,38 +7850,38 @@
       <c r="I3" s="23">
         <v>-9.45</v>
       </c>
-      <c r="J3" s="24">
+      <c r="J3" s="26">
         <v>-6.36</v>
       </c>
-      <c r="K3" s="20">
+      <c r="K3" s="24">
         <v>-10.55</v>
       </c>
-      <c r="L3" s="25">
+      <c r="L3" s="19">
         <v>-11.27</v>
       </c>
-      <c r="M3" s="21">
+      <c r="M3" s="20">
         <v>-12.64</v>
       </c>
-      <c r="N3" s="15">
+      <c r="N3" s="16">
         <v>-13.09</v>
       </c>
-      <c r="O3" s="16">
+      <c r="O3" s="21">
         <v>-16.36</v>
       </c>
-      <c r="P3" s="19">
+      <c r="P3" s="22">
         <v>-17.27</v>
       </c>
-      <c r="Q3" s="22">
+      <c r="Q3" s="14">
         <v>-18.09</v>
       </c>
-      <c r="R3" s="26">
+      <c r="R3" s="25">
         <v>-17.91</v>
       </c>
-      <c r="S3" s="14">
+      <c r="S3" s="17">
         <v>-17.55</v>
       </c>
-      <c r="T3" s="17">
-        <v>-36.09</v>
+      <c r="T3" s="15">
+        <v>-35.18</v>
       </c>
     </row>
     <row r="4">
@@ -7878,7 +7894,7 @@
       <c r="C4" t="str">
         <v>600540</v>
       </c>
-      <c r="D4" s="27" t="str">
+      <c r="D4" s="38" t="str">
         <v>净卖: -203.46万</v>
       </c>
       <c r="E4">
@@ -7893,41 +7909,41 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" s="37">
+      <c r="I4" s="39">
         <v>10.08</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="34">
         <v>21.19</v>
       </c>
-      <c r="K4" s="36">
+      <c r="K4" s="27">
         <v>33.33</v>
       </c>
-      <c r="L4" s="29">
+      <c r="L4" s="28">
         <v>46.77</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="35">
         <v>61.5</v>
       </c>
-      <c r="N4" s="31">
+      <c r="N4" s="29">
         <v>45.48</v>
       </c>
-      <c r="O4" s="32">
+      <c r="O4" s="30">
         <v>53.23</v>
       </c>
-      <c r="P4" s="33">
+      <c r="P4" s="36">
         <v>58.66</v>
       </c>
-      <c r="Q4" s="38">
+      <c r="Q4" s="31">
         <v>51.94</v>
       </c>
-      <c r="R4" s="35">
+      <c r="R4" s="32">
         <v>36.69</v>
       </c>
-      <c r="S4" s="34">
+      <c r="S4" s="37">
         <v>23</v>
       </c>
-      <c r="T4" s="39">
-        <v>24.55</v>
+      <c r="T4" s="33">
+        <v>29.72</v>
       </c>
     </row>
     <row r="5">
@@ -7955,41 +7971,41 @@
       <c r="H5">
         <v>4.75</v>
       </c>
-      <c r="I5" s="49">
+      <c r="I5" s="48">
         <v>4.91</v>
       </c>
-      <c r="J5" s="50">
+      <c r="J5" s="49">
         <v>15.37</v>
       </c>
-      <c r="K5" s="44">
+      <c r="K5" s="50">
         <v>10.56</v>
       </c>
-      <c r="L5" s="45">
+      <c r="L5" s="52">
         <v>11.76</v>
       </c>
-      <c r="M5" s="51">
+      <c r="M5" s="44">
         <v>4.07</v>
       </c>
-      <c r="N5" s="52">
+      <c r="N5" s="47">
         <v>5.09</v>
       </c>
-      <c r="O5" s="46">
+      <c r="O5" s="40">
         <v>2.87</v>
       </c>
-      <c r="P5" s="42">
+      <c r="P5" s="45">
         <v>0.56</v>
       </c>
-      <c r="Q5" s="47">
+      <c r="Q5" s="51">
         <v>0.19</v>
       </c>
-      <c r="R5" s="48">
+      <c r="R5" s="41">
         <v>-3.15</v>
       </c>
-      <c r="S5" s="40">
+      <c r="S5" s="46">
         <v>-2.31</v>
       </c>
-      <c r="T5" s="41">
-        <v>-8.7</v>
+      <c r="T5" s="42">
+        <v>-11.57</v>
       </c>
     </row>
     <row r="6">
@@ -8002,7 +8018,7 @@
       <c r="C6" t="str">
         <v>001368</v>
       </c>
-      <c r="D6" s="55" t="str">
+      <c r="D6" s="58" t="str">
         <v>净卖: -491.53万</v>
       </c>
       <c r="E6">
@@ -8023,7 +8039,7 @@
       <c r="J6" s="65">
         <v>-9.94</v>
       </c>
-      <c r="K6" s="56">
+      <c r="K6" s="59">
         <v>-12.52</v>
       </c>
       <c r="L6" s="53">
@@ -8032,26 +8048,26 @@
       <c r="M6" s="60">
         <v>-1.89</v>
       </c>
-      <c r="N6" s="57">
+      <c r="N6" s="54">
         <v>-5.64</v>
       </c>
-      <c r="O6" s="61">
+      <c r="O6" s="55">
         <v>-7.27</v>
       </c>
-      <c r="P6" s="58">
+      <c r="P6" s="61">
         <v>-8.13</v>
       </c>
-      <c r="Q6" s="59">
+      <c r="Q6" s="56">
         <v>-8.91</v>
       </c>
-      <c r="R6" s="54">
+      <c r="R6" s="57">
         <v>-8.61</v>
       </c>
       <c r="S6" s="62">
         <v>-5.85</v>
       </c>
       <c r="T6" s="63">
-        <v>22.12</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="7">
@@ -8064,7 +8080,7 @@
       <c r="C7" t="str">
         <v>603516</v>
       </c>
-      <c r="D7" s="69" t="str">
+      <c r="D7" s="78" t="str">
         <v>净买: 374.25万</v>
       </c>
       <c r="E7">
@@ -8079,41 +8095,41 @@
       <c r="H7">
         <v>-10.01</v>
       </c>
-      <c r="I7" s="73">
+      <c r="I7" s="66">
         <v>0</v>
       </c>
-      <c r="J7" s="66">
+      <c r="J7" s="68">
         <v>4.02</v>
       </c>
-      <c r="K7" s="70">
+      <c r="K7" s="67">
         <v>2.06</v>
       </c>
-      <c r="L7" s="76">
+      <c r="L7" s="73">
         <v>3.75</v>
       </c>
-      <c r="M7" s="67">
+      <c r="M7" s="69">
         <v>7.52</v>
       </c>
-      <c r="N7" s="71">
+      <c r="N7" s="70">
         <v>6.86</v>
       </c>
-      <c r="O7" s="68">
+      <c r="O7" s="71">
         <v>11.67</v>
       </c>
       <c r="P7" s="74">
         <v>9.4</v>
       </c>
-      <c r="Q7" s="77">
+      <c r="Q7" s="76">
         <v>11.63</v>
       </c>
       <c r="R7" s="72">
         <v>11.12</v>
       </c>
-      <c r="S7" s="78">
+      <c r="S7" s="77">
         <v>9.79</v>
       </c>
       <c r="T7" s="75">
-        <v>341.4</v>
+        <v>341.86</v>
       </c>
     </row>
     <row r="8">
@@ -8126,7 +8142,7 @@
       <c r="C8" t="str">
         <v>002510</v>
       </c>
-      <c r="D8" s="80" t="str">
+      <c r="D8" s="89" t="str">
         <v>净卖: -764.76万</v>
       </c>
       <c r="E8">
@@ -8141,40 +8157,40 @@
       <c r="H8">
         <v>10.06</v>
       </c>
-      <c r="I8" s="79">
+      <c r="I8" s="90">
         <v>0</v>
       </c>
-      <c r="J8" s="89">
+      <c r="J8" s="85">
         <v>10</v>
       </c>
-      <c r="K8" s="81">
+      <c r="K8" s="87">
         <v>21</v>
       </c>
-      <c r="L8" s="85">
+      <c r="L8" s="91">
         <v>17.57</v>
       </c>
-      <c r="M8" s="86">
+      <c r="M8" s="81">
         <v>5.86</v>
       </c>
       <c r="N8" s="82">
         <v>1.57</v>
       </c>
-      <c r="O8" s="90">
+      <c r="O8" s="86">
         <v>3.57</v>
       </c>
-      <c r="P8" s="83">
+      <c r="P8" s="79">
         <v>1.14</v>
       </c>
-      <c r="Q8" s="87">
+      <c r="Q8" s="83">
         <v>1.14</v>
       </c>
-      <c r="R8" s="91">
+      <c r="R8" s="80">
         <v>-4.57</v>
       </c>
-      <c r="S8" s="84">
+      <c r="S8" s="88">
         <v>-2.71</v>
       </c>
-      <c r="T8" s="88">
+      <c r="T8" s="84">
         <v>-3.29</v>
       </c>
     </row>
@@ -8188,7 +8204,7 @@
       <c r="C9" t="str">
         <v>600367</v>
       </c>
-      <c r="D9" s="95" t="str">
+      <c r="D9" s="94" t="str">
         <v>净买: 3583.76万</v>
       </c>
       <c r="E9">
@@ -8203,41 +8219,41 @@
       <c r="H9">
         <v>4.52</v>
       </c>
-      <c r="I9" s="96">
+      <c r="I9" s="104">
         <v>-0.98</v>
       </c>
-      <c r="J9" s="93">
+      <c r="J9" s="95">
         <v>-4.07</v>
       </c>
-      <c r="K9" s="97">
+      <c r="K9" s="96">
         <v>-0.39</v>
       </c>
-      <c r="L9" s="98">
+      <c r="L9" s="102">
         <v>5.44</v>
       </c>
-      <c r="M9" s="104">
+      <c r="M9" s="97">
         <v>5.18</v>
       </c>
-      <c r="N9" s="99">
+      <c r="N9" s="98">
         <v>12.52</v>
       </c>
-      <c r="O9" s="100">
+      <c r="O9" s="99">
         <v>1.25</v>
       </c>
-      <c r="P9" s="102">
+      <c r="P9" s="92">
         <v>11.34</v>
       </c>
-      <c r="Q9" s="101">
+      <c r="Q9" s="93">
         <v>4.07</v>
       </c>
-      <c r="R9" s="92">
+      <c r="R9" s="101">
         <v>0.26</v>
       </c>
-      <c r="S9" s="103">
+      <c r="S9" s="100">
         <v>2.89</v>
       </c>
-      <c r="T9" s="94">
-        <v>48.66</v>
+      <c r="T9" s="103">
+        <v>42.3</v>
       </c>
     </row>
     <row r="10">
@@ -8250,7 +8266,7 @@
       <c r="C10" t="str">
         <v>603585</v>
       </c>
-      <c r="D10" s="107" t="str">
+      <c r="D10" s="105" t="str">
         <v>净买: 620.83万</v>
       </c>
       <c r="E10">
@@ -8265,41 +8281,41 @@
       <c r="H10">
         <v>-7.49</v>
       </c>
-      <c r="I10" s="113">
+      <c r="I10" s="109">
         <v>-2.7</v>
       </c>
-      <c r="J10" s="114">
+      <c r="J10" s="110">
         <v>-7</v>
       </c>
-      <c r="K10" s="108">
+      <c r="K10" s="106">
         <v>-4.8</v>
       </c>
-      <c r="L10" s="117">
+      <c r="L10" s="116">
         <v>-5.45</v>
       </c>
-      <c r="M10" s="105">
+      <c r="M10" s="112">
         <v>-7.65</v>
       </c>
-      <c r="N10" s="106">
+      <c r="N10" s="113">
         <v>-8.8</v>
       </c>
-      <c r="O10" s="112">
+      <c r="O10" s="107">
         <v>-8.55</v>
       </c>
-      <c r="P10" s="109">
+      <c r="P10" s="117">
         <v>-7.55</v>
       </c>
-      <c r="Q10" s="110">
+      <c r="Q10" s="114">
         <v>-1.95</v>
       </c>
-      <c r="R10" s="115">
+      <c r="R10" s="108">
         <v>-3.1</v>
       </c>
-      <c r="S10" s="116">
+      <c r="S10" s="115">
         <v>6.6</v>
       </c>
       <c r="T10" s="111">
-        <v>0.15</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="11">
@@ -8312,7 +8328,7 @@
       <c r="C11" t="str">
         <v>600962</v>
       </c>
-      <c r="D11" s="128" t="str">
+      <c r="D11" s="124" t="str">
         <v>净卖: -17.88万</v>
       </c>
       <c r="E11">
@@ -8327,41 +8343,41 @@
       <c r="H11">
         <v>10.03</v>
       </c>
-      <c r="I11" s="118">
+      <c r="I11" s="125">
         <v>0</v>
       </c>
-      <c r="J11" s="120">
+      <c r="J11" s="121">
         <v>10.01</v>
       </c>
-      <c r="K11" s="125">
+      <c r="K11" s="119">
         <v>21.03</v>
       </c>
       <c r="L11" s="126">
         <v>19.13</v>
       </c>
-      <c r="M11" s="119">
+      <c r="M11" s="130">
         <v>9.62</v>
       </c>
-      <c r="N11" s="121">
+      <c r="N11" s="120">
         <v>16.33</v>
       </c>
-      <c r="O11" s="122">
+      <c r="O11" s="127">
         <v>18.74</v>
       </c>
-      <c r="P11" s="127">
+      <c r="P11" s="118">
         <v>18.01</v>
       </c>
-      <c r="Q11" s="129">
+      <c r="Q11" s="128">
         <v>14.09</v>
       </c>
-      <c r="R11" s="130">
+      <c r="R11" s="122">
         <v>10.91</v>
       </c>
-      <c r="S11" s="123">
+      <c r="S11" s="129">
         <v>10.29</v>
       </c>
-      <c r="T11" s="124">
-        <v>16.5</v>
+      <c r="T11" s="123">
+        <v>16.33</v>
       </c>
     </row>
     <row r="12">
@@ -8374,7 +8390,7 @@
       <c r="C12" t="str">
         <v>003037</v>
       </c>
-      <c r="D12" s="139" t="str">
+      <c r="D12" s="142" t="str">
         <v>净卖: -2233.11万</v>
       </c>
       <c r="E12">
@@ -8389,41 +8405,41 @@
       <c r="H12">
         <v>4.89</v>
       </c>
-      <c r="I12" s="140">
+      <c r="I12" s="138">
         <v>4.88</v>
       </c>
-      <c r="J12" s="132">
+      <c r="J12" s="134">
         <v>8.77</v>
       </c>
-      <c r="K12" s="133">
+      <c r="K12" s="135">
         <v>-1.89</v>
       </c>
       <c r="L12" s="143">
         <v>-3.22</v>
       </c>
-      <c r="M12" s="141">
+      <c r="M12" s="136">
         <v>6.44</v>
       </c>
-      <c r="N12" s="137">
+      <c r="N12" s="132">
         <v>17.09</v>
       </c>
-      <c r="O12" s="142">
+      <c r="O12" s="133">
         <v>16.09</v>
       </c>
-      <c r="P12" s="134">
+      <c r="P12" s="139">
         <v>14.32</v>
       </c>
-      <c r="Q12" s="135">
+      <c r="Q12" s="137">
         <v>4.88</v>
       </c>
-      <c r="R12" s="138">
+      <c r="R12" s="140">
         <v>3.77</v>
       </c>
-      <c r="S12" s="131">
+      <c r="S12" s="141">
         <v>4</v>
       </c>
-      <c r="T12" s="136">
-        <v>-21.75</v>
+      <c r="T12" s="131">
+        <v>-20.42</v>
       </c>
     </row>
     <row r="13">
@@ -8436,7 +8452,7 @@
       <c r="C13" t="str">
         <v>001306</v>
       </c>
-      <c r="D13" s="155" t="str">
+      <c r="D13" s="148" t="str">
         <v>净卖: -462.25万</v>
       </c>
       <c r="E13">
@@ -8451,41 +8467,41 @@
       <c r="H13">
         <v>0.03</v>
       </c>
-      <c r="I13" s="156">
+      <c r="I13" s="149">
         <v>6.62</v>
       </c>
-      <c r="J13" s="145">
+      <c r="J13" s="156">
         <v>17.29</v>
       </c>
-      <c r="K13" s="149">
+      <c r="K13" s="144">
         <v>22.79</v>
       </c>
-      <c r="L13" s="146">
+      <c r="L13" s="150">
         <v>28.15</v>
       </c>
-      <c r="M13" s="147">
+      <c r="M13" s="151">
         <v>23.18</v>
       </c>
-      <c r="N13" s="150">
+      <c r="N13" s="145">
         <v>22.64</v>
       </c>
-      <c r="O13" s="148">
+      <c r="O13" s="146">
         <v>27.89</v>
       </c>
-      <c r="P13" s="144">
+      <c r="P13" s="152">
         <v>23.34</v>
       </c>
-      <c r="Q13" s="151">
+      <c r="Q13" s="147">
         <v>24.33</v>
       </c>
-      <c r="R13" s="152">
+      <c r="R13" s="153">
         <v>22.68</v>
       </c>
-      <c r="S13" s="153">
+      <c r="S13" s="154">
         <v>28.62</v>
       </c>
-      <c r="T13" s="154">
-        <v>-13.1</v>
+      <c r="T13" s="155">
+        <v>-10.55</v>
       </c>
     </row>
     <row r="14">
@@ -8498,7 +8514,7 @@
       <c r="C14" t="str">
         <v>002953</v>
       </c>
-      <c r="D14" s="167" t="str">
+      <c r="D14" s="162" t="str">
         <v>净卖: -867.00万</v>
       </c>
       <c r="E14">
@@ -8513,41 +8529,41 @@
       <c r="H14">
         <v>-2.07</v>
       </c>
-      <c r="I14" s="168">
+      <c r="I14" s="167">
         <v>12.29</v>
       </c>
-      <c r="J14" s="160">
+      <c r="J14" s="168">
         <v>17.19</v>
       </c>
-      <c r="K14" s="165">
+      <c r="K14" s="169">
         <v>10.41</v>
       </c>
-      <c r="L14" s="169">
+      <c r="L14" s="163">
         <v>21.42</v>
       </c>
-      <c r="M14" s="161">
+      <c r="M14" s="164">
         <v>15.91</v>
       </c>
-      <c r="N14" s="162">
+      <c r="N14" s="165">
         <v>4.3</v>
       </c>
-      <c r="O14" s="163">
+      <c r="O14" s="157">
         <v>-1.96</v>
       </c>
-      <c r="P14" s="164">
+      <c r="P14" s="159">
         <v>-1.06</v>
       </c>
-      <c r="Q14" s="166">
+      <c r="Q14" s="158">
         <v>-0.75</v>
       </c>
-      <c r="R14" s="157">
+      <c r="R14" s="160">
         <v>-0.98</v>
       </c>
-      <c r="S14" s="158">
+      <c r="S14" s="166">
         <v>-4.68</v>
       </c>
-      <c r="T14" s="159">
-        <v>-10.26</v>
+      <c r="T14" s="161">
+        <v>-9.35</v>
       </c>
     </row>
     <row r="15">
@@ -8560,7 +8576,7 @@
       <c r="C15" t="str">
         <v>605133</v>
       </c>
-      <c r="D15" s="178" t="str">
+      <c r="D15" s="172" t="str">
         <v>净买: 3043.68万</v>
       </c>
       <c r="E15">
@@ -8575,41 +8591,41 @@
       <c r="H15">
         <v>-0.11</v>
       </c>
-      <c r="I15" s="170">
+      <c r="I15" s="181">
         <v>10.11</v>
       </c>
-      <c r="J15" s="171">
+      <c r="J15" s="174">
         <v>6.15</v>
       </c>
-      <c r="K15" s="172">
+      <c r="K15" s="175">
         <v>-4.46</v>
       </c>
-      <c r="L15" s="175">
+      <c r="L15" s="182">
         <v>-0.27</v>
       </c>
-      <c r="M15" s="179">
+      <c r="M15" s="176">
         <v>3.14</v>
       </c>
-      <c r="N15" s="176">
+      <c r="N15" s="173">
         <v>1.53</v>
       </c>
       <c r="O15" s="177">
         <v>-1.62</v>
       </c>
-      <c r="P15" s="173">
+      <c r="P15" s="178">
         <v>-0.46</v>
       </c>
-      <c r="Q15" s="180">
+      <c r="Q15" s="179">
         <v>-2.94</v>
       </c>
-      <c r="R15" s="181">
+      <c r="R15" s="170">
         <v>-0.55</v>
       </c>
-      <c r="S15" s="182">
+      <c r="S15" s="180">
         <v>9.41</v>
       </c>
-      <c r="T15" s="174">
-        <v>-28</v>
+      <c r="T15" s="171">
+        <v>-29.02</v>
       </c>
     </row>
     <row r="16">
@@ -8622,7 +8638,7 @@
       <c r="C16" t="str">
         <v>301533</v>
       </c>
-      <c r="D16" s="195" t="str">
+      <c r="D16" s="188" t="str">
         <v>净卖: -733.04万</v>
       </c>
       <c r="E16">
@@ -8637,41 +8653,41 @@
       <c r="H16">
         <v>2.26</v>
       </c>
-      <c r="I16" s="193">
+      <c r="I16" s="191">
         <v>3.46</v>
       </c>
-      <c r="J16" s="188">
+      <c r="J16" s="189">
         <v>8.33</v>
       </c>
-      <c r="K16" s="189">
+      <c r="K16" s="190">
         <v>10.64</v>
       </c>
-      <c r="L16" s="185">
+      <c r="L16" s="192">
         <v>7.14</v>
       </c>
-      <c r="M16" s="190">
+      <c r="M16" s="184">
         <v>11.64</v>
       </c>
-      <c r="N16" s="191">
+      <c r="N16" s="185">
         <v>6.19</v>
       </c>
-      <c r="O16" s="183">
+      <c r="O16" s="186">
         <v>3.76</v>
       </c>
-      <c r="P16" s="184">
+      <c r="P16" s="187">
         <v>0.97</v>
       </c>
-      <c r="Q16" s="194">
+      <c r="Q16" s="193">
         <v>-1.04</v>
       </c>
-      <c r="R16" s="192">
+      <c r="R16" s="194">
         <v>-2.01</v>
       </c>
-      <c r="S16" s="186">
+      <c r="S16" s="195">
         <v>-5.7</v>
       </c>
-      <c r="T16" s="187">
-        <v>-19.92</v>
+      <c r="T16" s="183">
+        <v>-18.45</v>
       </c>
     </row>
     <row r="17">
@@ -8684,7 +8700,7 @@
       <c r="C17" t="str">
         <v>688148</v>
       </c>
-      <c r="D17" s="207" t="str">
+      <c r="D17" s="198" t="str">
         <v>净卖: -1051.47万</v>
       </c>
       <c r="E17">
@@ -8699,41 +8715,41 @@
       <c r="H17">
         <v>4.34</v>
       </c>
-      <c r="I17" s="199">
+      <c r="I17" s="207">
         <v>15.03</v>
       </c>
-      <c r="J17" s="204">
+      <c r="J17" s="208">
         <v>37.63</v>
       </c>
-      <c r="K17" s="208">
+      <c r="K17" s="204">
         <v>33.37</v>
       </c>
-      <c r="L17" s="200">
+      <c r="L17" s="199">
         <v>33.9</v>
       </c>
-      <c r="M17" s="205">
+      <c r="M17" s="200">
         <v>29</v>
       </c>
-      <c r="N17" s="201">
+      <c r="N17" s="205">
         <v>24.95</v>
       </c>
-      <c r="O17" s="202">
+      <c r="O17" s="196">
         <v>20.36</v>
       </c>
-      <c r="P17" s="196">
+      <c r="P17" s="206">
         <v>18.44</v>
       </c>
-      <c r="Q17" s="203">
+      <c r="Q17" s="201">
         <v>13.11</v>
       </c>
       <c r="R17" s="197">
         <v>1.49</v>
       </c>
-      <c r="S17" s="206">
+      <c r="S17" s="203">
         <v>-1.39</v>
       </c>
-      <c r="T17" s="198">
-        <v>9.28</v>
+      <c r="T17" s="202">
+        <v>9.49</v>
       </c>
     </row>
     <row r="18">
@@ -8746,7 +8762,7 @@
       <c r="C18" t="str">
         <v>688148</v>
       </c>
-      <c r="D18" s="209" t="str">
+      <c r="D18" s="221" t="str">
         <v>净卖: -2325.34万</v>
       </c>
       <c r="E18">
@@ -8761,41 +8777,41 @@
       <c r="H18">
         <v>5.56</v>
       </c>
-      <c r="I18" s="216">
+      <c r="I18" s="209">
         <v>13.35</v>
       </c>
-      <c r="J18" s="219">
+      <c r="J18" s="213">
         <v>9.83</v>
       </c>
-      <c r="K18" s="220">
+      <c r="K18" s="219">
         <v>10.27</v>
       </c>
-      <c r="L18" s="210">
+      <c r="L18" s="214">
         <v>6.23</v>
       </c>
       <c r="M18" s="211">
         <v>2.9</v>
       </c>
-      <c r="N18" s="221">
+      <c r="N18" s="215">
         <v>-0.88</v>
       </c>
       <c r="O18" s="212">
         <v>-2.46</v>
       </c>
-      <c r="P18" s="217">
+      <c r="P18" s="220">
         <v>-6.85</v>
       </c>
-      <c r="Q18" s="213">
+      <c r="Q18" s="216">
         <v>-16.42</v>
       </c>
-      <c r="R18" s="214">
+      <c r="R18" s="210">
         <v>-18.79</v>
       </c>
-      <c r="S18" s="215">
+      <c r="S18" s="217">
         <v>-16.86</v>
       </c>
       <c r="T18" s="218">
-        <v>-10.01</v>
+        <v>-9.83</v>
       </c>
     </row>
     <row r="19">
@@ -8808,7 +8824,7 @@
       <c r="C19" t="str">
         <v>002506</v>
       </c>
-      <c r="D19" s="224" t="str">
+      <c r="D19" s="223" t="str">
         <v>净卖: -1046.77万</v>
       </c>
       <c r="E19">
@@ -8823,41 +8839,41 @@
       <c r="H19">
         <v>1.86</v>
       </c>
-      <c r="I19" s="234">
+      <c r="I19" s="231">
         <v>8.03</v>
       </c>
-      <c r="J19" s="222">
+      <c r="J19" s="224">
         <v>14.23</v>
       </c>
-      <c r="K19" s="227">
+      <c r="K19" s="225">
         <v>15.69</v>
       </c>
-      <c r="L19" s="228">
+      <c r="L19" s="232">
         <v>17.52</v>
       </c>
-      <c r="M19" s="230">
+      <c r="M19" s="233">
         <v>14.6</v>
       </c>
-      <c r="N19" s="225">
+      <c r="N19" s="226">
         <v>8.39</v>
       </c>
-      <c r="O19" s="231">
+      <c r="O19" s="234">
         <v>4.74</v>
       </c>
-      <c r="P19" s="226">
+      <c r="P19" s="230">
         <v>1.46</v>
       </c>
-      <c r="Q19" s="223">
+      <c r="Q19" s="222">
         <v>-6.93</v>
       </c>
-      <c r="R19" s="229">
+      <c r="R19" s="227">
         <v>-7.3</v>
       </c>
-      <c r="S19" s="232">
+      <c r="S19" s="228">
         <v>-6.57</v>
       </c>
-      <c r="T19" s="233">
-        <v>59.12</v>
+      <c r="T19" s="229">
+        <v>59.49</v>
       </c>
     </row>
     <row r="20">
@@ -8870,7 +8886,7 @@
       <c r="C20" t="str">
         <v>603778</v>
       </c>
-      <c r="D20" s="240" t="str">
+      <c r="D20" s="241" t="str">
         <v>净卖: -3366.51万</v>
       </c>
       <c r="E20">
@@ -8885,41 +8901,41 @@
       <c r="H20">
         <v>6.69</v>
       </c>
-      <c r="I20" s="235">
+      <c r="I20" s="245">
         <v>3.07</v>
       </c>
-      <c r="J20" s="241">
+      <c r="J20" s="235">
         <v>13.33</v>
       </c>
-      <c r="K20" s="236">
+      <c r="K20" s="246">
         <v>5.33</v>
       </c>
-      <c r="L20" s="242">
+      <c r="L20" s="236">
         <v>8.67</v>
       </c>
-      <c r="M20" s="237">
+      <c r="M20" s="247">
         <v>19.6</v>
       </c>
-      <c r="N20" s="243">
+      <c r="N20" s="237">
         <v>7.6</v>
       </c>
-      <c r="O20" s="245">
+      <c r="O20" s="242">
         <v>-2</v>
       </c>
-      <c r="P20" s="246">
+      <c r="P20" s="238">
         <v>7.87</v>
       </c>
-      <c r="Q20" s="247">
+      <c r="Q20" s="243">
         <v>18.67</v>
       </c>
-      <c r="R20" s="238">
+      <c r="R20" s="244">
         <v>27.73</v>
       </c>
-      <c r="S20" s="244">
+      <c r="S20" s="239">
         <v>40.53</v>
       </c>
-      <c r="T20" s="239">
-        <v>253.73</v>
+      <c r="T20" s="240">
+        <v>251.47</v>
       </c>
     </row>
     <row r="21">
@@ -8932,7 +8948,7 @@
       <c r="C21" t="str">
         <v>600252</v>
       </c>
-      <c r="D21" s="258" t="str">
+      <c r="D21" s="252" t="str">
         <v>净卖: -331.54万</v>
       </c>
       <c r="E21">
@@ -8947,41 +8963,41 @@
       <c r="H21">
         <v>0.37</v>
       </c>
-      <c r="I21" s="251">
+      <c r="I21" s="259">
         <v>9.67</v>
       </c>
-      <c r="J21" s="259">
+      <c r="J21" s="260">
         <v>6.32</v>
       </c>
-      <c r="K21" s="260">
+      <c r="K21" s="249">
         <v>7.81</v>
       </c>
-      <c r="L21" s="252">
+      <c r="L21" s="256">
         <v>10.41</v>
       </c>
-      <c r="M21" s="253">
+      <c r="M21" s="248">
         <v>9.29</v>
       </c>
-      <c r="N21" s="256">
+      <c r="N21" s="257">
         <v>11.9</v>
       </c>
-      <c r="O21" s="254">
+      <c r="O21" s="253">
         <v>10.78</v>
       </c>
-      <c r="P21" s="248">
+      <c r="P21" s="258">
         <v>11.52</v>
       </c>
-      <c r="Q21" s="249">
+      <c r="Q21" s="250">
         <v>10.04</v>
       </c>
-      <c r="R21" s="250">
+      <c r="R21" s="254">
         <v>6.32</v>
       </c>
-      <c r="S21" s="257">
+      <c r="S21" s="255">
         <v>5.58</v>
       </c>
-      <c r="T21" s="255">
-        <v>-7.81</v>
+      <c r="T21" s="251">
+        <v>-8.92</v>
       </c>
     </row>
     <row r="22">
@@ -8994,7 +9010,7 @@
       <c r="C22" t="str">
         <v>003018</v>
       </c>
-      <c r="D22" s="266" t="str">
+      <c r="D22" s="265" t="str">
         <v>净卖: -1172.31万</v>
       </c>
       <c r="E22">
@@ -9009,41 +9025,41 @@
       <c r="H22">
         <v>10.01</v>
       </c>
-      <c r="I22" s="267">
+      <c r="I22" s="269">
         <v>0</v>
       </c>
-      <c r="J22" s="268">
+      <c r="J22" s="270">
         <v>-9.99</v>
       </c>
-      <c r="K22" s="273">
+      <c r="K22" s="266">
         <v>-18.85</v>
       </c>
-      <c r="L22" s="269">
+      <c r="L22" s="273">
         <v>-18.77</v>
       </c>
-      <c r="M22" s="263">
+      <c r="M22" s="267">
         <v>-15.14</v>
       </c>
-      <c r="N22" s="272">
+      <c r="N22" s="261">
         <v>-23.48</v>
       </c>
-      <c r="O22" s="270">
+      <c r="O22" s="271">
         <v>-18.81</v>
       </c>
-      <c r="P22" s="261">
+      <c r="P22" s="262">
         <v>-22.71</v>
       </c>
-      <c r="Q22" s="264">
+      <c r="Q22" s="263">
         <v>-25.49</v>
       </c>
-      <c r="R22" s="262">
+      <c r="R22" s="264">
         <v>-25.49</v>
       </c>
-      <c r="S22" s="271">
+      <c r="S22" s="268">
         <v>-29.4</v>
       </c>
-      <c r="T22" s="265">
-        <v>130.69</v>
+      <c r="T22" s="272">
+        <v>123.64</v>
       </c>
     </row>
     <row r="23">
@@ -9056,7 +9072,7 @@
       <c r="C23" t="str">
         <v>603958</v>
       </c>
-      <c r="D23" s="277" t="str">
+      <c r="D23" s="282" t="str">
         <v>净买: 48.48万</v>
       </c>
       <c r="E23">
@@ -9071,41 +9087,41 @@
       <c r="H23">
         <v>-5.98</v>
       </c>
-      <c r="I23" s="274">
+      <c r="I23" s="286">
         <v>-4.29</v>
       </c>
       <c r="J23" s="278">
         <v>-7.64</v>
       </c>
-      <c r="K23" s="284">
+      <c r="K23" s="280">
         <v>-8.21</v>
       </c>
-      <c r="L23" s="279">
+      <c r="L23" s="274">
         <v>-4.29</v>
       </c>
-      <c r="M23" s="280">
+      <c r="M23" s="281">
         <v>-7.5</v>
       </c>
-      <c r="N23" s="285">
+      <c r="N23" s="283">
         <v>-8.36</v>
       </c>
-      <c r="O23" s="283">
+      <c r="O23" s="275">
         <v>-10.57</v>
       </c>
-      <c r="P23" s="275">
+      <c r="P23" s="284">
         <v>-8.86</v>
       </c>
-      <c r="Q23" s="281">
+      <c r="Q23" s="285">
         <v>-7.43</v>
       </c>
       <c r="R23" s="276">
         <v>-8</v>
       </c>
-      <c r="S23" s="286">
+      <c r="S23" s="279">
         <v>-8.71</v>
       </c>
-      <c r="T23" s="282">
-        <v>77.36</v>
+      <c r="T23" s="277">
+        <v>68.57</v>
       </c>
     </row>
     <row r="24">
@@ -9118,7 +9134,7 @@
       <c r="C24" t="str">
         <v>002187</v>
       </c>
-      <c r="D24" s="296" t="str">
+      <c r="D24" s="294" t="str">
         <v>净卖: -1062.98万</v>
       </c>
       <c r="E24">
@@ -9133,41 +9149,41 @@
       <c r="H24">
         <v>2</v>
       </c>
-      <c r="I24" s="297">
+      <c r="I24" s="290">
         <v>7.83</v>
       </c>
-      <c r="J24" s="299">
+      <c r="J24" s="291">
         <v>3.92</v>
       </c>
-      <c r="K24" s="294">
+      <c r="K24" s="288">
         <v>3.26</v>
       </c>
-      <c r="L24" s="298">
+      <c r="L24" s="295">
         <v>7.57</v>
       </c>
-      <c r="M24" s="295">
+      <c r="M24" s="292">
         <v>10.05</v>
       </c>
-      <c r="N24" s="287">
+      <c r="N24" s="296">
         <v>8.88</v>
       </c>
-      <c r="O24" s="290">
+      <c r="O24" s="289">
         <v>4.96</v>
       </c>
-      <c r="P24" s="288">
+      <c r="P24" s="297">
         <v>7.83</v>
       </c>
-      <c r="Q24" s="289">
+      <c r="Q24" s="293">
         <v>6.4</v>
       </c>
-      <c r="R24" s="291">
+      <c r="R24" s="298">
         <v>17.1</v>
       </c>
-      <c r="S24" s="292">
+      <c r="S24" s="299">
         <v>5.61</v>
       </c>
-      <c r="T24" s="293">
-        <v>-22.19</v>
+      <c r="T24" s="287">
+        <v>-20.5</v>
       </c>
     </row>
     <row r="25">
@@ -9180,7 +9196,7 @@
       <c r="C25" t="str">
         <v>688273</v>
       </c>
-      <c r="D25" s="305" t="str">
+      <c r="D25" s="308" t="str">
         <v>净卖: -963.67万</v>
       </c>
       <c r="E25">
@@ -9195,41 +9211,41 @@
       <c r="H25">
         <v>-1.99</v>
       </c>
-      <c r="I25" s="308">
+      <c r="I25" s="300">
         <v>-8.57</v>
       </c>
-      <c r="J25" s="300">
+      <c r="J25" s="301">
         <v>-8.03</v>
       </c>
-      <c r="K25" s="306">
+      <c r="K25" s="309">
         <v>-11.27</v>
       </c>
-      <c r="L25" s="301">
+      <c r="L25" s="304">
         <v>-8.63</v>
       </c>
-      <c r="M25" s="309">
+      <c r="M25" s="305">
         <v>-13</v>
       </c>
-      <c r="N25" s="310">
+      <c r="N25" s="306">
         <v>-13.83</v>
       </c>
-      <c r="O25" s="307">
+      <c r="O25" s="311">
         <v>-17.22</v>
       </c>
-      <c r="P25" s="302">
+      <c r="P25" s="312">
         <v>-20.37</v>
       </c>
-      <c r="Q25" s="304">
+      <c r="Q25" s="302">
         <v>-20.43</v>
       </c>
-      <c r="R25" s="311">
+      <c r="R25" s="307">
         <v>-22.83</v>
       </c>
-      <c r="S25" s="312">
+      <c r="S25" s="303">
         <v>-23.42</v>
       </c>
-      <c r="T25" s="303">
-        <v>-21.82</v>
+      <c r="T25" s="310">
+        <v>-22.17</v>
       </c>
     </row>
     <row r="26">
@@ -9242,7 +9258,7 @@
       <c r="C26" t="str">
         <v>688523</v>
       </c>
-      <c r="D26" s="321" t="str">
+      <c r="D26" s="325" t="str">
         <v>净卖: -2032.96万</v>
       </c>
       <c r="E26">
@@ -9257,41 +9273,41 @@
       <c r="H26">
         <v>-6.9</v>
       </c>
-      <c r="I26" s="322">
+      <c r="I26" s="315">
         <v>-12.28</v>
       </c>
-      <c r="J26" s="323">
+      <c r="J26" s="320">
         <v>-15.94</v>
       </c>
-      <c r="K26" s="324">
+      <c r="K26" s="316">
         <v>-22.53</v>
       </c>
-      <c r="L26" s="325">
+      <c r="L26" s="313">
         <v>-23.98</v>
       </c>
-      <c r="M26" s="317">
+      <c r="M26" s="314">
         <v>-21.69</v>
       </c>
-      <c r="N26" s="314">
+      <c r="N26" s="321">
         <v>-28.64</v>
       </c>
-      <c r="O26" s="318">
+      <c r="O26" s="317">
         <v>-29.76</v>
       </c>
-      <c r="P26" s="315">
+      <c r="P26" s="322">
         <v>-23.74</v>
       </c>
-      <c r="Q26" s="316">
+      <c r="Q26" s="318">
         <v>-13.62</v>
       </c>
       <c r="R26" s="319">
         <v>-23.24</v>
       </c>
-      <c r="S26" s="320">
+      <c r="S26" s="323">
         <v>-24.4</v>
       </c>
-      <c r="T26" s="313">
-        <v>-22.08</v>
+      <c r="T26" s="324">
+        <v>-24.06</v>
       </c>
     </row>
     <row r="27">
@@ -9304,7 +9320,7 @@
       <c r="C27" t="str">
         <v>002131</v>
       </c>
-      <c r="D27" s="338" t="str">
+      <c r="D27" s="329" t="str">
         <v>净买: 384.51万</v>
       </c>
       <c r="E27">
@@ -9319,41 +9335,41 @@
       <c r="H27">
         <v>-10</v>
       </c>
-      <c r="I27" s="337">
+      <c r="I27" s="326">
         <v>0</v>
       </c>
-      <c r="J27" s="335">
+      <c r="J27" s="330">
         <v>-10.04</v>
       </c>
-      <c r="K27" s="326">
+      <c r="K27" s="327">
         <v>-10.26</v>
       </c>
-      <c r="L27" s="332">
+      <c r="L27" s="335">
         <v>-14.53</v>
       </c>
-      <c r="M27" s="327">
+      <c r="M27" s="331">
         <v>-9.19</v>
       </c>
       <c r="N27" s="328">
         <v>-6.3</v>
       </c>
-      <c r="O27" s="329">
+      <c r="O27" s="332">
         <v>2.24</v>
       </c>
-      <c r="P27" s="330">
+      <c r="P27" s="333">
         <v>-0.43</v>
       </c>
-      <c r="Q27" s="333">
+      <c r="Q27" s="334">
         <v>5.88</v>
       </c>
-      <c r="R27" s="331">
+      <c r="R27" s="336">
         <v>8.76</v>
       </c>
-      <c r="S27" s="334">
+      <c r="S27" s="337">
         <v>-1.07</v>
       </c>
-      <c r="T27" s="336">
-        <v>-21.26</v>
+      <c r="T27" s="338">
+        <v>-27.35</v>
       </c>
     </row>
     <row r="28">
@@ -9366,7 +9382,7 @@
       <c r="C28" t="str">
         <v>603698</v>
       </c>
-      <c r="D28" s="342" t="str">
+      <c r="D28" s="345" t="str">
         <v>净卖: -1965.64万</v>
       </c>
       <c r="E28">
@@ -9384,38 +9400,38 @@
       <c r="I28" s="339">
         <v>-8.38</v>
       </c>
-      <c r="J28" s="343">
+      <c r="J28" s="340">
         <v>-9.03</v>
       </c>
-      <c r="K28" s="345">
+      <c r="K28" s="346">
         <v>-9.19</v>
       </c>
-      <c r="L28" s="344">
+      <c r="L28" s="342">
         <v>-8.54</v>
       </c>
-      <c r="M28" s="348">
+      <c r="M28" s="343">
         <v>-7.3</v>
       </c>
       <c r="N28" s="349">
         <v>-6.49</v>
       </c>
-      <c r="O28" s="350">
+      <c r="O28" s="344">
         <v>0.59</v>
       </c>
-      <c r="P28" s="351">
+      <c r="P28" s="350">
         <v>2.27</v>
       </c>
-      <c r="Q28" s="340">
+      <c r="Q28" s="341">
         <v>2.54</v>
       </c>
-      <c r="R28" s="346">
+      <c r="R28" s="351">
         <v>4.92</v>
       </c>
       <c r="S28" s="347">
         <v>10.54</v>
       </c>
-      <c r="T28" s="341">
-        <v>9.46</v>
+      <c r="T28" s="348">
+        <v>8.81</v>
       </c>
     </row>
     <row r="29">
@@ -9428,7 +9444,7 @@
       <c r="C29" t="str">
         <v>603619</v>
       </c>
-      <c r="D29" s="356" t="str">
+      <c r="D29" s="363" t="str">
         <v>净买: 3411.20万</v>
       </c>
       <c r="E29">
@@ -9443,41 +9459,41 @@
       <c r="H29">
         <v>1.96</v>
       </c>
-      <c r="I29" s="357">
+      <c r="I29" s="359">
         <v>-8.71</v>
       </c>
-      <c r="J29" s="362">
+      <c r="J29" s="360">
         <v>-17.84</v>
       </c>
-      <c r="K29" s="364">
+      <c r="K29" s="352">
         <v>-20.82</v>
       </c>
-      <c r="L29" s="352">
+      <c r="L29" s="361">
         <v>-14.71</v>
       </c>
-      <c r="M29" s="358">
+      <c r="M29" s="355">
         <v>-18.76</v>
       </c>
-      <c r="N29" s="363">
+      <c r="N29" s="356">
         <v>-14.24</v>
       </c>
-      <c r="O29" s="353">
+      <c r="O29" s="362">
         <v>-16.47</v>
       </c>
-      <c r="P29" s="354">
+      <c r="P29" s="357">
         <v>-12.61</v>
       </c>
-      <c r="Q29" s="355">
+      <c r="Q29" s="353">
         <v>-7.45</v>
       </c>
-      <c r="R29" s="359">
+      <c r="R29" s="364">
         <v>-9.16</v>
       </c>
-      <c r="S29" s="360">
+      <c r="S29" s="358">
         <v>-12.42</v>
       </c>
-      <c r="T29" s="361">
-        <v>-11.58</v>
+      <c r="T29" s="354">
+        <v>-11.24</v>
       </c>
     </row>
     <row r="30">
@@ -9490,7 +9506,7 @@
       <c r="C30" t="str">
         <v>688530</v>
       </c>
-      <c r="D30" s="369" t="str">
+      <c r="D30" s="371" t="str">
         <v>净卖: -1311.39万</v>
       </c>
       <c r="E30">
@@ -9505,41 +9521,41 @@
       <c r="H30">
         <v>-2.23</v>
       </c>
-      <c r="I30" s="373">
+      <c r="I30" s="375">
         <v>15.5</v>
       </c>
-      <c r="J30" s="374">
+      <c r="J30" s="369">
         <v>11.55</v>
       </c>
-      <c r="K30" s="376">
+      <c r="K30" s="366">
         <v>20.14</v>
       </c>
-      <c r="L30" s="377">
+      <c r="L30" s="372">
         <v>15.82</v>
       </c>
-      <c r="M30" s="365">
+      <c r="M30" s="376">
         <v>32.04</v>
       </c>
-      <c r="N30" s="370">
+      <c r="N30" s="377">
         <v>29.72</v>
       </c>
-      <c r="O30" s="366">
+      <c r="O30" s="370">
         <v>28.01</v>
       </c>
-      <c r="P30" s="368">
+      <c r="P30" s="373">
         <v>31.8</v>
       </c>
-      <c r="Q30" s="367">
+      <c r="Q30" s="365">
         <v>58.17</v>
       </c>
-      <c r="R30" s="371">
+      <c r="R30" s="367">
         <v>66.44</v>
       </c>
-      <c r="S30" s="375">
+      <c r="S30" s="374">
         <v>58.53</v>
       </c>
-      <c r="T30" s="372">
-        <v>53.82</v>
+      <c r="T30" s="368">
+        <v>84.58</v>
       </c>
     </row>
     <row r="31">
@@ -9567,41 +9583,41 @@
       <c r="H31">
         <v>-1.06</v>
       </c>
-      <c r="I31" s="383">
+      <c r="I31" s="378">
         <v>21.29</v>
       </c>
-      <c r="J31" s="380">
+      <c r="J31" s="379">
         <v>27.63</v>
       </c>
-      <c r="K31" s="389">
+      <c r="K31" s="386">
         <v>21.57</v>
       </c>
-      <c r="L31" s="390">
+      <c r="L31" s="380">
         <v>13.14</v>
       </c>
-      <c r="M31" s="378">
+      <c r="M31" s="389">
         <v>8.21</v>
       </c>
-      <c r="N31" s="386">
+      <c r="N31" s="382">
         <v>6.59</v>
       </c>
-      <c r="O31" s="384">
+      <c r="O31" s="387">
         <v>1.78</v>
       </c>
-      <c r="P31" s="379">
+      <c r="P31" s="383">
         <v>0.09</v>
       </c>
-      <c r="Q31" s="387">
+      <c r="Q31" s="384">
         <v>6.43</v>
       </c>
       <c r="R31" s="385">
         <v>1.5</v>
       </c>
-      <c r="S31" s="381">
+      <c r="S31" s="390">
         <v>5.55</v>
       </c>
-      <c r="T31" s="382">
-        <v>17.95</v>
+      <c r="T31" s="381">
+        <v>41.54</v>
       </c>
     </row>
     <row r="32">
@@ -9614,7 +9630,7 @@
       <c r="C32" t="str">
         <v>600367</v>
       </c>
-      <c r="D32" s="403" t="str">
+      <c r="D32" s="393" t="str">
         <v>净买: 7875.30万</v>
       </c>
       <c r="E32">
@@ -9629,41 +9645,41 @@
       <c r="H32">
         <v>6.88</v>
       </c>
-      <c r="I32" s="391">
+      <c r="I32" s="398">
         <v>2.94</v>
       </c>
-      <c r="J32" s="392">
+      <c r="J32" s="400">
         <v>-0.72</v>
       </c>
       <c r="K32" s="401">
         <v>-2.86</v>
       </c>
-      <c r="L32" s="395">
+      <c r="L32" s="391">
         <v>-5.36</v>
       </c>
-      <c r="M32" s="396">
+      <c r="M32" s="394">
         <v>-7.83</v>
       </c>
-      <c r="N32" s="397">
+      <c r="N32" s="395">
         <v>-11.24</v>
       </c>
-      <c r="O32" s="398">
+      <c r="O32" s="396">
         <v>-9.85</v>
       </c>
-      <c r="P32" s="393">
+      <c r="P32" s="392">
         <v>-6.2</v>
       </c>
-      <c r="Q32" s="399">
+      <c r="Q32" s="402">
         <v>-1.47</v>
       </c>
-      <c r="R32" s="402">
+      <c r="R32" s="403">
         <v>6.52</v>
       </c>
-      <c r="S32" s="400">
+      <c r="S32" s="397">
         <v>13.79</v>
       </c>
-      <c r="T32" s="394">
-        <v>-9.93</v>
+      <c r="T32" s="399">
+        <v>-13.79</v>
       </c>
     </row>
     <row r="33">
@@ -9676,7 +9692,7 @@
       <c r="C33" t="str">
         <v>600516</v>
       </c>
-      <c r="D33" s="414" t="str">
+      <c r="D33" s="413" t="str">
         <v>净卖: -4735.13万</v>
       </c>
       <c r="E33">
@@ -9691,41 +9707,41 @@
       <c r="H33">
         <v>0.8</v>
       </c>
-      <c r="I33" s="415">
+      <c r="I33" s="407">
         <v>9.21</v>
       </c>
-      <c r="J33" s="408">
+      <c r="J33" s="414">
         <v>6.83</v>
       </c>
-      <c r="K33" s="412">
+      <c r="K33" s="416">
         <v>5.87</v>
       </c>
-      <c r="L33" s="409">
+      <c r="L33" s="404">
         <v>7.46</v>
       </c>
-      <c r="M33" s="416">
+      <c r="M33" s="408">
         <v>10.32</v>
       </c>
-      <c r="N33" s="413">
+      <c r="N33" s="409">
         <v>12.86</v>
       </c>
-      <c r="O33" s="410">
+      <c r="O33" s="411">
         <v>7.3</v>
       </c>
-      <c r="P33" s="411">
+      <c r="P33" s="410">
         <v>4.92</v>
       </c>
-      <c r="Q33" s="404">
+      <c r="Q33" s="405">
         <v>1.11</v>
       </c>
-      <c r="R33" s="405">
+      <c r="R33" s="406">
         <v>-1.59</v>
       </c>
-      <c r="S33" s="406">
+      <c r="S33" s="412">
         <v>-5.24</v>
       </c>
-      <c r="T33" s="407">
-        <v>-12.22</v>
+      <c r="T33" s="415">
+        <v>-14.29</v>
       </c>
     </row>
     <row r="34">
@@ -9738,7 +9754,7 @@
       <c r="C34" t="str">
         <v>300131</v>
       </c>
-      <c r="D34" s="417" t="str">
+      <c r="D34" s="429" t="str">
         <v>净卖: -9057.02万</v>
       </c>
       <c r="E34">
@@ -9756,38 +9772,38 @@
       <c r="I34" s="424">
         <v>-18.81</v>
       </c>
-      <c r="J34" s="427">
+      <c r="J34" s="419">
         <v>-16.59</v>
       </c>
-      <c r="K34" s="418">
+      <c r="K34" s="427">
         <v>-10.32</v>
       </c>
-      <c r="L34" s="421">
+      <c r="L34" s="420">
         <v>-11.8</v>
       </c>
-      <c r="M34" s="425">
+      <c r="M34" s="421">
         <v>-16.08</v>
       </c>
-      <c r="N34" s="419">
+      <c r="N34" s="422">
         <v>-14.6</v>
       </c>
-      <c r="O34" s="422">
+      <c r="O34" s="428">
         <v>-17.4</v>
       </c>
-      <c r="P34" s="428">
+      <c r="P34" s="425">
         <v>-16.22</v>
       </c>
-      <c r="Q34" s="420">
+      <c r="Q34" s="417">
         <v>-16.74</v>
       </c>
-      <c r="R34" s="429">
+      <c r="R34" s="426">
         <v>-9.44</v>
       </c>
-      <c r="S34" s="426">
+      <c r="S34" s="418">
         <v>-5.24</v>
       </c>
       <c r="T34" s="423">
-        <v>20.06</v>
+        <v>26.92</v>
       </c>
     </row>
     <row r="35">
@@ -9800,7 +9816,7 @@
       <c r="C35" t="str">
         <v>603189</v>
       </c>
-      <c r="D35" s="436" t="str">
+      <c r="D35" s="434" t="str">
         <v>净买: 91.85万</v>
       </c>
       <c r="E35">
@@ -9815,29 +9831,31 @@
       <c r="H35">
         <v>-9.97</v>
       </c>
-      <c r="I35" s="430">
+      <c r="I35" s="435">
         <v>0</v>
       </c>
-      <c r="J35" s="431">
+      <c r="J35" s="436">
         <v>3.42</v>
       </c>
-      <c r="K35" s="432">
+      <c r="K35" s="437">
         <v>-6.85</v>
       </c>
-      <c r="L35" s="433">
+      <c r="L35" s="430">
         <v>-8.23</v>
       </c>
-      <c r="M35" s="434">
+      <c r="M35" s="431">
         <v>-8.01</v>
       </c>
-      <c r="N35" t="str"/>
+      <c r="N35" s="432">
+        <v>-9.61</v>
+      </c>
       <c r="O35" t="str"/>
       <c r="P35" t="str"/>
       <c r="Q35" t="str"/>
       <c r="R35" t="str"/>
       <c r="S35" t="str"/>
-      <c r="T35" s="435">
-        <v>-8.01</v>
+      <c r="T35" s="433">
+        <v>-9.61</v>
       </c>
     </row>
     <row r="36">
@@ -9867,7 +9885,7 @@
         <v>34</v>
       </c>
       <c r="N36">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O36">
         <v>33</v>
@@ -9899,41 +9917,41 @@
       <c r="F37" t="str"/>
       <c r="G37" t="str"/>
       <c r="H37" t="str"/>
-      <c r="I37" s="441">
+      <c r="I37" s="445">
         <v>52.94</v>
       </c>
-      <c r="J37" s="438">
+      <c r="J37" s="439">
         <v>58.82</v>
       </c>
-      <c r="K37" s="442">
+      <c r="K37" s="447">
         <v>50</v>
       </c>
-      <c r="L37" s="447">
+      <c r="L37" s="448">
         <v>52.94</v>
       </c>
-      <c r="M37" s="439">
+      <c r="M37" s="440">
         <v>58.82</v>
       </c>
       <c r="N37" s="443">
-        <v>57.58</v>
-      </c>
-      <c r="O37" s="440">
+        <v>55.88</v>
+      </c>
+      <c r="O37" s="446">
         <v>54.55</v>
       </c>
-      <c r="P37" s="448">
+      <c r="P37" s="449">
         <v>54.55</v>
       </c>
-      <c r="Q37" s="445">
+      <c r="Q37" s="441">
         <v>51.52</v>
       </c>
       <c r="R37" s="444">
         <v>45.45</v>
       </c>
-      <c r="S37" s="446">
+      <c r="S37" s="442">
         <v>45.45</v>
       </c>
-      <c r="T37" s="437">
-        <v>44.12</v>
+      <c r="T37" s="438">
+        <v>41.18</v>
       </c>
     </row>
     <row r="38">
@@ -9947,41 +9965,41 @@
       <c r="F38" t="str"/>
       <c r="G38" t="str"/>
       <c r="H38" t="str"/>
-      <c r="I38" s="452">
+      <c r="I38" s="458">
         <v>2.64</v>
       </c>
-      <c r="J38" s="458">
+      <c r="J38" s="454">
         <v>3.67</v>
       </c>
-      <c r="K38" s="456">
+      <c r="K38" s="451">
         <v>2.87</v>
       </c>
-      <c r="L38" s="453">
+      <c r="L38" s="455">
         <v>3.91</v>
       </c>
       <c r="M38" s="459">
         <v>4.02</v>
       </c>
-      <c r="N38" s="457">
-        <v>2.62</v>
-      </c>
-      <c r="O38" s="449">
+      <c r="N38" s="452">
+        <v>2.26</v>
+      </c>
+      <c r="O38" s="460">
         <v>1.54</v>
       </c>
-      <c r="P38" s="454">
+      <c r="P38" s="461">
         <v>1.8</v>
       </c>
-      <c r="Q38" s="460">
+      <c r="Q38" s="456">
         <v>2.18</v>
       </c>
-      <c r="R38" s="450">
+      <c r="R38" s="453">
         <v>1.38</v>
       </c>
-      <c r="S38" s="455">
+      <c r="S38" s="450">
         <v>1.44</v>
       </c>
-      <c r="T38" s="451">
-        <v>22.47</v>
+      <c r="T38" s="457">
+        <v>23.32</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/新生代/index.xlsx
+++ b/youzi/新生代/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="463">
+  <fills count="464">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,6 +39,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF24993F"/>
         <bgColor/>
       </patternFill>
@@ -51,25 +63,2287 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF29A746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E0BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1E8035"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8B94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D0D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D0D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF8F0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF79C88B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1C7A33"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF82CB93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1E2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35D6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB5E0BF"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF35AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAADCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1ECD7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3FB059"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C1C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8993"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3606D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3646"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0ECD7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA4AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -81,19 +2355,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8891"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF29A746"/>
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -105,12 +2475,126 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE3C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -129,289 +2613,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8B94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -423,7 +2661,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C3C8"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -435,61 +2679,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFF4C3C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8891"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C3C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD6AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD6AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -501,2310 +2805,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D0D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D0D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF71C584"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF8F0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF79C88B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1E2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAADCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1ECD7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF35AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C1C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3FB059"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8993"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3646"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3606D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0ECD7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8891"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBAE3C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8891"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C3C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C3C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4636F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
+        <fgColor rgb="FFE87A85"/>
         <bgColor/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="462">
+  <borders count="463">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -6043,7 +6056,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="462">
+  <cellXfs count="463">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -7426,6 +7439,9 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="461" fillId="462" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="462" fillId="463" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -7770,7 +7786,7 @@
       <c r="C2" t="str">
         <v>002238</v>
       </c>
-      <c r="D2" s="13" t="str">
+      <c r="D2" s="1" t="str">
         <v>净卖: -808.36万</v>
       </c>
       <c r="E2">
@@ -7785,41 +7801,41 @@
       <c r="H2">
         <v>4.28</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="2">
         <v>5.53</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="6">
         <v>-4.96</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="9">
         <v>-1.72</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="3">
         <v>-6.11</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="4">
         <v>-6.87</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="11">
         <v>-8.3</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O2" s="10">
         <v>-8.78</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="7">
         <v>-12.21</v>
       </c>
       <c r="Q2" s="8">
         <v>-13.17</v>
       </c>
-      <c r="R2" s="11">
+      <c r="R2" s="12">
         <v>-14.03</v>
       </c>
-      <c r="S2" s="9">
+      <c r="S2" s="5">
         <v>-13.84</v>
       </c>
-      <c r="T2" s="12">
-        <v>-31.97</v>
+      <c r="T2" s="13">
+        <v>-33.02</v>
       </c>
     </row>
     <row r="3">
@@ -7832,7 +7848,7 @@
       <c r="C3" t="str">
         <v>002238</v>
       </c>
-      <c r="D3" s="18" t="str">
+      <c r="D3" s="15" t="str">
         <v>净卖: -1634.66万</v>
       </c>
       <c r="E3">
@@ -7850,38 +7866,38 @@
       <c r="I3" s="23">
         <v>-9.45</v>
       </c>
-      <c r="J3" s="26">
+      <c r="J3" s="16">
         <v>-6.36</v>
       </c>
-      <c r="K3" s="24">
+      <c r="K3" s="20">
         <v>-10.55</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="24">
         <v>-11.27</v>
       </c>
-      <c r="M3" s="20">
+      <c r="M3" s="17">
         <v>-12.64</v>
       </c>
-      <c r="N3" s="16">
+      <c r="N3" s="25">
         <v>-13.09</v>
       </c>
       <c r="O3" s="21">
         <v>-16.36</v>
       </c>
-      <c r="P3" s="22">
+      <c r="P3" s="18">
         <v>-17.27</v>
       </c>
-      <c r="Q3" s="14">
+      <c r="Q3" s="22">
         <v>-18.09</v>
       </c>
-      <c r="R3" s="25">
+      <c r="R3" s="19">
         <v>-17.91</v>
       </c>
-      <c r="S3" s="17">
+      <c r="S3" s="26">
         <v>-17.55</v>
       </c>
-      <c r="T3" s="15">
-        <v>-35.18</v>
+      <c r="T3" s="14">
+        <v>-36.18</v>
       </c>
     </row>
     <row r="4">
@@ -7894,7 +7910,7 @@
       <c r="C4" t="str">
         <v>600540</v>
       </c>
-      <c r="D4" s="38" t="str">
+      <c r="D4" s="30" t="str">
         <v>净卖: -203.46万</v>
       </c>
       <c r="E4">
@@ -7909,41 +7925,41 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" s="39">
+      <c r="I4" s="35">
         <v>10.08</v>
       </c>
-      <c r="J4" s="34">
+      <c r="J4" s="36">
         <v>21.19</v>
       </c>
-      <c r="K4" s="27">
+      <c r="K4" s="37">
         <v>33.33</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="39">
         <v>46.77</v>
       </c>
-      <c r="M4" s="35">
+      <c r="M4" s="27">
         <v>61.5</v>
       </c>
-      <c r="N4" s="29">
+      <c r="N4" s="31">
         <v>45.48</v>
       </c>
-      <c r="O4" s="30">
+      <c r="O4" s="32">
         <v>53.23</v>
       </c>
-      <c r="P4" s="36">
+      <c r="P4" s="33">
         <v>58.66</v>
       </c>
-      <c r="Q4" s="31">
+      <c r="Q4" s="28">
         <v>51.94</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="29">
         <v>36.69</v>
       </c>
-      <c r="S4" s="37">
+      <c r="S4" s="34">
         <v>23</v>
       </c>
-      <c r="T4" s="33">
-        <v>29.72</v>
+      <c r="T4" s="38">
+        <v>26.36</v>
       </c>
     </row>
     <row r="5">
@@ -7956,7 +7972,7 @@
       <c r="C5" t="str">
         <v>002041</v>
       </c>
-      <c r="D5" s="43" t="str">
+      <c r="D5" s="47" t="str">
         <v>净卖: -388.51万</v>
       </c>
       <c r="E5">
@@ -7971,41 +7987,41 @@
       <c r="H5">
         <v>4.75</v>
       </c>
-      <c r="I5" s="48">
+      <c r="I5" s="43">
         <v>4.91</v>
       </c>
-      <c r="J5" s="49">
+      <c r="J5" s="52">
         <v>15.37</v>
       </c>
-      <c r="K5" s="50">
+      <c r="K5" s="48">
         <v>10.56</v>
       </c>
-      <c r="L5" s="52">
+      <c r="L5" s="44">
         <v>11.76</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="40">
         <v>4.07</v>
       </c>
-      <c r="N5" s="47">
+      <c r="N5" s="49">
         <v>5.09</v>
       </c>
-      <c r="O5" s="40">
+      <c r="O5" s="45">
         <v>2.87</v>
       </c>
-      <c r="P5" s="45">
+      <c r="P5" s="41">
         <v>0.56</v>
       </c>
-      <c r="Q5" s="51">
+      <c r="Q5" s="50">
         <v>0.19</v>
       </c>
-      <c r="R5" s="41">
+      <c r="R5" s="51">
         <v>-3.15</v>
       </c>
       <c r="S5" s="46">
         <v>-2.31</v>
       </c>
       <c r="T5" s="42">
-        <v>-11.57</v>
+        <v>-8.06</v>
       </c>
     </row>
     <row r="6">
@@ -8033,41 +8049,41 @@
       <c r="H6">
         <v>9.99</v>
       </c>
-      <c r="I6" s="64">
+      <c r="I6" s="61">
         <v>0</v>
       </c>
-      <c r="J6" s="65">
+      <c r="J6" s="62">
         <v>-9.94</v>
       </c>
-      <c r="K6" s="59">
+      <c r="K6" s="63">
         <v>-12.52</v>
       </c>
-      <c r="L6" s="53">
+      <c r="L6" s="59">
         <v>-3.79</v>
       </c>
-      <c r="M6" s="60">
+      <c r="M6" s="54">
         <v>-1.89</v>
       </c>
-      <c r="N6" s="54">
+      <c r="N6" s="55">
         <v>-5.64</v>
       </c>
-      <c r="O6" s="55">
+      <c r="O6" s="64">
         <v>-7.27</v>
       </c>
-      <c r="P6" s="61">
+      <c r="P6" s="60">
         <v>-8.13</v>
       </c>
-      <c r="Q6" s="56">
+      <c r="Q6" s="65">
         <v>-8.91</v>
       </c>
-      <c r="R6" s="57">
+      <c r="R6" s="53">
         <v>-8.61</v>
       </c>
-      <c r="S6" s="62">
+      <c r="S6" s="56">
         <v>-5.85</v>
       </c>
-      <c r="T6" s="63">
-        <v>22.2</v>
+      <c r="T6" s="57">
+        <v>25.69</v>
       </c>
     </row>
     <row r="7">
@@ -8095,41 +8111,41 @@
       <c r="H7">
         <v>-10.01</v>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="67">
         <v>0</v>
       </c>
-      <c r="J7" s="68">
+      <c r="J7" s="73">
         <v>4.02</v>
       </c>
-      <c r="K7" s="67">
+      <c r="K7" s="68">
         <v>2.06</v>
       </c>
-      <c r="L7" s="73">
+      <c r="L7" s="74">
         <v>3.75</v>
       </c>
       <c r="M7" s="69">
         <v>7.52</v>
       </c>
-      <c r="N7" s="70">
+      <c r="N7" s="66">
         <v>6.86</v>
       </c>
-      <c r="O7" s="71">
+      <c r="O7" s="70">
         <v>11.67</v>
       </c>
-      <c r="P7" s="74">
+      <c r="P7" s="75">
         <v>9.4</v>
       </c>
-      <c r="Q7" s="76">
+      <c r="Q7" s="71">
         <v>11.63</v>
       </c>
-      <c r="R7" s="72">
+      <c r="R7" s="77">
         <v>11.12</v>
       </c>
-      <c r="S7" s="77">
+      <c r="S7" s="72">
         <v>9.79</v>
       </c>
-      <c r="T7" s="75">
-        <v>341.86</v>
+      <c r="T7" s="76">
+        <v>334.21</v>
       </c>
     </row>
     <row r="8">
@@ -8142,7 +8158,7 @@
       <c r="C8" t="str">
         <v>002510</v>
       </c>
-      <c r="D8" s="89" t="str">
+      <c r="D8" s="84" t="str">
         <v>净卖: -764.76万</v>
       </c>
       <c r="E8">
@@ -8157,41 +8173,41 @@
       <c r="H8">
         <v>10.06</v>
       </c>
-      <c r="I8" s="90">
+      <c r="I8" s="86">
         <v>0</v>
       </c>
-      <c r="J8" s="85">
+      <c r="J8" s="88">
         <v>10</v>
       </c>
-      <c r="K8" s="87">
+      <c r="K8" s="89">
         <v>21</v>
       </c>
-      <c r="L8" s="91">
+      <c r="L8" s="90">
         <v>17.57</v>
       </c>
-      <c r="M8" s="81">
+      <c r="M8" s="87">
         <v>5.86</v>
       </c>
-      <c r="N8" s="82">
+      <c r="N8" s="80">
         <v>1.57</v>
       </c>
-      <c r="O8" s="86">
+      <c r="O8" s="81">
         <v>3.57</v>
       </c>
-      <c r="P8" s="79">
+      <c r="P8" s="82">
         <v>1.14</v>
       </c>
-      <c r="Q8" s="83">
+      <c r="Q8" s="85">
         <v>1.14</v>
       </c>
-      <c r="R8" s="80">
+      <c r="R8" s="83">
         <v>-4.57</v>
       </c>
-      <c r="S8" s="88">
+      <c r="S8" s="91">
         <v>-2.71</v>
       </c>
-      <c r="T8" s="84">
-        <v>-3.29</v>
+      <c r="T8" s="79">
+        <v>-6.14</v>
       </c>
     </row>
     <row r="9">
@@ -8204,7 +8220,7 @@
       <c r="C9" t="str">
         <v>600367</v>
       </c>
-      <c r="D9" s="94" t="str">
+      <c r="D9" s="93" t="str">
         <v>净买: 3583.76万</v>
       </c>
       <c r="E9">
@@ -8219,41 +8235,41 @@
       <c r="H9">
         <v>4.52</v>
       </c>
-      <c r="I9" s="104">
+      <c r="I9" s="99">
         <v>-0.98</v>
       </c>
-      <c r="J9" s="95">
+      <c r="J9" s="100">
         <v>-4.07</v>
       </c>
-      <c r="K9" s="96">
+      <c r="K9" s="101">
         <v>-0.39</v>
       </c>
-      <c r="L9" s="102">
+      <c r="L9" s="94">
         <v>5.44</v>
       </c>
-      <c r="M9" s="97">
+      <c r="M9" s="102">
         <v>5.18</v>
       </c>
-      <c r="N9" s="98">
+      <c r="N9" s="103">
         <v>12.52</v>
       </c>
-      <c r="O9" s="99">
+      <c r="O9" s="95">
         <v>1.25</v>
       </c>
-      <c r="P9" s="92">
+      <c r="P9" s="104">
         <v>11.34</v>
       </c>
-      <c r="Q9" s="93">
+      <c r="Q9" s="96">
         <v>4.07</v>
       </c>
-      <c r="R9" s="101">
+      <c r="R9" s="97">
         <v>0.26</v>
       </c>
-      <c r="S9" s="100">
+      <c r="S9" s="98">
         <v>2.89</v>
       </c>
-      <c r="T9" s="103">
-        <v>42.3</v>
+      <c r="T9" s="92">
+        <v>38.43</v>
       </c>
     </row>
     <row r="10">
@@ -8266,7 +8282,7 @@
       <c r="C10" t="str">
         <v>603585</v>
       </c>
-      <c r="D10" s="105" t="str">
+      <c r="D10" s="110" t="str">
         <v>净买: 620.83万</v>
       </c>
       <c r="E10">
@@ -8281,41 +8297,41 @@
       <c r="H10">
         <v>-7.49</v>
       </c>
-      <c r="I10" s="109">
+      <c r="I10" s="114">
         <v>-2.7</v>
       </c>
-      <c r="J10" s="110">
+      <c r="J10" s="111">
         <v>-7</v>
       </c>
-      <c r="K10" s="106">
+      <c r="K10" s="117">
         <v>-4.8</v>
       </c>
-      <c r="L10" s="116">
+      <c r="L10" s="115">
         <v>-5.45</v>
       </c>
-      <c r="M10" s="112">
+      <c r="M10" s="105">
         <v>-7.65</v>
       </c>
-      <c r="N10" s="113">
+      <c r="N10" s="108">
         <v>-8.8</v>
       </c>
-      <c r="O10" s="107">
+      <c r="O10" s="116">
         <v>-8.55</v>
       </c>
-      <c r="P10" s="117">
+      <c r="P10" s="112">
         <v>-7.55</v>
       </c>
-      <c r="Q10" s="114">
+      <c r="Q10" s="106">
         <v>-1.95</v>
       </c>
-      <c r="R10" s="108">
+      <c r="R10" s="107">
         <v>-3.1</v>
       </c>
-      <c r="S10" s="115">
+      <c r="S10" s="113">
         <v>6.6</v>
       </c>
-      <c r="T10" s="111">
-        <v>-2.4</v>
+      <c r="T10" s="109">
+        <v>-2.9</v>
       </c>
     </row>
     <row r="11">
@@ -8328,7 +8344,7 @@
       <c r="C11" t="str">
         <v>600962</v>
       </c>
-      <c r="D11" s="124" t="str">
+      <c r="D11" s="129" t="str">
         <v>净卖: -17.88万</v>
       </c>
       <c r="E11">
@@ -8343,41 +8359,41 @@
       <c r="H11">
         <v>10.03</v>
       </c>
-      <c r="I11" s="125">
+      <c r="I11" s="119">
         <v>0</v>
       </c>
       <c r="J11" s="121">
         <v>10.01</v>
       </c>
-      <c r="K11" s="119">
+      <c r="K11" s="120">
         <v>21.03</v>
       </c>
-      <c r="L11" s="126">
+      <c r="L11" s="122">
         <v>19.13</v>
       </c>
-      <c r="M11" s="130">
+      <c r="M11" s="123">
         <v>9.62</v>
       </c>
-      <c r="N11" s="120">
+      <c r="N11" s="130">
         <v>16.33</v>
       </c>
-      <c r="O11" s="127">
+      <c r="O11" s="124">
         <v>18.74</v>
       </c>
       <c r="P11" s="118">
         <v>18.01</v>
       </c>
-      <c r="Q11" s="128">
+      <c r="Q11" s="127">
         <v>14.09</v>
       </c>
-      <c r="R11" s="122">
+      <c r="R11" s="125">
         <v>10.91</v>
       </c>
-      <c r="S11" s="129">
+      <c r="S11" s="126">
         <v>10.29</v>
       </c>
-      <c r="T11" s="123">
-        <v>16.33</v>
+      <c r="T11" s="128">
+        <v>18.12</v>
       </c>
     </row>
     <row r="12">
@@ -8390,7 +8406,7 @@
       <c r="C12" t="str">
         <v>003037</v>
       </c>
-      <c r="D12" s="142" t="str">
+      <c r="D12" s="141" t="str">
         <v>净卖: -2233.11万</v>
       </c>
       <c r="E12">
@@ -8405,41 +8421,41 @@
       <c r="H12">
         <v>4.89</v>
       </c>
-      <c r="I12" s="138">
+      <c r="I12" s="142">
         <v>4.88</v>
       </c>
-      <c r="J12" s="134">
+      <c r="J12" s="135">
         <v>8.77</v>
       </c>
-      <c r="K12" s="135">
+      <c r="K12" s="131">
         <v>-1.89</v>
       </c>
-      <c r="L12" s="143">
+      <c r="L12" s="138">
         <v>-3.22</v>
       </c>
-      <c r="M12" s="136">
+      <c r="M12" s="139">
         <v>6.44</v>
       </c>
-      <c r="N12" s="132">
+      <c r="N12" s="136">
         <v>17.09</v>
       </c>
-      <c r="O12" s="133">
+      <c r="O12" s="132">
         <v>16.09</v>
       </c>
-      <c r="P12" s="139">
+      <c r="P12" s="137">
         <v>14.32</v>
       </c>
-      <c r="Q12" s="137">
+      <c r="Q12" s="133">
         <v>4.88</v>
       </c>
-      <c r="R12" s="140">
+      <c r="R12" s="143">
         <v>3.77</v>
       </c>
-      <c r="S12" s="141">
+      <c r="S12" s="134">
         <v>4</v>
       </c>
-      <c r="T12" s="131">
-        <v>-20.42</v>
+      <c r="T12" s="140">
+        <v>-19.98</v>
       </c>
     </row>
     <row r="13">
@@ -8452,7 +8468,7 @@
       <c r="C13" t="str">
         <v>001306</v>
       </c>
-      <c r="D13" s="148" t="str">
+      <c r="D13" s="151" t="str">
         <v>净卖: -462.25万</v>
       </c>
       <c r="E13">
@@ -8467,41 +8483,41 @@
       <c r="H13">
         <v>0.03</v>
       </c>
-      <c r="I13" s="149">
+      <c r="I13" s="147">
         <v>6.62</v>
       </c>
-      <c r="J13" s="156">
+      <c r="J13" s="152">
         <v>17.29</v>
       </c>
-      <c r="K13" s="144">
+      <c r="K13" s="155">
         <v>22.79</v>
       </c>
-      <c r="L13" s="150">
+      <c r="L13" s="148">
         <v>28.15</v>
       </c>
-      <c r="M13" s="151">
+      <c r="M13" s="153">
         <v>23.18</v>
       </c>
-      <c r="N13" s="145">
+      <c r="N13" s="154">
         <v>22.64</v>
       </c>
-      <c r="O13" s="146">
+      <c r="O13" s="144">
         <v>27.89</v>
       </c>
-      <c r="P13" s="152">
+      <c r="P13" s="145">
         <v>23.34</v>
       </c>
-      <c r="Q13" s="147">
+      <c r="Q13" s="156">
         <v>24.33</v>
       </c>
-      <c r="R13" s="153">
+      <c r="R13" s="146">
         <v>22.68</v>
       </c>
-      <c r="S13" s="154">
+      <c r="S13" s="149">
         <v>28.62</v>
       </c>
-      <c r="T13" s="155">
-        <v>-10.55</v>
+      <c r="T13" s="150">
+        <v>-13.38</v>
       </c>
     </row>
     <row r="14">
@@ -8514,7 +8530,7 @@
       <c r="C14" t="str">
         <v>002953</v>
       </c>
-      <c r="D14" s="162" t="str">
+      <c r="D14" s="164" t="str">
         <v>净卖: -867.00万</v>
       </c>
       <c r="E14">
@@ -8529,41 +8545,41 @@
       <c r="H14">
         <v>-2.07</v>
       </c>
-      <c r="I14" s="167">
+      <c r="I14" s="166">
         <v>12.29</v>
       </c>
-      <c r="J14" s="168">
+      <c r="J14" s="161">
         <v>17.19</v>
       </c>
       <c r="K14" s="169">
         <v>10.41</v>
       </c>
-      <c r="L14" s="163">
+      <c r="L14" s="157">
         <v>21.42</v>
       </c>
-      <c r="M14" s="164">
+      <c r="M14" s="162">
         <v>15.91</v>
       </c>
-      <c r="N14" s="165">
+      <c r="N14" s="158">
         <v>4.3</v>
       </c>
-      <c r="O14" s="157">
+      <c r="O14" s="163">
         <v>-1.96</v>
       </c>
-      <c r="P14" s="159">
+      <c r="P14" s="165">
         <v>-1.06</v>
       </c>
-      <c r="Q14" s="158">
+      <c r="Q14" s="159">
         <v>-0.75</v>
       </c>
-      <c r="R14" s="160">
+      <c r="R14" s="167">
         <v>-0.98</v>
       </c>
-      <c r="S14" s="166">
+      <c r="S14" s="160">
         <v>-4.68</v>
       </c>
-      <c r="T14" s="161">
-        <v>-9.35</v>
+      <c r="T14" s="168">
+        <v>-10.63</v>
       </c>
     </row>
     <row r="15">
@@ -8576,7 +8592,7 @@
       <c r="C15" t="str">
         <v>605133</v>
       </c>
-      <c r="D15" s="172" t="str">
+      <c r="D15" s="175" t="str">
         <v>净买: 3043.68万</v>
       </c>
       <c r="E15">
@@ -8591,41 +8607,41 @@
       <c r="H15">
         <v>-0.11</v>
       </c>
-      <c r="I15" s="181">
+      <c r="I15" s="172">
         <v>10.11</v>
       </c>
-      <c r="J15" s="174">
+      <c r="J15" s="173">
         <v>6.15</v>
       </c>
-      <c r="K15" s="175">
+      <c r="K15" s="176">
         <v>-4.46</v>
       </c>
-      <c r="L15" s="182">
+      <c r="L15" s="177">
         <v>-0.27</v>
       </c>
-      <c r="M15" s="176">
+      <c r="M15" s="181">
         <v>3.14</v>
       </c>
-      <c r="N15" s="173">
+      <c r="N15" s="182">
         <v>1.53</v>
       </c>
-      <c r="O15" s="177">
+      <c r="O15" s="170">
         <v>-1.62</v>
       </c>
-      <c r="P15" s="178">
+      <c r="P15" s="171">
         <v>-0.46</v>
       </c>
-      <c r="Q15" s="179">
+      <c r="Q15" s="178">
         <v>-2.94</v>
       </c>
-      <c r="R15" s="170">
+      <c r="R15" s="179">
         <v>-0.55</v>
       </c>
-      <c r="S15" s="180">
+      <c r="S15" s="174">
         <v>9.41</v>
       </c>
-      <c r="T15" s="171">
-        <v>-29.02</v>
+      <c r="T15" s="180">
+        <v>-30.96</v>
       </c>
     </row>
     <row r="16">
@@ -8638,7 +8654,7 @@
       <c r="C16" t="str">
         <v>301533</v>
       </c>
-      <c r="D16" s="188" t="str">
+      <c r="D16" s="195" t="str">
         <v>净卖: -733.04万</v>
       </c>
       <c r="E16">
@@ -8653,41 +8669,41 @@
       <c r="H16">
         <v>2.26</v>
       </c>
-      <c r="I16" s="191">
+      <c r="I16" s="189">
         <v>3.46</v>
       </c>
-      <c r="J16" s="189">
+      <c r="J16" s="183">
         <v>8.33</v>
       </c>
-      <c r="K16" s="190">
+      <c r="K16" s="186">
         <v>10.64</v>
       </c>
-      <c r="L16" s="192">
+      <c r="L16" s="187">
         <v>7.14</v>
       </c>
-      <c r="M16" s="184">
+      <c r="M16" s="190">
         <v>11.64</v>
       </c>
-      <c r="N16" s="185">
+      <c r="N16" s="193">
         <v>6.19</v>
       </c>
-      <c r="O16" s="186">
+      <c r="O16" s="188">
         <v>3.76</v>
       </c>
-      <c r="P16" s="187">
+      <c r="P16" s="194">
         <v>0.97</v>
       </c>
-      <c r="Q16" s="193">
+      <c r="Q16" s="191">
         <v>-1.04</v>
       </c>
-      <c r="R16" s="194">
+      <c r="R16" s="184">
         <v>-2.01</v>
       </c>
-      <c r="S16" s="195">
+      <c r="S16" s="185">
         <v>-5.7</v>
       </c>
-      <c r="T16" s="183">
-        <v>-18.45</v>
+      <c r="T16" s="192">
+        <v>-20.37</v>
       </c>
     </row>
     <row r="17">
@@ -8700,7 +8716,7 @@
       <c r="C17" t="str">
         <v>688148</v>
       </c>
-      <c r="D17" s="198" t="str">
+      <c r="D17" s="205" t="str">
         <v>净卖: -1051.47万</v>
       </c>
       <c r="E17">
@@ -8715,13 +8731,13 @@
       <c r="H17">
         <v>4.34</v>
       </c>
-      <c r="I17" s="207">
+      <c r="I17" s="202">
         <v>15.03</v>
       </c>
       <c r="J17" s="208">
         <v>37.63</v>
       </c>
-      <c r="K17" s="204">
+      <c r="K17" s="203">
         <v>33.37</v>
       </c>
       <c r="L17" s="199">
@@ -8730,26 +8746,26 @@
       <c r="M17" s="200">
         <v>29</v>
       </c>
-      <c r="N17" s="205">
+      <c r="N17" s="206">
         <v>24.95</v>
       </c>
-      <c r="O17" s="196">
+      <c r="O17" s="204">
         <v>20.36</v>
       </c>
-      <c r="P17" s="206">
+      <c r="P17" s="201">
         <v>18.44</v>
       </c>
-      <c r="Q17" s="201">
+      <c r="Q17" s="196">
         <v>13.11</v>
       </c>
       <c r="R17" s="197">
         <v>1.49</v>
       </c>
-      <c r="S17" s="203">
+      <c r="S17" s="207">
         <v>-1.39</v>
       </c>
-      <c r="T17" s="202">
-        <v>9.49</v>
+      <c r="T17" s="198">
+        <v>7.68</v>
       </c>
     </row>
     <row r="18">
@@ -8762,7 +8778,7 @@
       <c r="C18" t="str">
         <v>688148</v>
       </c>
-      <c r="D18" s="221" t="str">
+      <c r="D18" s="218" t="str">
         <v>净卖: -2325.34万</v>
       </c>
       <c r="E18">
@@ -8777,41 +8793,41 @@
       <c r="H18">
         <v>5.56</v>
       </c>
-      <c r="I18" s="209">
+      <c r="I18" s="212">
         <v>13.35</v>
       </c>
       <c r="J18" s="213">
         <v>9.83</v>
       </c>
-      <c r="K18" s="219">
+      <c r="K18" s="221">
         <v>10.27</v>
       </c>
       <c r="L18" s="214">
         <v>6.23</v>
       </c>
-      <c r="M18" s="211">
+      <c r="M18" s="209">
         <v>2.9</v>
       </c>
-      <c r="N18" s="215">
+      <c r="N18" s="219">
         <v>-0.88</v>
       </c>
-      <c r="O18" s="212">
+      <c r="O18" s="215">
         <v>-2.46</v>
       </c>
-      <c r="P18" s="220">
+      <c r="P18" s="216">
         <v>-6.85</v>
       </c>
-      <c r="Q18" s="216">
+      <c r="Q18" s="210">
         <v>-16.42</v>
       </c>
-      <c r="R18" s="210">
+      <c r="R18" s="211">
         <v>-18.79</v>
       </c>
       <c r="S18" s="217">
         <v>-16.86</v>
       </c>
-      <c r="T18" s="218">
-        <v>-9.83</v>
+      <c r="T18" s="220">
+        <v>-11.33</v>
       </c>
     </row>
     <row r="19">
@@ -8824,7 +8840,7 @@
       <c r="C19" t="str">
         <v>002506</v>
       </c>
-      <c r="D19" s="223" t="str">
+      <c r="D19" s="222" t="str">
         <v>净卖: -1046.77万</v>
       </c>
       <c r="E19">
@@ -8839,41 +8855,41 @@
       <c r="H19">
         <v>1.86</v>
       </c>
-      <c r="I19" s="231">
+      <c r="I19" s="228">
         <v>8.03</v>
       </c>
-      <c r="J19" s="224">
+      <c r="J19" s="229">
         <v>14.23</v>
       </c>
-      <c r="K19" s="225">
+      <c r="K19" s="223">
         <v>15.69</v>
       </c>
-      <c r="L19" s="232">
+      <c r="L19" s="230">
         <v>17.52</v>
       </c>
-      <c r="M19" s="233">
+      <c r="M19" s="224">
         <v>14.6</v>
       </c>
-      <c r="N19" s="226">
+      <c r="N19" s="232">
         <v>8.39</v>
       </c>
-      <c r="O19" s="234">
+      <c r="O19" s="233">
         <v>4.74</v>
       </c>
-      <c r="P19" s="230">
+      <c r="P19" s="225">
         <v>1.46</v>
       </c>
-      <c r="Q19" s="222">
+      <c r="Q19" s="234">
         <v>-6.93</v>
       </c>
-      <c r="R19" s="227">
+      <c r="R19" s="231">
         <v>-7.3</v>
       </c>
-      <c r="S19" s="228">
+      <c r="S19" s="226">
         <v>-6.57</v>
       </c>
-      <c r="T19" s="229">
-        <v>59.49</v>
+      <c r="T19" s="227">
+        <v>58.76</v>
       </c>
     </row>
     <row r="20">
@@ -8886,7 +8902,7 @@
       <c r="C20" t="str">
         <v>603778</v>
       </c>
-      <c r="D20" s="241" t="str">
+      <c r="D20" s="244" t="str">
         <v>净卖: -3366.51万</v>
       </c>
       <c r="E20">
@@ -8901,41 +8917,41 @@
       <c r="H20">
         <v>6.69</v>
       </c>
-      <c r="I20" s="245">
+      <c r="I20" s="240">
         <v>3.07</v>
       </c>
-      <c r="J20" s="235">
+      <c r="J20" s="245">
         <v>13.33</v>
       </c>
-      <c r="K20" s="246">
+      <c r="K20" s="241">
         <v>5.33</v>
       </c>
-      <c r="L20" s="236">
+      <c r="L20" s="238">
         <v>8.67</v>
       </c>
-      <c r="M20" s="247">
+      <c r="M20" s="242">
         <v>19.6</v>
       </c>
-      <c r="N20" s="237">
+      <c r="N20" s="246">
         <v>7.6</v>
       </c>
-      <c r="O20" s="242">
+      <c r="O20" s="239">
         <v>-2</v>
       </c>
-      <c r="P20" s="238">
+      <c r="P20" s="235">
         <v>7.87</v>
       </c>
-      <c r="Q20" s="243">
+      <c r="Q20" s="247">
         <v>18.67</v>
       </c>
-      <c r="R20" s="244">
+      <c r="R20" s="243">
         <v>27.73</v>
       </c>
-      <c r="S20" s="239">
+      <c r="S20" s="236">
         <v>40.53</v>
       </c>
-      <c r="T20" s="240">
-        <v>251.47</v>
+      <c r="T20" s="237">
+        <v>236.93</v>
       </c>
     </row>
     <row r="21">
@@ -8948,7 +8964,7 @@
       <c r="C21" t="str">
         <v>600252</v>
       </c>
-      <c r="D21" s="252" t="str">
+      <c r="D21" s="250" t="str">
         <v>净卖: -331.54万</v>
       </c>
       <c r="E21">
@@ -8966,38 +8982,38 @@
       <c r="I21" s="259">
         <v>9.67</v>
       </c>
-      <c r="J21" s="260">
+      <c r="J21" s="251">
         <v>6.32</v>
       </c>
-      <c r="K21" s="249">
+      <c r="K21" s="254">
         <v>7.81</v>
       </c>
-      <c r="L21" s="256">
+      <c r="L21" s="255">
         <v>10.41</v>
       </c>
-      <c r="M21" s="248">
+      <c r="M21" s="252">
         <v>9.29</v>
       </c>
-      <c r="N21" s="257">
+      <c r="N21" s="256">
         <v>11.9</v>
       </c>
-      <c r="O21" s="253">
+      <c r="O21" s="257">
         <v>10.78</v>
       </c>
       <c r="P21" s="258">
         <v>11.52</v>
       </c>
-      <c r="Q21" s="250">
+      <c r="Q21" s="260">
         <v>10.04</v>
       </c>
-      <c r="R21" s="254">
+      <c r="R21" s="248">
         <v>6.32</v>
       </c>
-      <c r="S21" s="255">
+      <c r="S21" s="249">
         <v>5.58</v>
       </c>
-      <c r="T21" s="251">
-        <v>-8.92</v>
+      <c r="T21" s="253">
+        <v>-8.55</v>
       </c>
     </row>
     <row r="22">
@@ -9010,7 +9026,7 @@
       <c r="C22" t="str">
         <v>003018</v>
       </c>
-      <c r="D22" s="265" t="str">
+      <c r="D22" s="266" t="str">
         <v>净卖: -1172.31万</v>
       </c>
       <c r="E22">
@@ -9025,41 +9041,41 @@
       <c r="H22">
         <v>10.01</v>
       </c>
-      <c r="I22" s="269">
+      <c r="I22" s="271">
         <v>0</v>
       </c>
-      <c r="J22" s="270">
+      <c r="J22" s="267">
         <v>-9.99</v>
       </c>
-      <c r="K22" s="266">
+      <c r="K22" s="265">
         <v>-18.85</v>
       </c>
-      <c r="L22" s="273">
+      <c r="L22" s="268">
         <v>-18.77</v>
       </c>
-      <c r="M22" s="267">
+      <c r="M22" s="272">
         <v>-15.14</v>
       </c>
-      <c r="N22" s="261">
+      <c r="N22" s="264">
         <v>-23.48</v>
       </c>
-      <c r="O22" s="271">
+      <c r="O22" s="273">
         <v>-18.81</v>
       </c>
-      <c r="P22" s="262">
+      <c r="P22" s="269">
         <v>-22.71</v>
       </c>
-      <c r="Q22" s="263">
+      <c r="Q22" s="261">
         <v>-25.49</v>
       </c>
-      <c r="R22" s="264">
+      <c r="R22" s="270">
         <v>-25.49</v>
       </c>
-      <c r="S22" s="268">
+      <c r="S22" s="262">
         <v>-29.4</v>
       </c>
-      <c r="T22" s="272">
-        <v>123.64</v>
+      <c r="T22" s="263">
+        <v>122.35</v>
       </c>
     </row>
     <row r="23">
@@ -9072,7 +9088,7 @@
       <c r="C23" t="str">
         <v>603958</v>
       </c>
-      <c r="D23" s="282" t="str">
+      <c r="D23" s="277" t="str">
         <v>净买: 48.48万</v>
       </c>
       <c r="E23">
@@ -9087,41 +9103,41 @@
       <c r="H23">
         <v>-5.98</v>
       </c>
-      <c r="I23" s="286">
+      <c r="I23" s="279">
         <v>-4.29</v>
       </c>
-      <c r="J23" s="278">
+      <c r="J23" s="283">
         <v>-7.64</v>
       </c>
-      <c r="K23" s="280">
+      <c r="K23" s="284">
         <v>-8.21</v>
       </c>
-      <c r="L23" s="274">
+      <c r="L23" s="285">
         <v>-4.29</v>
       </c>
-      <c r="M23" s="281">
+      <c r="M23" s="280">
         <v>-7.5</v>
       </c>
-      <c r="N23" s="283">
+      <c r="N23" s="286">
         <v>-8.36</v>
       </c>
       <c r="O23" s="275">
         <v>-10.57</v>
       </c>
-      <c r="P23" s="284">
+      <c r="P23" s="278">
         <v>-8.86</v>
       </c>
-      <c r="Q23" s="285">
+      <c r="Q23" s="281">
         <v>-7.43</v>
       </c>
       <c r="R23" s="276">
         <v>-8</v>
       </c>
-      <c r="S23" s="279">
+      <c r="S23" s="282">
         <v>-8.71</v>
       </c>
-      <c r="T23" s="277">
-        <v>68.57</v>
+      <c r="T23" s="274">
+        <v>66.36</v>
       </c>
     </row>
     <row r="24">
@@ -9134,7 +9150,7 @@
       <c r="C24" t="str">
         <v>002187</v>
       </c>
-      <c r="D24" s="294" t="str">
+      <c r="D24" s="291" t="str">
         <v>净卖: -1062.98万</v>
       </c>
       <c r="E24">
@@ -9149,41 +9165,41 @@
       <c r="H24">
         <v>2</v>
       </c>
-      <c r="I24" s="290">
+      <c r="I24" s="287">
         <v>7.83</v>
       </c>
-      <c r="J24" s="291">
+      <c r="J24" s="297">
         <v>3.92</v>
       </c>
-      <c r="K24" s="288">
+      <c r="K24" s="295">
         <v>3.26</v>
       </c>
-      <c r="L24" s="295">
+      <c r="L24" s="292">
         <v>7.57</v>
       </c>
-      <c r="M24" s="292">
+      <c r="M24" s="298">
         <v>10.05</v>
       </c>
-      <c r="N24" s="296">
+      <c r="N24" s="288">
         <v>8.88</v>
       </c>
-      <c r="O24" s="289">
+      <c r="O24" s="299">
         <v>4.96</v>
       </c>
-      <c r="P24" s="297">
+      <c r="P24" s="289">
         <v>7.83</v>
       </c>
       <c r="Q24" s="293">
         <v>6.4</v>
       </c>
-      <c r="R24" s="298">
+      <c r="R24" s="294">
         <v>17.1</v>
       </c>
-      <c r="S24" s="299">
+      <c r="S24" s="296">
         <v>5.61</v>
       </c>
-      <c r="T24" s="287">
-        <v>-20.5</v>
+      <c r="T24" s="290">
+        <v>-20.37</v>
       </c>
     </row>
     <row r="25">
@@ -9196,7 +9212,7 @@
       <c r="C25" t="str">
         <v>688273</v>
       </c>
-      <c r="D25" s="308" t="str">
+      <c r="D25" s="301" t="str">
         <v>净卖: -963.67万</v>
       </c>
       <c r="E25">
@@ -9211,41 +9227,41 @@
       <c r="H25">
         <v>-1.99</v>
       </c>
-      <c r="I25" s="300">
+      <c r="I25" s="310">
         <v>-8.57</v>
       </c>
-      <c r="J25" s="301">
+      <c r="J25" s="302">
         <v>-8.03</v>
       </c>
-      <c r="K25" s="309">
+      <c r="K25" s="311">
         <v>-11.27</v>
       </c>
-      <c r="L25" s="304">
+      <c r="L25" s="305">
         <v>-8.63</v>
       </c>
-      <c r="M25" s="305">
+      <c r="M25" s="304">
         <v>-13</v>
       </c>
       <c r="N25" s="306">
         <v>-13.83</v>
       </c>
-      <c r="O25" s="311">
+      <c r="O25" s="307">
         <v>-17.22</v>
       </c>
-      <c r="P25" s="312">
+      <c r="P25" s="308">
         <v>-20.37</v>
       </c>
-      <c r="Q25" s="302">
+      <c r="Q25" s="312">
         <v>-20.43</v>
       </c>
-      <c r="R25" s="307">
+      <c r="R25" s="303">
         <v>-22.83</v>
       </c>
-      <c r="S25" s="303">
+      <c r="S25" s="300">
         <v>-23.42</v>
       </c>
-      <c r="T25" s="310">
-        <v>-22.17</v>
+      <c r="T25" s="309">
+        <v>-23.08</v>
       </c>
     </row>
     <row r="26">
@@ -9258,7 +9274,7 @@
       <c r="C26" t="str">
         <v>688523</v>
       </c>
-      <c r="D26" s="325" t="str">
+      <c r="D26" s="323" t="str">
         <v>净卖: -2032.96万</v>
       </c>
       <c r="E26">
@@ -9273,41 +9289,41 @@
       <c r="H26">
         <v>-6.9</v>
       </c>
-      <c r="I26" s="315">
+      <c r="I26" s="320">
         <v>-12.28</v>
       </c>
-      <c r="J26" s="320">
+      <c r="J26" s="321">
         <v>-15.94</v>
       </c>
-      <c r="K26" s="316">
+      <c r="K26" s="314">
         <v>-22.53</v>
       </c>
-      <c r="L26" s="313">
+      <c r="L26" s="324">
         <v>-23.98</v>
       </c>
-      <c r="M26" s="314">
+      <c r="M26" s="315">
         <v>-21.69</v>
       </c>
-      <c r="N26" s="321">
+      <c r="N26" s="325">
         <v>-28.64</v>
       </c>
       <c r="O26" s="317">
         <v>-29.76</v>
       </c>
-      <c r="P26" s="322">
+      <c r="P26" s="316">
         <v>-23.74</v>
       </c>
-      <c r="Q26" s="318">
+      <c r="Q26" s="313">
         <v>-13.62</v>
       </c>
-      <c r="R26" s="319">
+      <c r="R26" s="318">
         <v>-23.24</v>
       </c>
-      <c r="S26" s="323">
+      <c r="S26" s="319">
         <v>-24.4</v>
       </c>
-      <c r="T26" s="324">
-        <v>-24.06</v>
+      <c r="T26" s="322">
+        <v>-26.93</v>
       </c>
     </row>
     <row r="27">
@@ -9320,7 +9336,7 @@
       <c r="C27" t="str">
         <v>002131</v>
       </c>
-      <c r="D27" s="329" t="str">
+      <c r="D27" s="335" t="str">
         <v>净买: 384.51万</v>
       </c>
       <c r="E27">
@@ -9335,41 +9351,41 @@
       <c r="H27">
         <v>-10</v>
       </c>
-      <c r="I27" s="326">
+      <c r="I27" s="327">
         <v>0</v>
       </c>
-      <c r="J27" s="330">
+      <c r="J27" s="336">
         <v>-10.04</v>
       </c>
-      <c r="K27" s="327">
+      <c r="K27" s="331">
         <v>-10.26</v>
       </c>
-      <c r="L27" s="335">
+      <c r="L27" s="332">
         <v>-14.53</v>
       </c>
-      <c r="M27" s="331">
+      <c r="M27" s="337">
         <v>-9.19</v>
       </c>
-      <c r="N27" s="328">
+      <c r="N27" s="329">
         <v>-6.3</v>
       </c>
-      <c r="O27" s="332">
+      <c r="O27" s="338">
         <v>2.24</v>
       </c>
-      <c r="P27" s="333">
+      <c r="P27" s="330">
         <v>-0.43</v>
       </c>
-      <c r="Q27" s="334">
+      <c r="Q27" s="326">
         <v>5.88</v>
       </c>
-      <c r="R27" s="336">
+      <c r="R27" s="333">
         <v>8.76</v>
       </c>
-      <c r="S27" s="337">
+      <c r="S27" s="328">
         <v>-1.07</v>
       </c>
-      <c r="T27" s="338">
-        <v>-27.35</v>
+      <c r="T27" s="334">
+        <v>-29.7</v>
       </c>
     </row>
     <row r="28">
@@ -9382,7 +9398,7 @@
       <c r="C28" t="str">
         <v>603698</v>
       </c>
-      <c r="D28" s="345" t="str">
+      <c r="D28" s="347" t="str">
         <v>净卖: -1965.64万</v>
       </c>
       <c r="E28">
@@ -9397,41 +9413,41 @@
       <c r="H28">
         <v>-1.78</v>
       </c>
-      <c r="I28" s="339">
+      <c r="I28" s="340">
         <v>-8.38</v>
       </c>
-      <c r="J28" s="340">
+      <c r="J28" s="341">
         <v>-9.03</v>
       </c>
-      <c r="K28" s="346">
+      <c r="K28" s="342">
         <v>-9.19</v>
       </c>
-      <c r="L28" s="342">
+      <c r="L28" s="344">
         <v>-8.54</v>
       </c>
-      <c r="M28" s="343">
+      <c r="M28" s="351">
         <v>-7.3</v>
       </c>
-      <c r="N28" s="349">
+      <c r="N28" s="339">
         <v>-6.49</v>
       </c>
-      <c r="O28" s="344">
+      <c r="O28" s="348">
         <v>0.59</v>
       </c>
-      <c r="P28" s="350">
+      <c r="P28" s="343">
         <v>2.27</v>
       </c>
-      <c r="Q28" s="341">
+      <c r="Q28" s="349">
         <v>2.54</v>
       </c>
-      <c r="R28" s="351">
+      <c r="R28" s="345">
         <v>4.92</v>
       </c>
-      <c r="S28" s="347">
+      <c r="S28" s="350">
         <v>10.54</v>
       </c>
-      <c r="T28" s="348">
-        <v>8.81</v>
+      <c r="T28" s="346">
+        <v>6.73</v>
       </c>
     </row>
     <row r="29">
@@ -9444,7 +9460,7 @@
       <c r="C29" t="str">
         <v>603619</v>
       </c>
-      <c r="D29" s="363" t="str">
+      <c r="D29" s="360" t="str">
         <v>净买: 3411.20万</v>
       </c>
       <c r="E29">
@@ -9462,38 +9478,38 @@
       <c r="I29" s="359">
         <v>-8.71</v>
       </c>
-      <c r="J29" s="360">
+      <c r="J29" s="363">
         <v>-17.84</v>
       </c>
-      <c r="K29" s="352">
+      <c r="K29" s="361">
         <v>-20.82</v>
       </c>
-      <c r="L29" s="361">
+      <c r="L29" s="364">
         <v>-14.71</v>
       </c>
-      <c r="M29" s="355">
+      <c r="M29" s="356">
         <v>-18.76</v>
       </c>
-      <c r="N29" s="356">
+      <c r="N29" s="362">
         <v>-14.24</v>
       </c>
-      <c r="O29" s="362">
+      <c r="O29" s="357">
         <v>-16.47</v>
       </c>
-      <c r="P29" s="357">
+      <c r="P29" s="352">
         <v>-12.61</v>
       </c>
-      <c r="Q29" s="353">
+      <c r="Q29" s="358">
         <v>-7.45</v>
       </c>
-      <c r="R29" s="364">
+      <c r="R29" s="353">
         <v>-9.16</v>
       </c>
-      <c r="S29" s="358">
+      <c r="S29" s="354">
         <v>-12.42</v>
       </c>
-      <c r="T29" s="354">
-        <v>-11.24</v>
+      <c r="T29" s="355">
+        <v>-8.26</v>
       </c>
     </row>
     <row r="30">
@@ -9506,7 +9522,7 @@
       <c r="C30" t="str">
         <v>688530</v>
       </c>
-      <c r="D30" s="371" t="str">
+      <c r="D30" s="370" t="str">
         <v>净卖: -1311.39万</v>
       </c>
       <c r="E30">
@@ -9521,41 +9537,41 @@
       <c r="H30">
         <v>-2.23</v>
       </c>
-      <c r="I30" s="375">
+      <c r="I30" s="371">
         <v>15.5</v>
       </c>
-      <c r="J30" s="369">
+      <c r="J30" s="372">
         <v>11.55</v>
       </c>
-      <c r="K30" s="366">
+      <c r="K30" s="376">
         <v>20.14</v>
       </c>
-      <c r="L30" s="372">
+      <c r="L30" s="373">
         <v>15.82</v>
       </c>
-      <c r="M30" s="376">
+      <c r="M30" s="377">
         <v>32.04</v>
       </c>
-      <c r="N30" s="377">
+      <c r="N30" s="374">
         <v>29.72</v>
       </c>
-      <c r="O30" s="370">
+      <c r="O30" s="367">
         <v>28.01</v>
       </c>
-      <c r="P30" s="373">
+      <c r="P30" s="365">
         <v>31.8</v>
       </c>
-      <c r="Q30" s="365">
+      <c r="Q30" s="375">
         <v>58.17</v>
       </c>
-      <c r="R30" s="367">
+      <c r="R30" s="368">
         <v>66.44</v>
       </c>
-      <c r="S30" s="374">
+      <c r="S30" s="366">
         <v>58.53</v>
       </c>
-      <c r="T30" s="368">
-        <v>84.58</v>
+      <c r="T30" s="369">
+        <v>117.3</v>
       </c>
     </row>
     <row r="31">
@@ -9568,7 +9584,7 @@
       <c r="C31" t="str">
         <v>688530</v>
       </c>
-      <c r="D31" s="388" t="str">
+      <c r="D31" s="387" t="str">
         <v>净卖: -4653.87万</v>
       </c>
       <c r="E31">
@@ -9583,41 +9599,41 @@
       <c r="H31">
         <v>-1.06</v>
       </c>
-      <c r="I31" s="378">
+      <c r="I31" s="383">
         <v>21.29</v>
       </c>
-      <c r="J31" s="379">
+      <c r="J31" s="380">
         <v>27.63</v>
       </c>
-      <c r="K31" s="386">
+      <c r="K31" s="381">
         <v>21.57</v>
       </c>
-      <c r="L31" s="380">
+      <c r="L31" s="384">
         <v>13.14</v>
       </c>
-      <c r="M31" s="389">
+      <c r="M31" s="378">
         <v>8.21</v>
       </c>
-      <c r="N31" s="382">
+      <c r="N31" s="379">
         <v>6.59</v>
       </c>
-      <c r="O31" s="387">
+      <c r="O31" s="385">
         <v>1.78</v>
       </c>
-      <c r="P31" s="383">
+      <c r="P31" s="388">
         <v>0.09</v>
       </c>
-      <c r="Q31" s="384">
+      <c r="Q31" s="382">
         <v>6.43</v>
       </c>
-      <c r="R31" s="385">
+      <c r="R31" s="389">
         <v>1.5</v>
       </c>
-      <c r="S31" s="390">
+      <c r="S31" s="386">
         <v>5.55</v>
       </c>
-      <c r="T31" s="381">
-        <v>41.54</v>
+      <c r="T31" s="390">
+        <v>66.64</v>
       </c>
     </row>
     <row r="32">
@@ -9645,41 +9661,41 @@
       <c r="H32">
         <v>6.88</v>
       </c>
-      <c r="I32" s="398">
+      <c r="I32" s="394">
         <v>2.94</v>
       </c>
-      <c r="J32" s="400">
+      <c r="J32" s="395">
         <v>-0.72</v>
       </c>
       <c r="K32" s="401">
         <v>-2.86</v>
       </c>
-      <c r="L32" s="391">
+      <c r="L32" s="396">
         <v>-5.36</v>
       </c>
-      <c r="M32" s="394">
+      <c r="M32" s="397">
         <v>-7.83</v>
       </c>
-      <c r="N32" s="395">
+      <c r="N32" s="402">
         <v>-11.24</v>
       </c>
-      <c r="O32" s="396">
+      <c r="O32" s="391">
         <v>-9.85</v>
       </c>
-      <c r="P32" s="392">
+      <c r="P32" s="403">
         <v>-6.2</v>
       </c>
-      <c r="Q32" s="402">
+      <c r="Q32" s="398">
         <v>-1.47</v>
       </c>
-      <c r="R32" s="403">
+      <c r="R32" s="399">
         <v>6.52</v>
       </c>
-      <c r="S32" s="397">
+      <c r="S32" s="400">
         <v>13.79</v>
       </c>
-      <c r="T32" s="399">
-        <v>-13.79</v>
+      <c r="T32" s="392">
+        <v>-16.13</v>
       </c>
     </row>
     <row r="33">
@@ -9692,7 +9708,7 @@
       <c r="C33" t="str">
         <v>600516</v>
       </c>
-      <c r="D33" s="413" t="str">
+      <c r="D33" s="412" t="str">
         <v>净卖: -4735.13万</v>
       </c>
       <c r="E33">
@@ -9707,41 +9723,41 @@
       <c r="H33">
         <v>0.8</v>
       </c>
-      <c r="I33" s="407">
+      <c r="I33" s="404">
         <v>9.21</v>
       </c>
-      <c r="J33" s="414">
+      <c r="J33" s="407">
         <v>6.83</v>
       </c>
-      <c r="K33" s="416">
+      <c r="K33" s="405">
         <v>5.87</v>
       </c>
-      <c r="L33" s="404">
+      <c r="L33" s="408">
         <v>7.46</v>
       </c>
-      <c r="M33" s="408">
+      <c r="M33" s="413">
         <v>10.32</v>
       </c>
       <c r="N33" s="409">
         <v>12.86</v>
       </c>
-      <c r="O33" s="411">
+      <c r="O33" s="414">
         <v>7.3</v>
       </c>
       <c r="P33" s="410">
         <v>4.92</v>
       </c>
-      <c r="Q33" s="405">
+      <c r="Q33" s="411">
         <v>1.11</v>
       </c>
-      <c r="R33" s="406">
+      <c r="R33" s="415">
         <v>-1.59</v>
       </c>
-      <c r="S33" s="412">
+      <c r="S33" s="416">
         <v>-5.24</v>
       </c>
-      <c r="T33" s="415">
-        <v>-14.29</v>
+      <c r="T33" s="406">
+        <v>-14.76</v>
       </c>
     </row>
     <row r="34">
@@ -9754,7 +9770,7 @@
       <c r="C34" t="str">
         <v>300131</v>
       </c>
-      <c r="D34" s="429" t="str">
+      <c r="D34" s="427" t="str">
         <v>净卖: -9057.02万</v>
       </c>
       <c r="E34">
@@ -9769,41 +9785,41 @@
       <c r="H34">
         <v>2.57</v>
       </c>
-      <c r="I34" s="424">
+      <c r="I34" s="423">
         <v>-18.81</v>
       </c>
-      <c r="J34" s="419">
+      <c r="J34" s="424">
         <v>-16.59</v>
       </c>
-      <c r="K34" s="427">
+      <c r="K34" s="428">
         <v>-10.32</v>
       </c>
-      <c r="L34" s="420">
+      <c r="L34" s="429">
         <v>-11.8</v>
       </c>
-      <c r="M34" s="421">
+      <c r="M34" s="417">
         <v>-16.08</v>
       </c>
-      <c r="N34" s="422">
+      <c r="N34" s="420">
         <v>-14.6</v>
       </c>
-      <c r="O34" s="428">
+      <c r="O34" s="422">
         <v>-17.4</v>
       </c>
-      <c r="P34" s="425">
+      <c r="P34" s="418">
         <v>-16.22</v>
       </c>
-      <c r="Q34" s="417">
+      <c r="Q34" s="421">
         <v>-16.74</v>
       </c>
-      <c r="R34" s="426">
+      <c r="R34" s="425">
         <v>-9.44</v>
       </c>
-      <c r="S34" s="418">
+      <c r="S34" s="419">
         <v>-5.24</v>
       </c>
-      <c r="T34" s="423">
-        <v>26.92</v>
+      <c r="T34" s="426">
+        <v>21.24</v>
       </c>
     </row>
     <row r="35">
@@ -9816,7 +9832,7 @@
       <c r="C35" t="str">
         <v>603189</v>
       </c>
-      <c r="D35" s="434" t="str">
+      <c r="D35" s="436" t="str">
         <v>净买: 91.85万</v>
       </c>
       <c r="E35">
@@ -9831,13 +9847,13 @@
       <c r="H35">
         <v>-9.97</v>
       </c>
-      <c r="I35" s="435">
+      <c r="I35" s="437">
         <v>0</v>
       </c>
-      <c r="J35" s="436">
+      <c r="J35" s="433">
         <v>3.42</v>
       </c>
-      <c r="K35" s="437">
+      <c r="K35" s="434">
         <v>-6.85</v>
       </c>
       <c r="L35" s="430">
@@ -9846,16 +9862,18 @@
       <c r="M35" s="431">
         <v>-8.01</v>
       </c>
-      <c r="N35" s="432">
+      <c r="N35" s="438">
         <v>-9.61</v>
       </c>
-      <c r="O35" t="str"/>
+      <c r="O35" s="432">
+        <v>-6.26</v>
+      </c>
       <c r="P35" t="str"/>
       <c r="Q35" t="str"/>
       <c r="R35" t="str"/>
       <c r="S35" t="str"/>
-      <c r="T35" s="433">
-        <v>-9.61</v>
+      <c r="T35" s="435">
+        <v>-6.26</v>
       </c>
     </row>
     <row r="36">
@@ -9888,7 +9906,7 @@
         <v>34</v>
       </c>
       <c r="O36">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P36">
         <v>33</v>
@@ -9917,40 +9935,40 @@
       <c r="F37" t="str"/>
       <c r="G37" t="str"/>
       <c r="H37" t="str"/>
-      <c r="I37" s="445">
+      <c r="I37" s="439">
         <v>52.94</v>
       </c>
-      <c r="J37" s="439">
+      <c r="J37" s="445">
         <v>58.82</v>
       </c>
-      <c r="K37" s="447">
+      <c r="K37" s="440">
         <v>50</v>
       </c>
-      <c r="L37" s="448">
+      <c r="L37" s="441">
         <v>52.94</v>
       </c>
-      <c r="M37" s="440">
+      <c r="M37" s="449">
         <v>58.82</v>
       </c>
-      <c r="N37" s="443">
+      <c r="N37" s="442">
         <v>55.88</v>
       </c>
-      <c r="O37" s="446">
+      <c r="O37" s="443">
+        <v>52.94</v>
+      </c>
+      <c r="P37" s="450">
         <v>54.55</v>
       </c>
-      <c r="P37" s="449">
-        <v>54.55</v>
-      </c>
-      <c r="Q37" s="441">
+      <c r="Q37" s="444">
         <v>51.52</v>
       </c>
-      <c r="R37" s="444">
+      <c r="R37" s="446">
         <v>45.45</v>
       </c>
-      <c r="S37" s="442">
+      <c r="S37" s="447">
         <v>45.45</v>
       </c>
-      <c r="T37" s="438">
+      <c r="T37" s="448">
         <v>41.18</v>
       </c>
     </row>
@@ -9965,41 +9983,41 @@
       <c r="F38" t="str"/>
       <c r="G38" t="str"/>
       <c r="H38" t="str"/>
-      <c r="I38" s="458">
+      <c r="I38" s="457">
         <v>2.64</v>
       </c>
-      <c r="J38" s="454">
+      <c r="J38" s="460">
         <v>3.67</v>
       </c>
-      <c r="K38" s="451">
+      <c r="K38" s="455">
         <v>2.87</v>
       </c>
-      <c r="L38" s="455">
+      <c r="L38" s="461">
         <v>3.91</v>
       </c>
-      <c r="M38" s="459">
+      <c r="M38" s="452">
         <v>4.02</v>
       </c>
-      <c r="N38" s="452">
+      <c r="N38" s="458">
         <v>2.26</v>
       </c>
-      <c r="O38" s="460">
-        <v>1.54</v>
-      </c>
-      <c r="P38" s="461">
+      <c r="O38" s="462">
+        <v>1.31</v>
+      </c>
+      <c r="P38" s="459">
         <v>1.8</v>
       </c>
-      <c r="Q38" s="456">
+      <c r="Q38" s="451">
         <v>2.18</v>
       </c>
       <c r="R38" s="453">
         <v>1.38</v>
       </c>
-      <c r="S38" s="450">
+      <c r="S38" s="456">
         <v>1.44</v>
       </c>
-      <c r="T38" s="457">
-        <v>23.32</v>
+      <c r="T38" s="454">
+        <v>23.52</v>
       </c>
     </row>
   </sheetData>
